--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="944">
   <si>
     <t>code</t>
   </si>
@@ -34,6 +34,9 @@
     <t>status</t>
   </si>
   <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
     <t>11110</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>Formal and non-formal education for basic life skills for young people and adults (adults education); literacy and numeracy training. Excludes health education (12261) and activities related to prevention of noncommunicable diseases. (123xx).</t>
   </si>
   <si>
+    <t>Insufficiently granular</t>
+  </si>
+  <si>
     <t>11231</t>
   </si>
   <si>
@@ -2414,6 +2420,9 @@
   </si>
   <si>
     <t>430</t>
+  </si>
+  <si>
+    <t>Unmappable</t>
   </si>
   <si>
     <t>43030</t>
@@ -3168,10 +3177,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F312"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3190,5211 +3199,5277 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
       <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
       <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
         <v>77</v>
       </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" t="s">
-        <v>100</v>
-      </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s">
         <v>121</v>
       </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" t="s">
-        <v>119</v>
-      </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
         <v>137</v>
       </c>
-      <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" t="s">
-        <v>135</v>
-      </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" t="s">
         <v>171</v>
       </c>
-      <c r="C53" t="s">
-        <v>172</v>
-      </c>
-      <c r="D53" t="s">
-        <v>169</v>
-      </c>
       <c r="F53" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C59" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F61" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" t="s">
+        <v>171</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" t="s">
+        <v>205</v>
+      </c>
+      <c r="D63" t="s">
+        <v>171</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" t="s">
+        <v>171</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" t="s">
+        <v>210</v>
+      </c>
+      <c r="C65" t="s">
+        <v>211</v>
+      </c>
+      <c r="D65" t="s">
+        <v>171</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" t="s">
+        <v>213</v>
+      </c>
+      <c r="C66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>171</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>215</v>
+      </c>
+      <c r="B67" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" t="s">
+        <v>171</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>218</v>
+      </c>
+      <c r="B68" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68" t="s">
+        <v>171</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>221</v>
+      </c>
+      <c r="B69" t="s">
+        <v>222</v>
+      </c>
+      <c r="C69" t="s">
+        <v>223</v>
+      </c>
+      <c r="D69" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>224</v>
+      </c>
+      <c r="B70" t="s">
+        <v>225</v>
+      </c>
+      <c r="C70" t="s">
+        <v>226</v>
+      </c>
+      <c r="D70" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" t="s">
+        <v>228</v>
+      </c>
+      <c r="C71" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" t="s">
+        <v>171</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" t="s">
+        <v>232</v>
+      </c>
+      <c r="D72" t="s">
+        <v>171</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>233</v>
+      </c>
+      <c r="B73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D73" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>236</v>
+      </c>
+      <c r="B74" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74" t="s">
+        <v>238</v>
+      </c>
+      <c r="D74" t="s">
+        <v>171</v>
+      </c>
+      <c r="F74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>239</v>
+      </c>
+      <c r="B75" t="s">
+        <v>240</v>
+      </c>
+      <c r="C75" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>242</v>
+      </c>
+      <c r="B76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C76" t="s">
+        <v>244</v>
+      </c>
+      <c r="D76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>245</v>
+      </c>
+      <c r="B77" t="s">
+        <v>246</v>
+      </c>
+      <c r="C77" t="s">
+        <v>247</v>
+      </c>
+      <c r="D77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>248</v>
+      </c>
+      <c r="B78" t="s">
+        <v>249</v>
+      </c>
+      <c r="D78" t="s">
+        <v>171</v>
+      </c>
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>250</v>
+      </c>
+      <c r="B79" t="s">
+        <v>251</v>
+      </c>
+      <c r="C79" t="s">
+        <v>252</v>
+      </c>
+      <c r="D79" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" t="s">
         <v>199</v>
       </c>
-      <c r="C62" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" t="s">
-        <v>201</v>
-      </c>
-      <c r="B63" t="s">
-        <v>202</v>
-      </c>
-      <c r="C63" t="s">
-        <v>203</v>
-      </c>
-      <c r="D63" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" t="s">
-        <v>204</v>
-      </c>
-      <c r="B64" t="s">
-        <v>205</v>
-      </c>
-      <c r="C64" t="s">
-        <v>206</v>
-      </c>
-      <c r="D64" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>207</v>
-      </c>
-      <c r="B65" t="s">
-        <v>208</v>
-      </c>
-      <c r="C65" t="s">
-        <v>209</v>
-      </c>
-      <c r="D65" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>210</v>
-      </c>
-      <c r="B66" t="s">
-        <v>211</v>
-      </c>
-      <c r="C66" t="s">
-        <v>212</v>
-      </c>
-      <c r="D66" t="s">
-        <v>169</v>
-      </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>213</v>
-      </c>
-      <c r="B67" t="s">
-        <v>214</v>
-      </c>
-      <c r="C67" t="s">
-        <v>215</v>
-      </c>
-      <c r="D67" t="s">
-        <v>169</v>
-      </c>
-      <c r="F67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>216</v>
-      </c>
-      <c r="B68" t="s">
-        <v>217</v>
-      </c>
-      <c r="C68" t="s">
-        <v>218</v>
-      </c>
-      <c r="D68" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>219</v>
-      </c>
-      <c r="B69" t="s">
-        <v>220</v>
-      </c>
-      <c r="C69" t="s">
-        <v>221</v>
-      </c>
-      <c r="D69" t="s">
-        <v>169</v>
-      </c>
-      <c r="F69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
-        <v>222</v>
-      </c>
-      <c r="B70" t="s">
-        <v>223</v>
-      </c>
-      <c r="C70" t="s">
-        <v>224</v>
-      </c>
-      <c r="D70" t="s">
-        <v>169</v>
-      </c>
-      <c r="F70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
-        <v>225</v>
-      </c>
-      <c r="B71" t="s">
-        <v>226</v>
-      </c>
-      <c r="C71" t="s">
-        <v>227</v>
-      </c>
-      <c r="D71" t="s">
-        <v>169</v>
-      </c>
-      <c r="F71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
-        <v>228</v>
-      </c>
-      <c r="B72" t="s">
-        <v>229</v>
-      </c>
-      <c r="C72" t="s">
-        <v>230</v>
-      </c>
-      <c r="D72" t="s">
-        <v>169</v>
-      </c>
-      <c r="F72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>231</v>
-      </c>
-      <c r="B73" t="s">
-        <v>232</v>
-      </c>
-      <c r="C73" t="s">
-        <v>233</v>
-      </c>
-      <c r="D73" t="s">
-        <v>169</v>
-      </c>
-      <c r="F73" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
-        <v>234</v>
-      </c>
-      <c r="B74" t="s">
-        <v>235</v>
-      </c>
-      <c r="C74" t="s">
-        <v>236</v>
-      </c>
-      <c r="D74" t="s">
-        <v>169</v>
-      </c>
-      <c r="F74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>237</v>
-      </c>
-      <c r="B75" t="s">
-        <v>238</v>
-      </c>
-      <c r="C75" t="s">
-        <v>239</v>
-      </c>
-      <c r="D75" t="s">
-        <v>169</v>
-      </c>
-      <c r="F75" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
-        <v>240</v>
-      </c>
-      <c r="B76" t="s">
-        <v>241</v>
-      </c>
-      <c r="C76" t="s">
-        <v>242</v>
-      </c>
-      <c r="D76" t="s">
-        <v>169</v>
-      </c>
-      <c r="F76" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
-        <v>243</v>
-      </c>
-      <c r="B77" t="s">
-        <v>244</v>
-      </c>
-      <c r="C77" t="s">
-        <v>245</v>
-      </c>
-      <c r="D77" t="s">
-        <v>169</v>
-      </c>
-      <c r="F77" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
-        <v>246</v>
-      </c>
-      <c r="B78" t="s">
-        <v>247</v>
-      </c>
-      <c r="D78" t="s">
-        <v>169</v>
-      </c>
-      <c r="F78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>248</v>
-      </c>
-      <c r="B79" t="s">
-        <v>249</v>
-      </c>
-      <c r="C79" t="s">
-        <v>250</v>
-      </c>
-      <c r="D79" t="s">
-        <v>169</v>
-      </c>
-      <c r="F79" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C80" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D80" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D81" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D82" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D83" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D84" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D85" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B86" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C86" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D86" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C87" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D87" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D88" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D89" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B90" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D90" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D91" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F91" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D92" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B93" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C93" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D93" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D94" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F94" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
+        <v>295</v>
+      </c>
+      <c r="B95" t="s">
         <v>293</v>
       </c>
-      <c r="B95" t="s">
-        <v>291</v>
-      </c>
       <c r="C95" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D95" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B96" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C96" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D96" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F96" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B97" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C97" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D97" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F97" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B98" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C98" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D98" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B99" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C99" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D99" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B100" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" t="s">
         <v>309</v>
       </c>
-      <c r="C100" t="s">
-        <v>310</v>
-      </c>
-      <c r="D100" t="s">
-        <v>307</v>
-      </c>
       <c r="F100" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C101" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D101" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B102" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C102" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D102" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B103" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C103" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D103" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B104" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C104" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D104" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B105" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C105" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D105" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F105" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G105" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B106" t="s">
+        <v>330</v>
+      </c>
+      <c r="C106" t="s">
+        <v>331</v>
+      </c>
+      <c r="D106" t="s">
         <v>328</v>
       </c>
-      <c r="C106" t="s">
-        <v>329</v>
-      </c>
-      <c r="D106" t="s">
-        <v>326</v>
-      </c>
       <c r="F106" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B107" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C107" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D107" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F107" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B108" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C108" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D108" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F108" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B109" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C109" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D109" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F109" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C110" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D110" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F110" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C111" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F111" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C112" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D112" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F112" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B113" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C113" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D113" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F113" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B114" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C114" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D114" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B115" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C115" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D115" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G115" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B116" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C116" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D116" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F116" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B117" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C117" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D117" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B118" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C118" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D118" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B119" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D119" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F119" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B120" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D120" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F120" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B121" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C121" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D121" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F121" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B122" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C122" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D122" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F122" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B123" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C123" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D123" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G123" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s">
+        <v>383</v>
+      </c>
+      <c r="C124" t="s">
+        <v>384</v>
+      </c>
+      <c r="D124" t="s">
         <v>381</v>
       </c>
-      <c r="C124" t="s">
-        <v>382</v>
-      </c>
-      <c r="D124" t="s">
-        <v>379</v>
-      </c>
       <c r="F124" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D125" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F125" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B126" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F126" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F127" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G127" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B128" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C128" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F128" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C129" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F129" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B130" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C130" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F130" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B131" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C131" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B132" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C132" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B133" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C133" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B134" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C134" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F134" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B135" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C135" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D135" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F135" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B136" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B137" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C137" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F137" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G137" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B138" t="s">
+        <v>425</v>
+      </c>
+      <c r="D138" t="s">
         <v>423</v>
       </c>
-      <c r="D138" t="s">
-        <v>421</v>
-      </c>
       <c r="F138" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B139" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C139" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D139" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B140" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C140" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D140" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F140" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B141" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C141" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D141" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F141" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B142" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C142" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D142" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F142" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B143" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C143" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D143" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F143" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B144" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C144" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D144" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F144" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B145" t="s">
+        <v>446</v>
+      </c>
+      <c r="C145" t="s">
+        <v>447</v>
+      </c>
+      <c r="D145" t="s">
         <v>444</v>
       </c>
-      <c r="C145" t="s">
-        <v>445</v>
-      </c>
-      <c r="D145" t="s">
-        <v>442</v>
-      </c>
       <c r="F145" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B146" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C146" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D146" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F146" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B147" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C147" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D147" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F147" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B148" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C148" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D148" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F148" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B149" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C149" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D149" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F149" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B150" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D150" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F150" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B151" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D151" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F151" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B152" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C152" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D152" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F152" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B153" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C153" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D153" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F153" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B154" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D154" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F154" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B155" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C155" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D155" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F155" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B156" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C156" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D156" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F156" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B157" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C157" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D157" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F157" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B158" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C158" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D158" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F158" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B159" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C159" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D159" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F159" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
+        <v>487</v>
+      </c>
+      <c r="B160" t="s">
+        <v>488</v>
+      </c>
+      <c r="C160" t="s">
+        <v>489</v>
+      </c>
+      <c r="D160" t="s">
+        <v>444</v>
+      </c>
+      <c r="F160" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>490</v>
+      </c>
+      <c r="B161" t="s">
+        <v>442</v>
+      </c>
+      <c r="C161" t="s">
+        <v>491</v>
+      </c>
+      <c r="D161" t="s">
+        <v>492</v>
+      </c>
+      <c r="F161" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>493</v>
+      </c>
+      <c r="B162" t="s">
+        <v>494</v>
+      </c>
+      <c r="D162" t="s">
+        <v>492</v>
+      </c>
+      <c r="F162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>495</v>
+      </c>
+      <c r="B163" t="s">
+        <v>496</v>
+      </c>
+      <c r="C163" t="s">
+        <v>497</v>
+      </c>
+      <c r="D163" t="s">
+        <v>492</v>
+      </c>
+      <c r="F163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>498</v>
+      </c>
+      <c r="B164" t="s">
         <v>485</v>
       </c>
-      <c r="B160" t="s">
-        <v>486</v>
-      </c>
-      <c r="C160" t="s">
-        <v>487</v>
-      </c>
-      <c r="D160" t="s">
-        <v>442</v>
-      </c>
-      <c r="F160" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
+      <c r="C164" t="s">
+        <v>499</v>
+      </c>
+      <c r="D164" t="s">
+        <v>492</v>
+      </c>
+      <c r="F164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>500</v>
+      </c>
+      <c r="B165" t="s">
         <v>488</v>
       </c>
-      <c r="B161" t="s">
-        <v>440</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="C165" t="s">
         <v>489</v>
       </c>
-      <c r="D161" t="s">
-        <v>490</v>
-      </c>
-      <c r="F161" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" t="s">
-        <v>491</v>
-      </c>
-      <c r="B162" t="s">
+      <c r="D165" t="s">
         <v>492</v>
       </c>
-      <c r="D162" t="s">
-        <v>490</v>
-      </c>
-      <c r="F162" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" t="s">
-        <v>493</v>
-      </c>
-      <c r="B163" t="s">
-        <v>494</v>
-      </c>
-      <c r="C163" t="s">
-        <v>495</v>
-      </c>
-      <c r="D163" t="s">
-        <v>490</v>
-      </c>
-      <c r="F163" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" t="s">
-        <v>496</v>
-      </c>
-      <c r="B164" t="s">
-        <v>483</v>
-      </c>
-      <c r="C164" t="s">
-        <v>497</v>
-      </c>
-      <c r="D164" t="s">
-        <v>490</v>
-      </c>
-      <c r="F164" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
-        <v>498</v>
-      </c>
-      <c r="B165" t="s">
-        <v>486</v>
-      </c>
-      <c r="C165" t="s">
-        <v>487</v>
-      </c>
-      <c r="D165" t="s">
-        <v>490</v>
-      </c>
       <c r="F165" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B166" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C166" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D166" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F166" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B167" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C167" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D167" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F167" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B168" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C168" t="s">
+        <v>509</v>
+      </c>
+      <c r="D168" t="s">
         <v>507</v>
       </c>
-      <c r="D168" t="s">
-        <v>505</v>
-      </c>
       <c r="F168" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B169" t="s">
+        <v>473</v>
+      </c>
+      <c r="C169" t="s">
+        <v>474</v>
+      </c>
+      <c r="D169" t="s">
+        <v>507</v>
+      </c>
+      <c r="F169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>511</v>
+      </c>
+      <c r="B170" t="s">
+        <v>512</v>
+      </c>
+      <c r="C170" t="s">
+        <v>477</v>
+      </c>
+      <c r="D170" t="s">
+        <v>507</v>
+      </c>
+      <c r="F170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>513</v>
+      </c>
+      <c r="B171" t="s">
+        <v>514</v>
+      </c>
+      <c r="C171" t="s">
+        <v>480</v>
+      </c>
+      <c r="D171" t="s">
+        <v>507</v>
+      </c>
+      <c r="F171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>515</v>
+      </c>
+      <c r="B172" t="s">
         <v>471</v>
       </c>
-      <c r="C169" t="s">
-        <v>472</v>
-      </c>
-      <c r="D169" t="s">
-        <v>505</v>
-      </c>
-      <c r="F169" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170" t="s">
-        <v>509</v>
-      </c>
-      <c r="B170" t="s">
-        <v>510</v>
-      </c>
-      <c r="C170" t="s">
-        <v>475</v>
-      </c>
-      <c r="D170" t="s">
-        <v>505</v>
-      </c>
-      <c r="F170" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" t="s">
-        <v>511</v>
-      </c>
-      <c r="B171" t="s">
-        <v>512</v>
-      </c>
-      <c r="C171" t="s">
-        <v>478</v>
-      </c>
-      <c r="D171" t="s">
-        <v>505</v>
-      </c>
-      <c r="F171" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172" t="s">
-        <v>513</v>
-      </c>
-      <c r="B172" t="s">
-        <v>469</v>
-      </c>
       <c r="C172" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D172" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F172" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B173" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C173" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D173" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F173" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B174" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C174" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D174" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F174" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B175" t="s">
+        <v>525</v>
+      </c>
+      <c r="C175" t="s">
+        <v>526</v>
+      </c>
+      <c r="D175" t="s">
         <v>523</v>
       </c>
-      <c r="C175" t="s">
-        <v>524</v>
-      </c>
-      <c r="D175" t="s">
-        <v>521</v>
-      </c>
       <c r="F175" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B176" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C176" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D176" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F176" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B177" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C177" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D177" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F177" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B178" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C178" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D178" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F178" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B179" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C179" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D179" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F179" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B180" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C180" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D180" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F180" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B181" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C181" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D181" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F181" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B182" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C182" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D182" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F182" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B183" t="s">
+        <v>551</v>
+      </c>
+      <c r="C183" t="s">
+        <v>552</v>
+      </c>
+      <c r="D183" t="s">
         <v>549</v>
       </c>
-      <c r="C183" t="s">
-        <v>550</v>
-      </c>
-      <c r="D183" t="s">
-        <v>547</v>
-      </c>
       <c r="F183" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B184" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C184" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D184" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F184" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B185" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C185" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D185" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F185" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B186" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C186" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D186" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F186" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B187" t="s">
+        <v>562</v>
+      </c>
+      <c r="C187" t="s">
+        <v>563</v>
+      </c>
+      <c r="D187" t="s">
         <v>560</v>
       </c>
-      <c r="C187" t="s">
-        <v>561</v>
-      </c>
-      <c r="D187" t="s">
-        <v>558</v>
-      </c>
       <c r="F187" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B188" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C188" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D188" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F188" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B189" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C189" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D189" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F189" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B190" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C190" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D190" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F190" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B191" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D191" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F191" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B192" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C192" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D192" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F192" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B193" t="s">
+        <v>580</v>
+      </c>
+      <c r="C193" t="s">
+        <v>581</v>
+      </c>
+      <c r="D193" t="s">
         <v>578</v>
       </c>
-      <c r="C193" t="s">
-        <v>579</v>
-      </c>
-      <c r="D193" t="s">
-        <v>576</v>
-      </c>
       <c r="F193" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B194" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C194" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D194" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F194" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B195" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C195" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D195" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F195" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B196" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C196" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D196" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F196" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B197" t="s">
+        <v>593</v>
+      </c>
+      <c r="C197" t="s">
+        <v>594</v>
+      </c>
+      <c r="D197" t="s">
         <v>591</v>
       </c>
-      <c r="C197" t="s">
-        <v>592</v>
-      </c>
-      <c r="D197" t="s">
-        <v>589</v>
-      </c>
       <c r="F197" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B198" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C198" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D198" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F198" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B199" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C199" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D199" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F199" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B200" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C200" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D200" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F200" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B201" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C201" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D201" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F201" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B202" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C202" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D202" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F202" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B203" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C203" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D203" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F203" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B204" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C204" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D204" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F204" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B205" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C205" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D205" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F205" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B206" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C206" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D206" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F206" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B207" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D207" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F207" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B208" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C208" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D208" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F208" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B209" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C209" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D209" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F209" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B210" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C210" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D210" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F210" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B211" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C211" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D211" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F211" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B212" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C212" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D212" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F212" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B213" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C213" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D213" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F213" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B214" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C214" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D214" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F214" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B215" t="s">
+        <v>647</v>
+      </c>
+      <c r="C215" t="s">
+        <v>648</v>
+      </c>
+      <c r="D215" t="s">
         <v>645</v>
       </c>
-      <c r="C215" t="s">
-        <v>646</v>
-      </c>
-      <c r="D215" t="s">
-        <v>643</v>
-      </c>
       <c r="F215" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B216" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C216" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D216" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F216" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B217" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D217" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F217" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B218" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C218" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D218" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F218" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B219" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D219" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F219" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B220" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C220" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D220" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F220" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B221" t="s">
+        <v>664</v>
+      </c>
+      <c r="C221" t="s">
+        <v>665</v>
+      </c>
+      <c r="D221" t="s">
         <v>662</v>
       </c>
-      <c r="C221" t="s">
-        <v>663</v>
-      </c>
-      <c r="D221" t="s">
-        <v>660</v>
-      </c>
       <c r="F221" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B222" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D222" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F222" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B223" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C223" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D223" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F223" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B224" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C224" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D224" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F224" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B225" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C225" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D225" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F225" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B226" t="s">
+        <v>679</v>
+      </c>
+      <c r="D226" t="s">
         <v>677</v>
       </c>
-      <c r="D226" t="s">
-        <v>675</v>
-      </c>
       <c r="F226" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B227" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C227" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D227" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F227" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B228" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D228" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F228" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B229" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C229" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D229" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F229" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B230" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C230" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D230" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F230" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B231" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C231" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D231" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F231" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B232" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C232" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D232" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F232" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B233" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D233" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F233" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B234" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D234" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F234" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B235" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C235" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D235" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F235" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B236" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C236" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D236" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F236" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B237" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C237" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D237" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F237" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B238" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D238" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F238" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B239" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C239" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D239" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F239" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B240" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C240" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D240" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F240" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B241" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C241" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D241" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F241" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B242" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C242" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D242" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F242" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B243" t="s">
+        <v>726</v>
+      </c>
+      <c r="C243" t="s">
+        <v>727</v>
+      </c>
+      <c r="D243" t="s">
         <v>724</v>
       </c>
-      <c r="C243" t="s">
-        <v>725</v>
-      </c>
-      <c r="D243" t="s">
-        <v>722</v>
-      </c>
       <c r="F243" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B244" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C244" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D244" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F244" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B245" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C245" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D245" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F245" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B246" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C246" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D246" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F246" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B247" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C247" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D247" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F247" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B248" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C248" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D248" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F248" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B249" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C249" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D249" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F249" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B250" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C250" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D250" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F250" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B251" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C251" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D251" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F251" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B252" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C252" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D252" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F252" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B253" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C253" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D253" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F253" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B254" t="s">
+        <v>761</v>
+      </c>
+      <c r="C254" t="s">
+        <v>762</v>
+      </c>
+      <c r="D254" t="s">
         <v>759</v>
       </c>
-      <c r="C254" t="s">
-        <v>760</v>
-      </c>
-      <c r="D254" t="s">
-        <v>757</v>
-      </c>
       <c r="F254" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B255" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C255" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D255" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F255" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B256" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C256" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D256" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F256" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B257" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C257" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D257" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F257" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B258" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C258" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D258" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F258" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B259" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D259" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="F259" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B260" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C260" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D260" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F260" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B261" t="s">
+        <v>783</v>
+      </c>
+      <c r="C261" t="s">
+        <v>784</v>
+      </c>
+      <c r="D261" t="s">
         <v>781</v>
       </c>
-      <c r="C261" t="s">
-        <v>782</v>
-      </c>
-      <c r="D261" t="s">
-        <v>779</v>
-      </c>
       <c r="F261" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B262" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C262" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D262" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F262" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B263" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C263" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D263" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F263" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B264" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C264" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D264" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F264" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B265" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D265" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F265" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B266" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C266" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D266" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F266" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B267" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D267" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F267" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G267" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B268" t="s">
+        <v>804</v>
+      </c>
+      <c r="C268" t="s">
+        <v>805</v>
+      </c>
+      <c r="D268" t="s">
         <v>801</v>
       </c>
-      <c r="C268" t="s">
+      <c r="F268" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269" t="s">
+        <v>806</v>
+      </c>
+      <c r="B269" t="s">
+        <v>807</v>
+      </c>
+      <c r="C269" t="s">
+        <v>808</v>
+      </c>
+      <c r="D269" t="s">
+        <v>801</v>
+      </c>
+      <c r="F269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270" t="s">
+        <v>809</v>
+      </c>
+      <c r="B270" t="s">
+        <v>810</v>
+      </c>
+      <c r="C270" t="s">
+        <v>811</v>
+      </c>
+      <c r="D270" t="s">
+        <v>801</v>
+      </c>
+      <c r="F270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271" t="s">
+        <v>812</v>
+      </c>
+      <c r="B271" t="s">
+        <v>813</v>
+      </c>
+      <c r="C271" t="s">
+        <v>814</v>
+      </c>
+      <c r="D271" t="s">
+        <v>801</v>
+      </c>
+      <c r="F271" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272" t="s">
+        <v>815</v>
+      </c>
+      <c r="B272" t="s">
+        <v>816</v>
+      </c>
+      <c r="C272" t="s">
+        <v>817</v>
+      </c>
+      <c r="D272" t="s">
+        <v>801</v>
+      </c>
+      <c r="F272" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
+        <v>818</v>
+      </c>
+      <c r="B273" t="s">
+        <v>813</v>
+      </c>
+      <c r="C273" t="s">
+        <v>819</v>
+      </c>
+      <c r="D273" t="s">
+        <v>801</v>
+      </c>
+      <c r="F273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
+        <v>820</v>
+      </c>
+      <c r="B274" t="s">
+        <v>821</v>
+      </c>
+      <c r="C274" t="s">
+        <v>822</v>
+      </c>
+      <c r="D274" t="s">
+        <v>801</v>
+      </c>
+      <c r="F274" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" t="s">
         <v>802</v>
       </c>
-      <c r="D268" t="s">
-        <v>799</v>
-      </c>
-      <c r="F268" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269" t="s">
-        <v>803</v>
-      </c>
-      <c r="B269" t="s">
-        <v>804</v>
-      </c>
-      <c r="C269" t="s">
-        <v>805</v>
-      </c>
-      <c r="D269" t="s">
-        <v>799</v>
-      </c>
-      <c r="F269" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" t="s">
-        <v>806</v>
-      </c>
-      <c r="B270" t="s">
-        <v>807</v>
-      </c>
-      <c r="C270" t="s">
-        <v>808</v>
-      </c>
-      <c r="D270" t="s">
-        <v>799</v>
-      </c>
-      <c r="F270" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271" t="s">
-        <v>809</v>
-      </c>
-      <c r="B271" t="s">
-        <v>810</v>
-      </c>
-      <c r="C271" t="s">
-        <v>811</v>
-      </c>
-      <c r="D271" t="s">
-        <v>799</v>
-      </c>
-      <c r="F271" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="A272" t="s">
-        <v>812</v>
-      </c>
-      <c r="B272" t="s">
-        <v>813</v>
-      </c>
-      <c r="C272" t="s">
-        <v>814</v>
-      </c>
-      <c r="D272" t="s">
-        <v>799</v>
-      </c>
-      <c r="F272" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
-      <c r="A273" t="s">
-        <v>815</v>
-      </c>
-      <c r="B273" t="s">
-        <v>810</v>
-      </c>
-      <c r="C273" t="s">
-        <v>816</v>
-      </c>
-      <c r="D273" t="s">
-        <v>799</v>
-      </c>
-      <c r="F273" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
-      <c r="A274" t="s">
-        <v>817</v>
-      </c>
-      <c r="B274" t="s">
-        <v>818</v>
-      </c>
-      <c r="C274" t="s">
-        <v>819</v>
-      </c>
-      <c r="D274" t="s">
-        <v>799</v>
-      </c>
-      <c r="F274" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B275" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C275" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D275" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F275" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B276" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C276" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D276" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F276" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B277" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C277" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D277" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F277" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B278" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C278" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D278" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F278" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B279" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C279" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D279" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F279" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G279" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B280" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C280" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D280" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F280" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G280" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B281" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C281" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D281" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="F281" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B282" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C282" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D282" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="F282" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G282" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B283" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C283" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D283" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="F283" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B284" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C284" t="s">
+        <v>855</v>
+      </c>
+      <c r="D284" t="s">
         <v>852</v>
       </c>
-      <c r="D284" t="s">
-        <v>849</v>
-      </c>
       <c r="F284" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B285" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C285" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D285" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F285" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B286" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="D286" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F286" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
+        <v>862</v>
+      </c>
+      <c r="B287" t="s">
+        <v>863</v>
+      </c>
+      <c r="C287" t="s">
+        <v>864</v>
+      </c>
+      <c r="D287" t="s">
         <v>859</v>
       </c>
-      <c r="B287" t="s">
-        <v>860</v>
-      </c>
-      <c r="C287" t="s">
-        <v>861</v>
-      </c>
-      <c r="D287" t="s">
-        <v>856</v>
-      </c>
       <c r="F287" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B288" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D288" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F288" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B289" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C289" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D289" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F289" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B290" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C290" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D290" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F290" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B291" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C291" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D291" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F291" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B292" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C292" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D292" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="F292" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B293" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C293" t="s">
+        <v>882</v>
+      </c>
+      <c r="D293" t="s">
         <v>879</v>
       </c>
-      <c r="D293" t="s">
-        <v>876</v>
-      </c>
       <c r="F293" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B294" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C294" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="D294" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="F294" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B295" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C295" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D295" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="F295" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B296" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C296" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D296" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="F296" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B297" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C297" t="s">
+        <v>896</v>
+      </c>
+      <c r="D297" t="s">
         <v>893</v>
       </c>
-      <c r="D297" t="s">
-        <v>890</v>
-      </c>
       <c r="F297" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B298" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D298" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F298" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B299" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C299" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D299" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="F299" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B300" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="D300" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="F300" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
+        <v>906</v>
+      </c>
+      <c r="B301" t="s">
+        <v>907</v>
+      </c>
+      <c r="C301" t="s">
+        <v>908</v>
+      </c>
+      <c r="D301" t="s">
         <v>903</v>
       </c>
-      <c r="B301" t="s">
-        <v>904</v>
-      </c>
-      <c r="C301" t="s">
-        <v>905</v>
-      </c>
-      <c r="D301" t="s">
-        <v>900</v>
-      </c>
       <c r="F301" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B302" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C302" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D302" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F302" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B303" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C303" t="s">
+        <v>915</v>
+      </c>
+      <c r="D303" t="s">
         <v>912</v>
       </c>
-      <c r="D303" t="s">
-        <v>909</v>
-      </c>
       <c r="F303" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B304" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C304" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D304" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F304" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B305" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C305" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D305" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F305" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B306" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C306" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D306" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F306" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B307" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C307" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="D307" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F307" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B308" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C308" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D308" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F308" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B309" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C309" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D309" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F309" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B310" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C310" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="D310" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="F310" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B311" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C311" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D311" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="F311" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G311" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B312" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C312" t="s">
+        <v>943</v>
+      </c>
+      <c r="D312" t="s">
         <v>940</v>
       </c>
-      <c r="D312" t="s">
-        <v>937</v>
-      </c>
       <c r="F312" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="985">
   <si>
     <t>code</t>
   </si>
@@ -238,6 +238,15 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>12196</t>
+  </si>
+  <si>
+    <t>Health statistics and data</t>
+  </si>
+  <si>
+    <t>Collection, production, management and dissemination of statistics and data related to health. Includes health surveys, establishment of health databases, data collection on epidemics, etc.</t>
+  </si>
+  <si>
     <t>12220</t>
   </si>
   <si>
@@ -376,7 +385,7 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
-    <t>Population/development policies; census work, vital registration; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees.)</t>
+    <t>Population/development policies; demographic research/analysis; reproductive health research; unspecified population activities. (Use purpose code 15190 for data on migration and refugees. Use code 13096 for census work, vital registration and migration data collection.)</t>
   </si>
   <si>
     <t>130</t>
@@ -418,6 +427,15 @@
     <t>Education and training of health staff for population and reproductive health care services.</t>
   </si>
   <si>
+    <t>13096</t>
+  </si>
+  <si>
+    <t>Population statistics and data</t>
+  </si>
+  <si>
+    <t>Collection, production, management and dissemination of statistics and data related to Population and Reproductive Health. Includes census work, vital registration, migration data collection, demographic data, etc.</t>
+  </si>
+  <si>
     <t>14010</t>
   </si>
   <si>
@@ -703,7 +721,7 @@
     <t>Legal and judicial development</t>
   </si>
   <si>
-    <t>Support to institutions, systems and procedures of the justice sector, both formal and informal; support to ministries of justice, the interior and home affairs; judges and courts; legal drafting services; bar and lawyers associations; professional legal education; maintenance of law and order and public safety; border management; law enforcement agencies, police, prisons and their supervision; ombudsmen; alternative dispute resolution, arbitration and mediation; legal aid and counsel; traditional, indigenous and paralegal practices that fall outside the formal legal system. Measures that support the improvement of legal frameworks, constitutions, laws and regulations; legislative and constitutional drafting and review; legal reform; integration of formal and informal systems of law. Public legal education; dissemination of information on entitlements and remedies for injustice; awareness campaigns. (Use codes 152xx for activities that are primarily aimed at supporting security system reform or undertaken in connection with post-conflict and peace building activities. Use code 15130 for capacity building in border management related to migration.)</t>
+    <t>Support to institutions, systems and procedures of the justice sector, both formal and informal; support to ministries of justice, the interior and home affairs; judges and courts; legal drafting services; bar and lawyers associations; professional legal education; maintenance of law and order and public safety; border management; law enforcement agencies, police, prisons and their supervision; ombudsmen; alternative dispute resolution, arbitration and mediation; legal aid and counsel; traditional, indigenous and paralegal practices that fall outside the formal legal system. Measures that support the improvement of legal frameworks, constitutions, laws and regulations; legislative and constitutional drafting and review; legal reform; integration of formal and informal systems of law. Public legal education; dissemination of information on entitlements and remedies for injustice; awareness campaigns. (Use codes 152xx for activities that are primarily aimed at supporting security system reform or undertaken in connection with post-conflict and peace building activities. Use code 15190 for capacity building in border management related to migration.)</t>
   </si>
   <si>
     <t>15131</t>
@@ -904,7 +922,10 @@
     <t>15170</t>
   </si>
   <si>
-    <t>Support for institutions and organisations (governmental and non-governmental) working for gender equality and women’s empowerment.</t>
+    <t>Women’s rights organisations and movements, and government institutions</t>
+  </si>
+  <si>
+    <t>Support for feminist, women-led and women’s rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
     <t>15180</t>
@@ -934,6 +955,15 @@
     <t>Assistance to developing countries that facilitates the orderly, safe, regular and responsible migration and mobility of people. This includes:• Capacity building in migration and mobility policy, analysis, planning and management. This includes support to facilitate safe and regular migration and address irregular migration, engagement with diaspora and programmes enhancing the development impact of remittances and/or their use for developmental projects in developing countries.• Measures to improve migrant labour recruitment systems in developing countries.• Capacity building for strategy and policy development as well as legal and judicial development (including border management) in developing countries. This includes support to address and reduce vulnerabilities in migration, and strengthen the transnational response to smuggling of migrants and preventing and combating trafficking in human beings.• Support to effective strategies to ensure international protection and the right to asylum.• Support to effective strategies to ensure access to justice and assistance for displaced persons.• Assistance to migrants for their safe, dignified, informed and voluntary return to their country of origin (covers only returns from another developing country; assistance to forced returns is excluded from ODA).• Assistance to migrants for their sustainable reintegration in their country of origin (use code 93010 for pre-departure assistance provided in donor countries in the context of voluntary returns). Activities that pursue first and foremost providers’ interest are excluded from ODA. Activities addressing the root causes of forced displacement and irregular migration should not be coded here, but under their relevant sector of intervention. In addition, use code 15136 for support to countries' authorities for immigration affairs and services (optional), code 24050 for programmes aiming at reducing the sending costs of remittances, code 72010 for humanitarian aspects of assistance to refugees and internally displaced persons (IDPs) such as delivery of emergency services and humanitarian protection. Use code 93010 when expenditure is for the temporary sustenance of refugees in the donor country, including for their voluntary return and for their reintegration when support is provided in a donor country in connection with the return from that donor country (i.e. pre-departure assistance), or voluntary resettlement in a third developed country.</t>
   </si>
   <si>
+    <t>15196</t>
+  </si>
+  <si>
+    <t>Government and civil society statistics and data</t>
+  </si>
+  <si>
+    <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
+  </si>
+  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1099,7 +1129,7 @@
     <t>Statistical capacity building</t>
   </si>
   <si>
-    <t>Both in national statistical offices and any other government ministries.</t>
+    <t>All statistical activities, such as data collection, processing, dissemination and analysis; support to development and management of official statistics including demographic, social, economic, environmental and multi-sectoral statistics; statistical quality frameworks; development of human and technological resources for statistics, investments in data innovation. Activities related to data and statistics in the sectors 120, 130 or 150 should preferably be coded under the voluntary purpose codes 12196, 13096 and 15196. Activities with the sole purpose of monitoring development co-operation activities, including if performed by third parties, should be coded under 91010 (Administrative costs).</t>
   </si>
   <si>
     <t>16063</t>
@@ -1489,7 +1519,7 @@
     <t>23110</t>
   </si>
   <si>
-    <t>Energy sector policy, planning; aid to energy ministries; institution capacity building and advice; unspecified energy activities.</t>
+    <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
     <t>231</t>
@@ -1525,7 +1555,7 @@
     <t>Energy conservation and demand-side efficiency</t>
   </si>
   <si>
-    <t>All projects in support of energy demand reduction, e.g. building and industry upgrades, smart grids, metering and tariffs. Also includes efficient cook-stoves and biogas projects.</t>
+    <t>Support for energy demand reduction, e.g. building and industry upgrades, smart grids, metering and tariffs. For clean cooking appliances use code 32174.</t>
   </si>
   <si>
     <t>23210</t>
@@ -1549,6 +1579,30 @@
     <t>23230</t>
   </si>
   <si>
+    <t>Solar energy for centralised grids</t>
+  </si>
+  <si>
+    <t>Including photo-voltaic cells, concentrated solar power systems connected to the main grid and net-metered decentralised solutions.</t>
+  </si>
+  <si>
+    <t>23231</t>
+  </si>
+  <si>
+    <t>Solar energy for isolated grids and standalone systems</t>
+  </si>
+  <si>
+    <t>Solar power generation for isolated mini-grids, solar home systems (including integrated wiring and related appliances), solar lanterns distribution and commercialisation. This code refers to the power generation component only.</t>
+  </si>
+  <si>
+    <t>23232</t>
+  </si>
+  <si>
+    <t>Solar energy - thermal applications</t>
+  </si>
+  <si>
+    <t>Solar solutions for indoor space and water heating (except for solar cook stoves 32174).</t>
+  </si>
+  <si>
     <t>23240</t>
   </si>
   <si>
@@ -1573,7 +1627,7 @@
     <t>Biofuel-fired power plants</t>
   </si>
   <si>
-    <t>Use of solids and liquids produced from biomass for direct power generation. Also includes biogases from anaerobic fermentation (e.g. landfill gas, sewage sludge gas, fermentation of energy crops and manure) and thermal processes (also known as syngas); waste-fired power plants making use of biodegradable municipal waste (household waste and waste from companies and public services that resembles household waste, collected at installations specifically designed for their disposal with recovery of combustible liquids, gases or heat). See code 23360 for non- renewable waste-fired power plants.</t>
+    <t>Use of solids and liquids produced from biomass for direct power generation. Also includes biogases from anaerobic fermentation (e.g. landfill gas, sewage sludge gas, fermentation of energy crops and manure) and thermal processes (also known as syngas); waste-fired power plants making use of biodegradable municipal waste (household waste and waste from companies and public services that resembles household waste, collected at installations specifically designed for their disposal with recovery of combustible liquids, gases or heat). See code 23360 for non-renewable waste-fired power plants.</t>
   </si>
   <si>
     <t>23310</t>
@@ -1612,7 +1666,7 @@
     <t>Natural gas-fired electric power plants</t>
   </si>
   <si>
-    <t>Electric power plants that are fuelled by natural gas.</t>
+    <t>Electric power plants that are fuelled by natural gas; related feed-in infrastructure (LNG terminals, gasifiers, pipelines to feed the plant).</t>
   </si>
   <si>
     <t>23350</t>
@@ -1648,7 +1702,10 @@
     <t>23510</t>
   </si>
   <si>
-    <t>Nuclear energy electric power plants</t>
+    <t>Nuclear energy electric power plants and nuclear safety</t>
+  </si>
+  <si>
+    <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
     <t>235</t>
@@ -1678,15 +1735,45 @@
     <t>23630</t>
   </si>
   <si>
-    <t>Electric power transmission and distribution</t>
+    <t>Electric power transmission and distribution (centralised grids)</t>
   </si>
   <si>
     <t>Grid distribution from power source to end user; transmission lines. Also includes storage of energy to generate power (e.g. pumped hydro, batteries) and the extension of grid access, often to rural areas.</t>
   </si>
   <si>
+    <t>23631</t>
+  </si>
+  <si>
+    <t>Electric power transmission and distribution (isolated mini-grids)</t>
+  </si>
+  <si>
+    <t>Includes village grids and other electricity distribution technologies to end users that are not connected to the main national grid. Also includes related electricity storage. This code refers to the network infrastructure only regardless of the power generation technologies.</t>
+  </si>
+  <si>
     <t>23640</t>
   </si>
   <si>
+    <t>Retail gas distribution</t>
+  </si>
+  <si>
+    <t>Includes urban infrastructure for the delivery of urban gas and LPG cylinder production, distribution and refill. Excludes gas distribution for purposes of electricity generation (23340) and pipelines (32262).</t>
+  </si>
+  <si>
+    <t>23641</t>
+  </si>
+  <si>
+    <t>Retail distribution of liquid or solid fossil fuels</t>
+  </si>
+  <si>
+    <t>23642</t>
+  </si>
+  <si>
+    <t>Electric mobility infrastructures</t>
+  </si>
+  <si>
+    <t>Includes electricity or hydrogen recharging stations for private and public transport systems and related infrastructure (except for rail transport 21030).</t>
+  </si>
+  <si>
     <t>24010</t>
   </si>
   <si>
@@ -1969,7 +2056,7 @@
     <t>Fuelwood/charcoal</t>
   </si>
   <si>
-    <t>Forestry development whose primary purpose is production of fuelwood and charcoal.</t>
+    <t>Sustainable forestry development whose primary purpose is production of fuelwood and charcoal. Further transformation of biomass in biofuels is coded under 32173.</t>
   </si>
   <si>
     <t>31281</t>
@@ -2122,10 +2209,10 @@
     <t>32167</t>
   </si>
   <si>
-    <t>Energy manufacturing</t>
-  </si>
-  <si>
-    <t>Including gas liquefaction; petroleum refineries.</t>
+    <t>Energy manufacturing (fossil fuels)</t>
+  </si>
+  <si>
+    <t>Including gas liquefaction; petroleum refineries, wholesale distribution of fossil fuels. (Use 23640 for retail distribution of gas and 23641 for retail distribution of liquid or solid fossil fuels.)</t>
   </si>
   <si>
     <t>32168</t>
@@ -2170,6 +2257,24 @@
     <t>Shipbuilding, fishing boats building; railroad equipment; motor vehicles and motor passenger cars; aircraft; navigation/guidance systems.</t>
   </si>
   <si>
+    <t>32173</t>
+  </si>
+  <si>
+    <t>Modern biofuels manufacturing</t>
+  </si>
+  <si>
+    <t>Includes biogas, liquid biofuels and pellets for domestic and non-domestic use. Excludes raw fuelwood and charcoal (31261).</t>
+  </si>
+  <si>
+    <t>32174</t>
+  </si>
+  <si>
+    <t>Clean cooking appliances manufacturing</t>
+  </si>
+  <si>
+    <t>Includes manufacturing and distribution of efficient biomass cooking stoves, gasifiers, liquid biofuels stoves, solar stoves, gas and biogas stoves, electric stoves.</t>
+  </si>
+  <si>
     <t>32182</t>
   </si>
   <si>
@@ -2212,10 +2317,10 @@
     <t>32262</t>
   </si>
   <si>
-    <t>Oil and gas</t>
-  </si>
-  <si>
-    <t>Petroleum, natural gas, condensates, liquefied petroleum gas (LPG), liquefied natural gas (LNG); including drilling and production, and oil and gas pipelines.</t>
+    <t>Oil and gas (upstream)</t>
+  </si>
+  <si>
+    <t>Petroleum, natural gas, condensates, liquefied petroleum gas (LPG), liquefied natural gas (LNG); including drilling and production, oil and gas pipelines.</t>
   </si>
   <si>
     <t>32263</t>
@@ -2650,19 +2755,37 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
-    <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, and other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
+    <t>Shelter, water, sanitation, education, health services including supply of medicines and malnutrition management, including medical nutrition management; supply of other nonfood relief items (including cash and voucher delivery modalities) for the benefit of crisisaffected people, including refugees and internally displaced people in developing countries, Includes assistance delivered by or coordinated by international civil protection units in the immediate aftermath of a disaster (in-kind assistance, deployment of specially-equipped teams, logistics and transportation, or assessment and coordination by experts sent to the field). Also includes measures to promote and protect the safety, well-being, dignity and integrity of crisis-affected people including refugees and internally displaced persons in developing countries. (Activities designed to protect the security of persons or properties through the use or display of force are not reportable as ODA.)</t>
   </si>
   <si>
     <t>720</t>
   </si>
   <si>
+    <t>72011</t>
+  </si>
+  <si>
+    <t>Basic Health Care Services in Emergencies</t>
+  </si>
+  <si>
+    <t>Provision of health services (basic health services, mental health, sexual and reproductive health), medical nutritional intervention (therapeutic feeding and medical interventions for treating malnutrition) and supply of medicines for the benefit of affected people. Excludes supplemental feeding (72040).</t>
+  </si>
+  <si>
+    <t>72012</t>
+  </si>
+  <si>
+    <t>Education in emergencies</t>
+  </si>
+  <si>
+    <t>Support for education facilities (including restoring pre-existing essential infrastructure and school facilities), teaching, training and learning materials (including digital technologies, as appropriate) and immediate access to quality basic and primary education (including formal and non-formal education), and secondary education (including vocational training and secondary level technical education) in emergencies for the benefit of affected children and youth, particularly targeting girls and women and refugees, life skills for youth and adults, and vocational training for youth and adults</t>
+  </si>
+  <si>
     <t>72040</t>
   </si>
   <si>
     <t>Emergency food assistance</t>
   </si>
   <si>
-    <t>Provision and distribution of food; cash and vouchers for the purchase of food; non-medical nutritional interventions for the benefit of crisis-affected people, including refugees and internally displaced people in developing countries in emergency situations. Includes logistical costs. Excludes non-emergency food assistance (52010), food security policy and administrative management (43071), household food programmes (43072) and medical nutrition interventions (therapeutic feeding) (72010).</t>
+    <t>Provision and distribution of food; cash and vouchers for the purchase of food; non-medical nutritional interventions for the benefit of crisis-affected people, including refugees and internally displaced people in developing countries in emergency situations. Includes logistical costs. Excludes non-emergency food assistance (52010), food security policy and administrative management (43071), household food programmes (43072) and medical nutrition interventions (therapeutic feeding) (72010 and 72011).</t>
   </si>
   <si>
     <t>72050</t>
@@ -3177,7 +3300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3560,7 +3683,7 @@
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -3568,16 +3691,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
         <v>78</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -3594,7 +3717,7 @@
         <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
@@ -3611,7 +3734,7 @@
         <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -3628,7 +3751,7 @@
         <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -3645,7 +3768,7 @@
         <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -3662,7 +3785,7 @@
         <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -3679,7 +3802,7 @@
         <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -3696,7 +3819,7 @@
         <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -3704,16 +3827,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
         <v>103</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>105</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -3730,7 +3853,7 @@
         <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
         <v>11</v>
@@ -3747,7 +3870,7 @@
         <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -3764,7 +3887,7 @@
         <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -3781,7 +3904,7 @@
         <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -3798,7 +3921,7 @@
         <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -3806,16 +3929,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
         <v>122</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>123</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>124</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -3832,7 +3955,7 @@
         <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -3849,7 +3972,7 @@
         <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -3866,7 +3989,7 @@
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -3883,7 +4006,7 @@
         <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -3891,16 +4014,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" t="s">
         <v>138</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>139</v>
       </c>
-      <c r="C42" t="s">
-        <v>140</v>
-      </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -3908,16 +4031,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
         <v>141</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>142</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>143</v>
-      </c>
-      <c r="D43" t="s">
-        <v>137</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
@@ -3934,7 +4057,7 @@
         <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
@@ -3951,7 +4074,7 @@
         <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -3968,7 +4091,7 @@
         <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F46" t="s">
         <v>11</v>
@@ -3985,7 +4108,7 @@
         <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -4002,7 +4125,7 @@
         <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -4019,7 +4142,7 @@
         <v>161</v>
       </c>
       <c r="D49" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -4036,7 +4159,7 @@
         <v>164</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
@@ -4053,7 +4176,7 @@
         <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
@@ -4070,47 +4193,41 @@
         <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
-      </c>
-      <c r="G52" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" t="s">
         <v>172</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>173</v>
       </c>
-      <c r="C53" t="s">
-        <v>174</v>
-      </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
-      </c>
-      <c r="G53" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54" t="s">
         <v>175</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>176</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>177</v>
-      </c>
-      <c r="D54" t="s">
-        <v>171</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
@@ -4130,10 +4247,13 @@
         <v>180</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
+      </c>
+      <c r="G55" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -4147,7 +4267,7 @@
         <v>183</v>
       </c>
       <c r="D56" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F56" t="s">
         <v>11</v>
@@ -4167,7 +4287,7 @@
         <v>186</v>
       </c>
       <c r="D57" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -4184,10 +4304,13 @@
         <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
+      </c>
+      <c r="G58" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4201,7 +4324,7 @@
         <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -4218,7 +4341,7 @@
         <v>195</v>
       </c>
       <c r="D60" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -4235,24 +4358,24 @@
         <v>198</v>
       </c>
       <c r="D61" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F61" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" t="s">
         <v>200</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>201</v>
       </c>
-      <c r="C62" t="s">
-        <v>202</v>
-      </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -4260,19 +4383,19 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" t="s">
         <v>203</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>204</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" t="s">
         <v>205</v>
-      </c>
-      <c r="D63" t="s">
-        <v>171</v>
-      </c>
-      <c r="F63" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4286,7 +4409,7 @@
         <v>208</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
@@ -4303,7 +4426,7 @@
         <v>211</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -4320,7 +4443,7 @@
         <v>214</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F66" t="s">
         <v>11</v>
@@ -4337,7 +4460,7 @@
         <v>217</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -4354,7 +4477,7 @@
         <v>220</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -4371,7 +4494,7 @@
         <v>223</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F69" t="s">
         <v>11</v>
@@ -4388,7 +4511,7 @@
         <v>226</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F70" t="s">
         <v>11</v>
@@ -4405,13 +4528,10 @@
         <v>229</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
-      </c>
-      <c r="G71" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -4425,7 +4545,7 @@
         <v>232</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -4442,10 +4562,13 @@
         <v>235</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
+      </c>
+      <c r="G73" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4459,7 +4582,7 @@
         <v>238</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -4476,7 +4599,7 @@
         <v>241</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -4493,7 +4616,7 @@
         <v>244</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
@@ -4510,7 +4633,7 @@
         <v>247</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
@@ -4523,8 +4646,11 @@
       <c r="B78" t="s">
         <v>249</v>
       </c>
+      <c r="C78" t="s">
+        <v>250</v>
+      </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
@@ -4532,33 +4658,30 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C79" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D79" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F79" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
-      </c>
-      <c r="C80" t="s">
         <v>255</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -4575,10 +4698,10 @@
         <v>258</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -4592,7 +4715,7 @@
         <v>261</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
@@ -4609,7 +4732,7 @@
         <v>264</v>
       </c>
       <c r="D83" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F83" t="s">
         <v>11</v>
@@ -4626,7 +4749,7 @@
         <v>267</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
@@ -4643,7 +4766,7 @@
         <v>270</v>
       </c>
       <c r="D85" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F85" t="s">
         <v>11</v>
@@ -4660,7 +4783,7 @@
         <v>273</v>
       </c>
       <c r="D86" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F86" t="s">
         <v>11</v>
@@ -4677,7 +4800,7 @@
         <v>276</v>
       </c>
       <c r="D87" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F87" t="s">
         <v>11</v>
@@ -4690,8 +4813,11 @@
       <c r="B88" t="s">
         <v>278</v>
       </c>
+      <c r="C88" t="s">
+        <v>279</v>
+      </c>
       <c r="D88" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
@@ -4699,16 +4825,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F89" t="s">
         <v>11</v>
@@ -4716,16 +4842,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B90" t="s">
-        <v>283</v>
-      </c>
-      <c r="C90" t="s">
         <v>284</v>
       </c>
       <c r="D90" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F90" t="s">
         <v>11</v>
@@ -4736,67 +4859,67 @@
         <v>285</v>
       </c>
       <c r="B91" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D91" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F91" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B92" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C92" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D92" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F92" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="C93" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D93" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F93" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B94" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C94" t="s">
         <v>294</v>
       </c>
       <c r="D94" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F94" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4804,47 +4927,47 @@
         <v>295</v>
       </c>
       <c r="B95" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D95" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F95" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D96" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F96" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D97" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -4852,16 +4975,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D98" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F98" t="s">
         <v>11</v>
@@ -4869,16 +4992,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B99" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D99" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -4895,7 +5018,7 @@
         <v>312</v>
       </c>
       <c r="D100" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="F100" t="s">
         <v>11</v>
@@ -4912,7 +5035,7 @@
         <v>315</v>
       </c>
       <c r="D101" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -4929,7 +5052,7 @@
         <v>318</v>
       </c>
       <c r="D102" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F102" t="s">
         <v>11</v>
@@ -4937,16 +5060,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
+        <v>320</v>
+      </c>
+      <c r="B103" t="s">
+        <v>321</v>
+      </c>
+      <c r="C103" t="s">
+        <v>322</v>
+      </c>
+      <c r="D103" t="s">
         <v>319</v>
-      </c>
-      <c r="B103" t="s">
-        <v>320</v>
-      </c>
-      <c r="C103" t="s">
-        <v>321</v>
-      </c>
-      <c r="D103" t="s">
-        <v>309</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -4954,16 +5077,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B104" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C104" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D104" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -4971,22 +5094,19 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B105" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C105" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D105" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F105" t="s">
         <v>11</v>
-      </c>
-      <c r="G105" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -5000,7 +5120,7 @@
         <v>331</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -5017,7 +5137,7 @@
         <v>334</v>
       </c>
       <c r="D107" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -5034,24 +5154,27 @@
         <v>337</v>
       </c>
       <c r="D108" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
+      </c>
+      <c r="G108" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" t="s">
+        <v>340</v>
+      </c>
+      <c r="C109" t="s">
+        <v>341</v>
+      </c>
+      <c r="D109" t="s">
         <v>338</v>
-      </c>
-      <c r="B109" t="s">
-        <v>339</v>
-      </c>
-      <c r="C109" t="s">
-        <v>340</v>
-      </c>
-      <c r="D109" t="s">
-        <v>328</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
@@ -5059,16 +5182,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C110" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D110" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -5076,16 +5199,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D111" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -5093,16 +5216,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C112" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D112" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -5110,16 +5233,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D113" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F113" t="s">
         <v>11</v>
@@ -5127,16 +5250,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B114" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C114" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D114" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
@@ -5144,36 +5267,33 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C115" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D115" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F115" t="s">
         <v>11</v>
-      </c>
-      <c r="G115" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B116" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D116" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F116" t="s">
         <v>11</v>
@@ -5181,16 +5301,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B117" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C117" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D117" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -5198,30 +5318,36 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C118" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D118" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F118" t="s">
         <v>11</v>
+      </c>
+      <c r="G118" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B119" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="C119" t="s">
+        <v>371</v>
       </c>
       <c r="D119" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -5229,13 +5355,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B120" t="s">
-        <v>371</v>
+        <v>373</v>
+      </c>
+      <c r="C120" t="s">
+        <v>374</v>
       </c>
       <c r="D120" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F120" t="s">
         <v>11</v>
@@ -5243,16 +5372,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B121" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D121" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F121" t="s">
         <v>11</v>
@@ -5260,16 +5389,13 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s">
-        <v>376</v>
-      </c>
-      <c r="C122" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D122" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -5277,22 +5403,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B123" t="s">
-        <v>379</v>
-      </c>
-      <c r="C123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D123" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="F123" t="s">
         <v>11</v>
-      </c>
-      <c r="G123" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -5306,7 +5426,7 @@
         <v>384</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="F124" t="s">
         <v>11</v>
@@ -5323,7 +5443,7 @@
         <v>387</v>
       </c>
       <c r="D125" t="s">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -5340,44 +5460,44 @@
         <v>390</v>
       </c>
       <c r="D126" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
+      </c>
+      <c r="G126" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
+        <v>392</v>
+      </c>
+      <c r="B127" t="s">
+        <v>393</v>
+      </c>
+      <c r="C127" t="s">
+        <v>394</v>
+      </c>
+      <c r="D127" t="s">
         <v>391</v>
       </c>
-      <c r="B127" t="s">
-        <v>392</v>
-      </c>
-      <c r="C127" t="s">
-        <v>393</v>
-      </c>
-      <c r="D127" t="s">
-        <v>381</v>
-      </c>
       <c r="F127" t="s">
         <v>11</v>
-      </c>
-      <c r="G127" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C128" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D128" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F128" t="s">
         <v>11</v>
@@ -5385,16 +5505,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B129" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C129" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D129" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
@@ -5402,33 +5522,36 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B130" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
+      </c>
+      <c r="G130" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C131" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -5436,16 +5559,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B132" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C132" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -5453,16 +5576,16 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C133" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F133" t="s">
         <v>11</v>
@@ -5470,16 +5593,16 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C134" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -5487,16 +5610,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C135" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -5504,13 +5627,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B136" t="s">
-        <v>419</v>
+        <v>420</v>
+      </c>
+      <c r="C136" t="s">
+        <v>421</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -5518,33 +5644,33 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C137" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D137" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="F137" t="s">
         <v>11</v>
-      </c>
-      <c r="G137" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B138" t="s">
-        <v>425</v>
+        <v>426</v>
+      </c>
+      <c r="C138" t="s">
+        <v>427</v>
       </c>
       <c r="D138" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="F138" t="s">
         <v>11</v>
@@ -5552,16 +5678,13 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B139" t="s">
-        <v>427</v>
-      </c>
-      <c r="C139" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D139" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="F139" t="s">
         <v>11</v>
@@ -5569,33 +5692,33 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B140" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C140" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D140" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F140" t="s">
         <v>11</v>
+      </c>
+      <c r="G140" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B141" t="s">
+        <v>435</v>
+      </c>
+      <c r="D141" t="s">
         <v>433</v>
-      </c>
-      <c r="C141" t="s">
-        <v>434</v>
-      </c>
-      <c r="D141" t="s">
-        <v>423</v>
       </c>
       <c r="F141" t="s">
         <v>11</v>
@@ -5603,16 +5726,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B142" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C142" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D142" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F142" t="s">
         <v>11</v>
@@ -5620,16 +5743,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B143" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C143" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D143" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F143" t="s">
         <v>11</v>
@@ -5637,19 +5760,19 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B144" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C144" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D144" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="F144" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5663,10 +5786,10 @@
         <v>447</v>
       </c>
       <c r="D145" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="F145" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5680,10 +5803,10 @@
         <v>450</v>
       </c>
       <c r="D146" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="F146" t="s">
-        <v>199</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5697,304 +5820,304 @@
         <v>453</v>
       </c>
       <c r="D147" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F147" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
+        <v>455</v>
+      </c>
+      <c r="B148" t="s">
+        <v>456</v>
+      </c>
+      <c r="C148" t="s">
+        <v>457</v>
+      </c>
+      <c r="D148" t="s">
         <v>454</v>
       </c>
-      <c r="B148" t="s">
-        <v>455</v>
-      </c>
-      <c r="C148" t="s">
-        <v>456</v>
-      </c>
-      <c r="D148" t="s">
-        <v>444</v>
-      </c>
       <c r="F148" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B149" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C149" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D149" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F149" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B150" t="s">
-        <v>461</v>
+        <v>462</v>
+      </c>
+      <c r="C150" t="s">
+        <v>463</v>
       </c>
       <c r="D150" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F150" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B151" t="s">
-        <v>463</v>
+        <v>465</v>
+      </c>
+      <c r="C151" t="s">
+        <v>466</v>
       </c>
       <c r="D151" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F151" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B152" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C152" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D152" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F152" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B153" t="s">
-        <v>468</v>
-      </c>
-      <c r="C153" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D153" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F153" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B154" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D154" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F154" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B155" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C155" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D155" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F155" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B156" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C156" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D156" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F156" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B157" t="s">
-        <v>479</v>
-      </c>
-      <c r="C157" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D157" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F157" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B158" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C158" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D158" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F158" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B159" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C159" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D159" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F159" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B160" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C160" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D160" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F160" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B161" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="C161" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D161" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="F161" t="s">
-        <v>11</v>
-      </c>
-      <c r="G161" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B162" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="C162" t="s">
+        <v>496</v>
       </c>
       <c r="D162" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="F162" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B163" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C163" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D163" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="F163" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B164" t="s">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="C164" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D164" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="F164" t="s">
         <v>11</v>
+      </c>
+      <c r="G164" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B165" t="s">
-        <v>488</v>
-      </c>
-      <c r="C165" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D165" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="F165" t="s">
         <v>11</v>
@@ -6002,16 +6125,16 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B166" t="s">
+        <v>506</v>
+      </c>
+      <c r="C166" t="s">
+        <v>507</v>
+      </c>
+      <c r="D166" t="s">
         <v>502</v>
-      </c>
-      <c r="C166" t="s">
-        <v>503</v>
-      </c>
-      <c r="D166" t="s">
-        <v>492</v>
       </c>
       <c r="F166" t="s">
         <v>11</v>
@@ -6019,16 +6142,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B167" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C167" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="D167" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F167" t="s">
         <v>11</v>
@@ -6036,16 +6159,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B168" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="C168" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D168" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F168" t="s">
         <v>11</v>
@@ -6053,16 +6176,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B169" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="C169" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="D169" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F169" t="s">
         <v>11</v>
@@ -6070,16 +6193,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B170" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C170" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="D170" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="F170" t="s">
         <v>11</v>
@@ -6087,16 +6210,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B171" t="s">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="C171" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="D171" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="F171" t="s">
         <v>11</v>
@@ -6104,16 +6227,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B172" t="s">
-        <v>471</v>
+        <v>521</v>
       </c>
       <c r="C172" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D172" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="F172" t="s">
         <v>11</v>
@@ -6121,16 +6244,16 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
+        <v>523</v>
+      </c>
+      <c r="B173" t="s">
+        <v>524</v>
+      </c>
+      <c r="C173" t="s">
+        <v>525</v>
+      </c>
+      <c r="D173" t="s">
         <v>517</v>
-      </c>
-      <c r="B173" t="s">
-        <v>518</v>
-      </c>
-      <c r="C173" t="s">
-        <v>519</v>
-      </c>
-      <c r="D173" t="s">
-        <v>507</v>
       </c>
       <c r="F173" t="s">
         <v>11</v>
@@ -6138,16 +6261,16 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B174" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C174" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D174" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F174" t="s">
         <v>11</v>
@@ -6155,16 +6278,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B175" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C175" t="s">
-        <v>526</v>
+        <v>487</v>
       </c>
       <c r="D175" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F175" t="s">
         <v>11</v>
@@ -6172,16 +6295,16 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B176" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C176" t="s">
-        <v>529</v>
+        <v>490</v>
       </c>
       <c r="D176" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F176" t="s">
         <v>11</v>
@@ -6189,16 +6312,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B177" t="s">
-        <v>531</v>
+        <v>481</v>
       </c>
       <c r="C177" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D177" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F177" t="s">
         <v>11</v>
@@ -6206,16 +6329,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B178" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C178" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D178" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F178" t="s">
         <v>11</v>
@@ -6223,16 +6346,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B179" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C179" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D179" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="F179" t="s">
         <v>11</v>
@@ -6240,16 +6363,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B180" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C180" t="s">
+        <v>544</v>
+      </c>
+      <c r="D180" t="s">
         <v>541</v>
-      </c>
-      <c r="D180" t="s">
-        <v>542</v>
       </c>
       <c r="F180" t="s">
         <v>11</v>
@@ -6257,16 +6380,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B181" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C181" t="s">
-        <v>466</v>
+        <v>547</v>
       </c>
       <c r="D181" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F181" t="s">
         <v>11</v>
@@ -6274,16 +6397,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B182" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C182" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D182" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="F182" t="s">
         <v>11</v>
@@ -6291,16 +6414,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B183" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C183" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D183" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="F183" t="s">
         <v>11</v>
@@ -6308,16 +6431,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B184" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C184" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D184" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="F184" t="s">
         <v>11</v>
@@ -6325,16 +6448,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B185" t="s">
-        <v>455</v>
+        <v>558</v>
       </c>
       <c r="C185" t="s">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="D185" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="F185" t="s">
         <v>11</v>
@@ -6342,16 +6465,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B186" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C186" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D186" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F186" t="s">
         <v>11</v>
@@ -6359,16 +6482,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B187" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C187" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D187" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F187" t="s">
         <v>11</v>
@@ -6376,16 +6499,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B188" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C188" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D188" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F188" t="s">
         <v>11</v>
@@ -6393,16 +6516,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B189" t="s">
+        <v>573</v>
+      </c>
+      <c r="C189" t="s">
+        <v>574</v>
+      </c>
+      <c r="D189" t="s">
         <v>568</v>
-      </c>
-      <c r="C189" t="s">
-        <v>569</v>
-      </c>
-      <c r="D189" t="s">
-        <v>560</v>
       </c>
       <c r="F189" t="s">
         <v>11</v>
@@ -6410,16 +6533,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B190" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C190" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D190" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F190" t="s">
         <v>11</v>
@@ -6427,13 +6550,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B191" t="s">
-        <v>574</v>
+        <v>579</v>
+      </c>
+      <c r="C191" t="s">
+        <v>580</v>
       </c>
       <c r="D191" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F191" t="s">
         <v>11</v>
@@ -6441,16 +6567,13 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B192" t="s">
-        <v>576</v>
-      </c>
-      <c r="C192" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D192" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="F192" t="s">
         <v>11</v>
@@ -6458,16 +6581,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B193" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C193" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D193" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="F193" t="s">
         <v>11</v>
@@ -6475,16 +6598,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B194" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C194" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D194" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="F194" t="s">
         <v>11</v>
@@ -6492,16 +6615,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B195" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C195" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D195" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="F195" t="s">
         <v>11</v>
@@ -6509,16 +6632,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B196" t="s">
+        <v>594</v>
+      </c>
+      <c r="C196" t="s">
+        <v>595</v>
+      </c>
+      <c r="D196" t="s">
         <v>589</v>
-      </c>
-      <c r="C196" t="s">
-        <v>590</v>
-      </c>
-      <c r="D196" t="s">
-        <v>591</v>
       </c>
       <c r="F196" t="s">
         <v>11</v>
@@ -6526,16 +6649,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B197" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C197" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D197" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F197" t="s">
         <v>11</v>
@@ -6543,16 +6666,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B198" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C198" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D198" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F198" t="s">
         <v>11</v>
@@ -6560,16 +6683,13 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B199" t="s">
-        <v>599</v>
-      </c>
-      <c r="C199" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D199" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F199" t="s">
         <v>11</v>
@@ -6577,16 +6697,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B200" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C200" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D200" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="F200" t="s">
         <v>11</v>
@@ -6594,16 +6714,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B201" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C201" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D201" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="F201" t="s">
         <v>11</v>
@@ -6611,16 +6731,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
+        <v>611</v>
+      </c>
+      <c r="B202" t="s">
+        <v>612</v>
+      </c>
+      <c r="C202" t="s">
+        <v>613</v>
+      </c>
+      <c r="D202" t="s">
         <v>607</v>
-      </c>
-      <c r="B202" t="s">
-        <v>608</v>
-      </c>
-      <c r="C202" t="s">
-        <v>609</v>
-      </c>
-      <c r="D202" t="s">
-        <v>591</v>
       </c>
       <c r="F202" t="s">
         <v>11</v>
@@ -6628,16 +6748,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B203" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C203" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D203" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="F203" t="s">
         <v>11</v>
@@ -6645,16 +6765,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B204" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C204" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D204" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F204" t="s">
         <v>11</v>
@@ -6662,16 +6782,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B205" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C205" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="D205" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F205" t="s">
         <v>11</v>
@@ -6679,16 +6799,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B206" t="s">
+        <v>625</v>
+      </c>
+      <c r="C206" t="s">
+        <v>626</v>
+      </c>
+      <c r="D206" t="s">
         <v>620</v>
-      </c>
-      <c r="C206" t="s">
-        <v>621</v>
-      </c>
-      <c r="D206" t="s">
-        <v>591</v>
       </c>
       <c r="F206" t="s">
         <v>11</v>
@@ -6696,13 +6816,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B207" t="s">
-        <v>623</v>
+        <v>628</v>
+      </c>
+      <c r="C207" t="s">
+        <v>629</v>
       </c>
       <c r="D207" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F207" t="s">
         <v>11</v>
@@ -6710,16 +6833,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B208" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C208" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D208" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F208" t="s">
         <v>11</v>
@@ -6727,16 +6850,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B209" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C209" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D209" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F209" t="s">
         <v>11</v>
@@ -6744,16 +6867,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B210" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C210" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D210" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F210" t="s">
         <v>11</v>
@@ -6761,16 +6884,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B211" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C211" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D211" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F211" t="s">
         <v>11</v>
@@ -6778,16 +6901,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B212" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C212" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D212" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F212" t="s">
         <v>11</v>
@@ -6795,16 +6918,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B213" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C213" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D213" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F213" t="s">
         <v>11</v>
@@ -6812,16 +6935,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B214" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C214" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D214" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F214" t="s">
         <v>11</v>
@@ -6829,16 +6952,13 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B215" t="s">
-        <v>647</v>
-      </c>
-      <c r="C215" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D215" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F215" t="s">
         <v>11</v>
@@ -6846,16 +6966,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B216" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C216" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D216" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F216" t="s">
         <v>11</v>
@@ -6863,13 +6983,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B217" t="s">
-        <v>653</v>
+        <v>657</v>
+      </c>
+      <c r="C217" t="s">
+        <v>658</v>
       </c>
       <c r="D217" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F217" t="s">
         <v>11</v>
@@ -6877,16 +7000,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B218" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C218" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D218" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F218" t="s">
         <v>11</v>
@@ -6894,13 +7017,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="B219" t="s">
-        <v>658</v>
+        <v>663</v>
+      </c>
+      <c r="C219" t="s">
+        <v>664</v>
       </c>
       <c r="D219" t="s">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="F219" t="s">
         <v>11</v>
@@ -6908,16 +7034,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B220" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C220" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D220" t="s">
-        <v>662</v>
+        <v>620</v>
       </c>
       <c r="F220" t="s">
         <v>11</v>
@@ -6925,16 +7051,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B221" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C221" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="D221" t="s">
-        <v>662</v>
+        <v>620</v>
       </c>
       <c r="F221" t="s">
         <v>11</v>
@@ -6942,13 +7068,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="B222" t="s">
-        <v>667</v>
+        <v>672</v>
+      </c>
+      <c r="C222" t="s">
+        <v>673</v>
       </c>
       <c r="D222" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="F222" t="s">
         <v>11</v>
@@ -6956,16 +7085,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="B223" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C223" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="D223" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="F223" t="s">
         <v>11</v>
@@ -6973,16 +7102,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="B224" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="C224" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D224" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="F224" t="s">
         <v>11</v>
@@ -6990,16 +7119,13 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
+        <v>681</v>
+      </c>
+      <c r="B225" t="s">
+        <v>682</v>
+      </c>
+      <c r="D225" t="s">
         <v>674</v>
-      </c>
-      <c r="B225" t="s">
-        <v>675</v>
-      </c>
-      <c r="C225" t="s">
-        <v>676</v>
-      </c>
-      <c r="D225" t="s">
-        <v>677</v>
       </c>
       <c r="F225" t="s">
         <v>11</v>
@@ -7007,13 +7133,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B226" t="s">
-        <v>679</v>
+        <v>684</v>
+      </c>
+      <c r="C226" t="s">
+        <v>685</v>
       </c>
       <c r="D226" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F226" t="s">
         <v>11</v>
@@ -7021,16 +7150,13 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B227" t="s">
-        <v>681</v>
-      </c>
-      <c r="C227" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="D227" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F227" t="s">
         <v>11</v>
@@ -7038,13 +7164,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B228" t="s">
-        <v>684</v>
+        <v>689</v>
+      </c>
+      <c r="C228" t="s">
+        <v>690</v>
       </c>
       <c r="D228" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="F228" t="s">
         <v>11</v>
@@ -7052,16 +7181,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B229" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="C229" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="D229" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="F229" t="s">
         <v>11</v>
@@ -7069,16 +7198,13 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="B230" t="s">
-        <v>689</v>
-      </c>
-      <c r="C230" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D230" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="F230" t="s">
         <v>11</v>
@@ -7086,16 +7212,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
+        <v>697</v>
+      </c>
+      <c r="B231" t="s">
+        <v>698</v>
+      </c>
+      <c r="C231" t="s">
+        <v>699</v>
+      </c>
+      <c r="D231" t="s">
         <v>691</v>
-      </c>
-      <c r="B231" t="s">
-        <v>692</v>
-      </c>
-      <c r="C231" t="s">
-        <v>693</v>
-      </c>
-      <c r="D231" t="s">
-        <v>677</v>
       </c>
       <c r="F231" t="s">
         <v>11</v>
@@ -7103,16 +7229,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="B232" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C232" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D232" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="F232" t="s">
         <v>11</v>
@@ -7120,13 +7246,16 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B233" t="s">
-        <v>698</v>
+        <v>704</v>
+      </c>
+      <c r="C233" t="s">
+        <v>705</v>
       </c>
       <c r="D233" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F233" t="s">
         <v>11</v>
@@ -7134,13 +7263,13 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="B234" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D234" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F234" t="s">
         <v>11</v>
@@ -7148,16 +7277,16 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B235" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C235" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D235" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F235" t="s">
         <v>11</v>
@@ -7165,16 +7294,13 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="B236" t="s">
-        <v>705</v>
-      </c>
-      <c r="C236" t="s">
+        <v>713</v>
+      </c>
+      <c r="D236" t="s">
         <v>706</v>
-      </c>
-      <c r="D236" t="s">
-        <v>677</v>
       </c>
       <c r="F236" t="s">
         <v>11</v>
@@ -7182,16 +7308,16 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B237" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="C237" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="D237" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F237" t="s">
         <v>11</v>
@@ -7199,13 +7325,16 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="B238" t="s">
-        <v>711</v>
+        <v>718</v>
+      </c>
+      <c r="C238" t="s">
+        <v>719</v>
       </c>
       <c r="D238" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F238" t="s">
         <v>11</v>
@@ -7213,16 +7342,16 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="B239" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C239" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="D239" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F239" t="s">
         <v>11</v>
@@ -7230,16 +7359,16 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="B240" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="C240" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D240" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F240" t="s">
         <v>11</v>
@@ -7247,16 +7376,13 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="B241" t="s">
-        <v>719</v>
-      </c>
-      <c r="C241" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="D241" t="s">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="F241" t="s">
         <v>11</v>
@@ -7264,16 +7390,13 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B242" t="s">
-        <v>722</v>
-      </c>
-      <c r="C242" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="D242" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F242" t="s">
         <v>11</v>
@@ -7281,16 +7404,16 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B243" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="C243" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D243" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F243" t="s">
         <v>11</v>
@@ -7298,16 +7421,16 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B244" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C244" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D244" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F244" t="s">
         <v>11</v>
@@ -7315,16 +7438,16 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B245" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C245" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="D245" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F245" t="s">
         <v>11</v>
@@ -7332,16 +7455,13 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B246" t="s">
-        <v>735</v>
-      </c>
-      <c r="C246" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D246" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F246" t="s">
         <v>11</v>
@@ -7349,16 +7469,16 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B247" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C247" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D247" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F247" t="s">
         <v>11</v>
@@ -7366,16 +7486,16 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B248" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C248" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D248" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F248" t="s">
         <v>11</v>
@@ -7383,16 +7503,16 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B249" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C249" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D249" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F249" t="s">
         <v>11</v>
@@ -7400,16 +7520,16 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B250" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C250" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D250" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F250" t="s">
         <v>11</v>
@@ -7417,16 +7537,16 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B251" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C251" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D251" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F251" t="s">
         <v>11</v>
@@ -7434,16 +7554,16 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B252" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C252" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D252" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="F252" t="s">
         <v>11</v>
@@ -7451,13 +7571,13 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B253" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C253" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D253" t="s">
         <v>759</v>
@@ -7468,13 +7588,13 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B254" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C254" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D254" t="s">
         <v>759</v>
@@ -7485,13 +7605,13 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B255" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C255" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D255" t="s">
         <v>759</v>
@@ -7502,13 +7622,13 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B256" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C256" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="D256" t="s">
         <v>759</v>
@@ -7517,15 +7637,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B257" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C257" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D257" t="s">
         <v>759</v>
@@ -7534,15 +7654,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B258" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C258" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D258" t="s">
         <v>759</v>
@@ -7551,239 +7671,236 @@
         <v>11</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B259" t="s">
-        <v>776</v>
+        <v>779</v>
+      </c>
+      <c r="C259" t="s">
+        <v>780</v>
       </c>
       <c r="D259" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="F259" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B260" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C260" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D260" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="F260" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B261" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C261" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D261" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="F261" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B262" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C262" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D262" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="F262" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B263" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C263" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D263" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="F263" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B264" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C264" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D264" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="F264" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
+        <v>798</v>
+      </c>
+      <c r="B265" t="s">
+        <v>799</v>
+      </c>
+      <c r="C265" t="s">
+        <v>800</v>
+      </c>
+      <c r="D265" t="s">
         <v>794</v>
       </c>
-      <c r="B265" t="s">
-        <v>795</v>
-      </c>
-      <c r="D265" t="s">
-        <v>781</v>
-      </c>
       <c r="F265" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B266" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C266" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="D266" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="F266" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B267" t="s">
-        <v>800</v>
+        <v>805</v>
+      </c>
+      <c r="C267" t="s">
+        <v>806</v>
       </c>
       <c r="D267" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="F267" t="s">
         <v>11</v>
       </c>
-      <c r="G267" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B268" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C268" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D268" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="F268" t="s">
         <v>11</v>
       </c>
-      <c r="G268" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B269" t="s">
-        <v>807</v>
-      </c>
-      <c r="C269" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D269" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="F269" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B270" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C270" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D270" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F270" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="B271" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C271" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D271" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F271" t="s">
         <v>11</v>
       </c>
-      <c r="G271" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="B272" t="s">
+        <v>821</v>
+      </c>
+      <c r="C272" t="s">
+        <v>822</v>
+      </c>
+      <c r="D272" t="s">
         <v>816</v>
-      </c>
-      <c r="C272" t="s">
-        <v>817</v>
-      </c>
-      <c r="D272" t="s">
-        <v>801</v>
       </c>
       <c r="F272" t="s">
         <v>11</v>
@@ -7791,16 +7908,16 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="B273" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="C273" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="D273" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F273" t="s">
         <v>11</v>
@@ -7808,36 +7925,30 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="B274" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C274" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="D274" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F274" t="s">
-        <v>11</v>
-      </c>
-      <c r="G274" t="s">
-        <v>802</v>
+        <v>205</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="B275" t="s">
-        <v>824</v>
-      </c>
-      <c r="C275" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="D275" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F275" t="s">
         <v>11</v>
@@ -7845,16 +7956,16 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="B276" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C276" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="D276" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="F276" t="s">
         <v>11</v>
@@ -7862,127 +7973,124 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="B277" t="s">
-        <v>830</v>
-      </c>
-      <c r="C277" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D277" t="s">
-        <v>801</v>
+        <v>836</v>
       </c>
       <c r="F277" t="s">
         <v>11</v>
+      </c>
+      <c r="G277" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="B278" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C278" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D278" t="s">
-        <v>801</v>
+        <v>836</v>
       </c>
       <c r="F278" t="s">
         <v>11</v>
+      </c>
+      <c r="G278" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="B279" t="s">
+        <v>842</v>
+      </c>
+      <c r="C279" t="s">
+        <v>843</v>
+      </c>
+      <c r="D279" t="s">
         <v>836</v>
       </c>
-      <c r="C279" t="s">
-        <v>837</v>
-      </c>
-      <c r="D279" t="s">
-        <v>801</v>
-      </c>
       <c r="F279" t="s">
         <v>11</v>
-      </c>
-      <c r="G279" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="B280" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="C280" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="D280" t="s">
-        <v>801</v>
+        <v>836</v>
       </c>
       <c r="F280" t="s">
         <v>11</v>
-      </c>
-      <c r="G280" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="B281" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C281" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D281" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="F281" t="s">
         <v>11</v>
+      </c>
+      <c r="G281" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="B282" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C282" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="D282" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="F282" t="s">
         <v>11</v>
-      </c>
-      <c r="G282" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B283" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C283" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D283" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="F283" t="s">
         <v>11</v>
@@ -7990,33 +8098,36 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B284" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C284" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D284" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="F284" t="s">
         <v>11</v>
+      </c>
+      <c r="G284" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B285" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C285" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D285" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F285" t="s">
         <v>11</v>
@@ -8024,13 +8135,16 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B286" t="s">
-        <v>861</v>
+        <v>862</v>
+      </c>
+      <c r="C286" t="s">
+        <v>863</v>
       </c>
       <c r="D286" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F286" t="s">
         <v>11</v>
@@ -8038,16 +8152,16 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B287" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C287" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D287" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F287" t="s">
         <v>11</v>
@@ -8055,420 +8169,630 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B288" t="s">
-        <v>866</v>
+        <v>868</v>
+      </c>
+      <c r="C288" t="s">
+        <v>869</v>
       </c>
       <c r="D288" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F288" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B289" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C289" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D289" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F289" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="290" spans="1:6">
+      <c r="G289" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B290" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C290" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="D290" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F290" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="291" spans="1:6">
+      <c r="G290" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B291" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C291" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D291" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="F291" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B292" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C292" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="D292" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="F292" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="293" spans="1:6">
+      <c r="G292" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B293" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C293" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="D293" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="F293" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B294" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C294" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="D294" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="F294" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="B295" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C295" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="D295" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="F295" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B296" t="s">
-        <v>891</v>
-      </c>
-      <c r="C296" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D296" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F296" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
       <c r="A297" t="s">
+        <v>897</v>
+      </c>
+      <c r="B297" t="s">
+        <v>898</v>
+      </c>
+      <c r="C297" t="s">
+        <v>899</v>
+      </c>
+      <c r="D297" t="s">
         <v>894</v>
       </c>
-      <c r="B297" t="s">
-        <v>895</v>
-      </c>
-      <c r="C297" t="s">
-        <v>896</v>
-      </c>
-      <c r="D297" t="s">
-        <v>893</v>
-      </c>
       <c r="F297" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B298" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D298" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="F298" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B299" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C299" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D299" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="F299" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B300" t="s">
-        <v>905</v>
+        <v>906</v>
+      </c>
+      <c r="C300" t="s">
+        <v>907</v>
       </c>
       <c r="D300" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="F300" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B301" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C301" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D301" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="F301" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B302" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C302" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D302" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F302" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B303" t="s">
+        <v>916</v>
+      </c>
+      <c r="C303" t="s">
+        <v>917</v>
+      </c>
+      <c r="D303" t="s">
         <v>914</v>
       </c>
-      <c r="C303" t="s">
-        <v>915</v>
-      </c>
-      <c r="D303" t="s">
-        <v>912</v>
-      </c>
       <c r="F303" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B304" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C304" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D304" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F304" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B305" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C305" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D305" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F305" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B306" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C306" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D306" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F306" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B307" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C307" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D307" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="F307" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B308" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C308" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D308" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
       <c r="F308" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B309" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C309" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D309" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
       <c r="F309" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B310" t="s">
-        <v>935</v>
-      </c>
-      <c r="C310" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D310" t="s">
-        <v>912</v>
+        <v>940</v>
       </c>
       <c r="F310" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B311" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="C311" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D311" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="F311" t="s">
-        <v>11</v>
-      </c>
-      <c r="G311" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B312" t="s">
-        <v>942</v>
-      </c>
-      <c r="C312" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D312" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="F312" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>947</v>
+      </c>
+      <c r="B313" t="s">
+        <v>948</v>
+      </c>
+      <c r="C313" t="s">
+        <v>949</v>
+      </c>
+      <c r="D313" t="s">
+        <v>944</v>
+      </c>
+      <c r="F313" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" t="s">
+        <v>950</v>
+      </c>
+      <c r="B314" t="s">
+        <v>951</v>
+      </c>
+      <c r="C314" t="s">
+        <v>952</v>
+      </c>
+      <c r="D314" t="s">
+        <v>953</v>
+      </c>
+      <c r="F314" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" t="s">
+        <v>954</v>
+      </c>
+      <c r="B315" t="s">
+        <v>955</v>
+      </c>
+      <c r="C315" t="s">
+        <v>956</v>
+      </c>
+      <c r="D315" t="s">
+        <v>953</v>
+      </c>
+      <c r="F315" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" t="s">
+        <v>957</v>
+      </c>
+      <c r="B316" t="s">
+        <v>958</v>
+      </c>
+      <c r="C316" t="s">
+        <v>959</v>
+      </c>
+      <c r="D316" t="s">
+        <v>953</v>
+      </c>
+      <c r="F316" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" t="s">
+        <v>960</v>
+      </c>
+      <c r="B317" t="s">
+        <v>961</v>
+      </c>
+      <c r="C317" t="s">
+        <v>962</v>
+      </c>
+      <c r="D317" t="s">
+        <v>953</v>
+      </c>
+      <c r="F317" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" t="s">
+        <v>963</v>
+      </c>
+      <c r="B318" t="s">
+        <v>964</v>
+      </c>
+      <c r="C318" t="s">
+        <v>965</v>
+      </c>
+      <c r="D318" t="s">
+        <v>953</v>
+      </c>
+      <c r="F318" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" t="s">
+        <v>966</v>
+      </c>
+      <c r="B319" t="s">
+        <v>967</v>
+      </c>
+      <c r="C319" t="s">
+        <v>968</v>
+      </c>
+      <c r="D319" t="s">
+        <v>953</v>
+      </c>
+      <c r="F319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" t="s">
+        <v>969</v>
+      </c>
+      <c r="B320" t="s">
+        <v>970</v>
+      </c>
+      <c r="C320" t="s">
+        <v>971</v>
+      </c>
+      <c r="D320" t="s">
+        <v>953</v>
+      </c>
+      <c r="F320" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" t="s">
+        <v>972</v>
+      </c>
+      <c r="B321" t="s">
+        <v>973</v>
+      </c>
+      <c r="C321" t="s">
+        <v>974</v>
+      </c>
+      <c r="D321" t="s">
+        <v>953</v>
+      </c>
+      <c r="F321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" t="s">
+        <v>975</v>
+      </c>
+      <c r="B322" t="s">
+        <v>976</v>
+      </c>
+      <c r="C322" t="s">
+        <v>977</v>
+      </c>
+      <c r="D322" t="s">
+        <v>953</v>
+      </c>
+      <c r="F322" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" t="s">
+        <v>978</v>
+      </c>
+      <c r="B323" t="s">
+        <v>979</v>
+      </c>
+      <c r="C323" t="s">
+        <v>980</v>
+      </c>
+      <c r="D323" t="s">
+        <v>981</v>
+      </c>
+      <c r="F323" t="s">
+        <v>11</v>
+      </c>
+      <c r="G323" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" t="s">
+        <v>982</v>
+      </c>
+      <c r="B324" t="s">
+        <v>983</v>
+      </c>
+      <c r="C324" t="s">
+        <v>984</v>
+      </c>
+      <c r="D324" t="s">
+        <v>981</v>
+      </c>
+      <c r="F324" t="s">
         <v>11</v>
       </c>
     </row>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="986">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>{http://iatistandard.org/activity-standard/overview/country-budget-alignment/}status</t>
   </si>
   <si>
     <t>budget_alignment_guidance</t>
@@ -3300,10 +3303,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3325,5475 +3328,5541 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
       <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
       <c r="F13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
         <v>58</v>
       </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>57</v>
-      </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
         <v>65</v>
       </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
         <v>81</v>
       </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>80</v>
-      </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" t="s">
         <v>106</v>
       </c>
-      <c r="B32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" t="s">
         <v>125</v>
       </c>
-      <c r="B38" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" t="s">
         <v>144</v>
       </c>
-      <c r="B44" t="s">
-        <v>145</v>
-      </c>
-      <c r="C44" t="s">
-        <v>146</v>
-      </c>
-      <c r="D44" t="s">
-        <v>143</v>
-      </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" t="s">
+        <v>180</v>
+      </c>
+      <c r="C55" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" t="s">
         <v>178</v>
       </c>
-      <c r="B55" t="s">
-        <v>179</v>
-      </c>
-      <c r="C55" t="s">
-        <v>180</v>
-      </c>
-      <c r="D55" t="s">
-        <v>177</v>
-      </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H58" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D62" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F63" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D67" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D68" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D70" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H73" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C74" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D74" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D77" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D82" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B88" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B91" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C91" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D91" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B92" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C92" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C93" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F94" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F95" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F96" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B100" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C100" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F100" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C101" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C102" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D102" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
+        <v>321</v>
+      </c>
+      <c r="B103" t="s">
+        <v>322</v>
+      </c>
+      <c r="C103" t="s">
+        <v>323</v>
+      </c>
+      <c r="D103" t="s">
         <v>320</v>
       </c>
-      <c r="B103" t="s">
-        <v>321</v>
-      </c>
-      <c r="C103" t="s">
-        <v>322</v>
-      </c>
-      <c r="D103" t="s">
-        <v>319</v>
-      </c>
       <c r="F103" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B104" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C104" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B105" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C105" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D105" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F105" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B106" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C106" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F106" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D107" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F107" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B108" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C108" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D108" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H108" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
+        <v>340</v>
+      </c>
+      <c r="B109" t="s">
+        <v>341</v>
+      </c>
+      <c r="C109" t="s">
+        <v>342</v>
+      </c>
+      <c r="D109" t="s">
         <v>339</v>
       </c>
-      <c r="B109" t="s">
-        <v>340</v>
-      </c>
-      <c r="C109" t="s">
-        <v>341</v>
-      </c>
-      <c r="D109" t="s">
-        <v>338</v>
-      </c>
       <c r="F109" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C110" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D110" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F110" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F111" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B112" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C112" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D112" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F112" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C113" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D113" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C114" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F114" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B115" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C115" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D115" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F115" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C116" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D116" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F116" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B117" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C117" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D117" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D118" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F118" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G118" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H118" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B119" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C119" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D119" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D120" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F120" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D121" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D122" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D123" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C124" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D124" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B125" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C126" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D126" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F126" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G126" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H126" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
+        <v>393</v>
+      </c>
+      <c r="B127" t="s">
+        <v>394</v>
+      </c>
+      <c r="C127" t="s">
+        <v>395</v>
+      </c>
+      <c r="D127" t="s">
         <v>392</v>
       </c>
-      <c r="B127" t="s">
-        <v>393</v>
-      </c>
-      <c r="C127" t="s">
-        <v>394</v>
-      </c>
-      <c r="D127" t="s">
-        <v>391</v>
-      </c>
       <c r="F127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B128" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C128" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F128" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B129" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C129" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F129" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B130" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C130" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F130" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B131" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C131" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D131" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F131" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B132" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C132" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D132" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F132" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B133" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C133" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D133" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F133" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B134" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C134" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F134" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B135" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C135" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D135" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F135" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B136" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F136" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C137" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D137" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F137" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C138" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D138" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F138" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B139" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D139" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F139" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B140" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C140" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D140" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G140" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="H140" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
+        <v>435</v>
+      </c>
+      <c r="B141" t="s">
+        <v>436</v>
+      </c>
+      <c r="D141" t="s">
         <v>434</v>
       </c>
-      <c r="B141" t="s">
-        <v>435</v>
-      </c>
-      <c r="D141" t="s">
-        <v>433</v>
-      </c>
       <c r="F141" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B142" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C142" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D142" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F142" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B143" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C143" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D143" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B144" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C144" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D144" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F144" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B145" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C145" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D145" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B146" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C146" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D146" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F146" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B147" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C147" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D147" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F147" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
+        <v>456</v>
+      </c>
+      <c r="B148" t="s">
+        <v>457</v>
+      </c>
+      <c r="C148" t="s">
+        <v>458</v>
+      </c>
+      <c r="D148" t="s">
         <v>455</v>
       </c>
-      <c r="B148" t="s">
-        <v>456</v>
-      </c>
-      <c r="C148" t="s">
-        <v>457</v>
-      </c>
-      <c r="D148" t="s">
-        <v>454</v>
-      </c>
       <c r="F148" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B149" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C149" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D149" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F149" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B150" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C150" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D150" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F150" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B151" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C151" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D151" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F151" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B152" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C152" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D152" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B153" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D153" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F153" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B154" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D154" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F154" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B155" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C155" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D155" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B156" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C156" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D156" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B157" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D157" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B158" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C158" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D158" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F158" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B159" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C159" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D159" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F159" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
+        <v>489</v>
+      </c>
+      <c r="B160" t="s">
+        <v>490</v>
+      </c>
+      <c r="C160" t="s">
+        <v>491</v>
+      </c>
+      <c r="D160" t="s">
+        <v>455</v>
+      </c>
+      <c r="F160" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>492</v>
+      </c>
+      <c r="B161" t="s">
+        <v>493</v>
+      </c>
+      <c r="C161" t="s">
+        <v>494</v>
+      </c>
+      <c r="D161" t="s">
+        <v>455</v>
+      </c>
+      <c r="F161" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>495</v>
+      </c>
+      <c r="B162" t="s">
+        <v>496</v>
+      </c>
+      <c r="C162" t="s">
+        <v>497</v>
+      </c>
+      <c r="D162" t="s">
+        <v>455</v>
+      </c>
+      <c r="F162" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>498</v>
+      </c>
+      <c r="B163" t="s">
+        <v>499</v>
+      </c>
+      <c r="C163" t="s">
+        <v>500</v>
+      </c>
+      <c r="D163" t="s">
+        <v>455</v>
+      </c>
+      <c r="F163" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" t="s">
+        <v>501</v>
+      </c>
+      <c r="B164" t="s">
+        <v>453</v>
+      </c>
+      <c r="C164" t="s">
+        <v>502</v>
+      </c>
+      <c r="D164" t="s">
+        <v>503</v>
+      </c>
+      <c r="F164" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" t="s">
+        <v>29</v>
+      </c>
+      <c r="H164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>504</v>
+      </c>
+      <c r="B165" t="s">
+        <v>505</v>
+      </c>
+      <c r="D165" t="s">
+        <v>503</v>
+      </c>
+      <c r="F165" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" t="s">
+        <v>506</v>
+      </c>
+      <c r="B166" t="s">
+        <v>507</v>
+      </c>
+      <c r="C166" t="s">
+        <v>508</v>
+      </c>
+      <c r="D166" t="s">
+        <v>503</v>
+      </c>
+      <c r="F166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
+        <v>509</v>
+      </c>
+      <c r="B167" t="s">
+        <v>496</v>
+      </c>
+      <c r="C167" t="s">
+        <v>510</v>
+      </c>
+      <c r="D167" t="s">
+        <v>503</v>
+      </c>
+      <c r="F167" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>511</v>
+      </c>
+      <c r="B168" t="s">
+        <v>499</v>
+      </c>
+      <c r="C168" t="s">
+        <v>500</v>
+      </c>
+      <c r="D168" t="s">
+        <v>503</v>
+      </c>
+      <c r="F168" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>512</v>
+      </c>
+      <c r="B169" t="s">
+        <v>513</v>
+      </c>
+      <c r="C169" t="s">
+        <v>514</v>
+      </c>
+      <c r="D169" t="s">
+        <v>503</v>
+      </c>
+      <c r="F169" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>515</v>
+      </c>
+      <c r="B170" t="s">
+        <v>516</v>
+      </c>
+      <c r="C170" t="s">
+        <v>517</v>
+      </c>
+      <c r="D170" t="s">
+        <v>518</v>
+      </c>
+      <c r="F170" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>519</v>
+      </c>
+      <c r="B171" t="s">
+        <v>479</v>
+      </c>
+      <c r="C171" t="s">
+        <v>520</v>
+      </c>
+      <c r="D171" t="s">
+        <v>518</v>
+      </c>
+      <c r="F171" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>521</v>
+      </c>
+      <c r="B172" t="s">
+        <v>522</v>
+      </c>
+      <c r="C172" t="s">
+        <v>523</v>
+      </c>
+      <c r="D172" t="s">
+        <v>518</v>
+      </c>
+      <c r="F172" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>524</v>
+      </c>
+      <c r="B173" t="s">
+        <v>525</v>
+      </c>
+      <c r="C173" t="s">
+        <v>526</v>
+      </c>
+      <c r="D173" t="s">
+        <v>518</v>
+      </c>
+      <c r="F173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>527</v>
+      </c>
+      <c r="B174" t="s">
+        <v>528</v>
+      </c>
+      <c r="C174" t="s">
+        <v>529</v>
+      </c>
+      <c r="D174" t="s">
+        <v>518</v>
+      </c>
+      <c r="F174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>530</v>
+      </c>
+      <c r="B175" t="s">
+        <v>531</v>
+      </c>
+      <c r="C175" t="s">
         <v>488</v>
       </c>
-      <c r="B160" t="s">
-        <v>489</v>
-      </c>
-      <c r="C160" t="s">
-        <v>490</v>
-      </c>
-      <c r="D160" t="s">
-        <v>454</v>
-      </c>
-      <c r="F160" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
+      <c r="D175" t="s">
+        <v>518</v>
+      </c>
+      <c r="F175" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>532</v>
+      </c>
+      <c r="B176" t="s">
+        <v>533</v>
+      </c>
+      <c r="C176" t="s">
         <v>491</v>
       </c>
-      <c r="B161" t="s">
-        <v>492</v>
-      </c>
-      <c r="C161" t="s">
-        <v>493</v>
-      </c>
-      <c r="D161" t="s">
-        <v>454</v>
-      </c>
-      <c r="F161" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>494</v>
-      </c>
-      <c r="B162" t="s">
-        <v>495</v>
-      </c>
-      <c r="C162" t="s">
-        <v>496</v>
-      </c>
-      <c r="D162" t="s">
-        <v>454</v>
-      </c>
-      <c r="F162" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
-        <v>497</v>
-      </c>
-      <c r="B163" t="s">
-        <v>498</v>
-      </c>
-      <c r="C163" t="s">
-        <v>499</v>
-      </c>
-      <c r="D163" t="s">
-        <v>454</v>
-      </c>
-      <c r="F163" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
-        <v>500</v>
-      </c>
-      <c r="B164" t="s">
-        <v>452</v>
-      </c>
-      <c r="C164" t="s">
-        <v>501</v>
-      </c>
-      <c r="D164" t="s">
-        <v>502</v>
-      </c>
-      <c r="F164" t="s">
-        <v>11</v>
-      </c>
-      <c r="G164" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
-        <v>503</v>
-      </c>
-      <c r="B165" t="s">
-        <v>504</v>
-      </c>
-      <c r="D165" t="s">
-        <v>502</v>
-      </c>
-      <c r="F165" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>505</v>
-      </c>
-      <c r="B166" t="s">
-        <v>506</v>
-      </c>
-      <c r="C166" t="s">
-        <v>507</v>
-      </c>
-      <c r="D166" t="s">
-        <v>502</v>
-      </c>
-      <c r="F166" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
-        <v>508</v>
-      </c>
-      <c r="B167" t="s">
-        <v>495</v>
-      </c>
-      <c r="C167" t="s">
-        <v>509</v>
-      </c>
-      <c r="D167" t="s">
-        <v>502</v>
-      </c>
-      <c r="F167" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>510</v>
-      </c>
-      <c r="B168" t="s">
-        <v>498</v>
-      </c>
-      <c r="C168" t="s">
-        <v>499</v>
-      </c>
-      <c r="D168" t="s">
-        <v>502</v>
-      </c>
-      <c r="F168" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
-        <v>511</v>
-      </c>
-      <c r="B169" t="s">
-        <v>512</v>
-      </c>
-      <c r="C169" t="s">
-        <v>513</v>
-      </c>
-      <c r="D169" t="s">
-        <v>502</v>
-      </c>
-      <c r="F169" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>514</v>
-      </c>
-      <c r="B170" t="s">
-        <v>515</v>
-      </c>
-      <c r="C170" t="s">
-        <v>516</v>
-      </c>
-      <c r="D170" t="s">
-        <v>517</v>
-      </c>
-      <c r="F170" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
+      <c r="D176" t="s">
         <v>518</v>
       </c>
-      <c r="B171" t="s">
-        <v>478</v>
-      </c>
-      <c r="C171" t="s">
-        <v>519</v>
-      </c>
-      <c r="D171" t="s">
-        <v>517</v>
-      </c>
-      <c r="F171" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
-        <v>520</v>
-      </c>
-      <c r="B172" t="s">
-        <v>521</v>
-      </c>
-      <c r="C172" t="s">
-        <v>522</v>
-      </c>
-      <c r="D172" t="s">
-        <v>517</v>
-      </c>
-      <c r="F172" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
-        <v>523</v>
-      </c>
-      <c r="B173" t="s">
-        <v>524</v>
-      </c>
-      <c r="C173" t="s">
-        <v>525</v>
-      </c>
-      <c r="D173" t="s">
-        <v>517</v>
-      </c>
-      <c r="F173" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
-        <v>526</v>
-      </c>
-      <c r="B174" t="s">
-        <v>527</v>
-      </c>
-      <c r="C174" t="s">
-        <v>528</v>
-      </c>
-      <c r="D174" t="s">
-        <v>517</v>
-      </c>
-      <c r="F174" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
-        <v>529</v>
-      </c>
-      <c r="B175" t="s">
-        <v>530</v>
-      </c>
-      <c r="C175" t="s">
-        <v>487</v>
-      </c>
-      <c r="D175" t="s">
-        <v>517</v>
-      </c>
-      <c r="F175" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
-        <v>531</v>
-      </c>
-      <c r="B176" t="s">
-        <v>532</v>
-      </c>
-      <c r="C176" t="s">
-        <v>490</v>
-      </c>
-      <c r="D176" t="s">
-        <v>517</v>
-      </c>
       <c r="F176" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B177" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C177" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D177" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F177" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B178" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C178" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D178" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F178" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B179" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C179" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D179" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F179" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
+        <v>543</v>
+      </c>
+      <c r="B180" t="s">
+        <v>544</v>
+      </c>
+      <c r="C180" t="s">
+        <v>545</v>
+      </c>
+      <c r="D180" t="s">
         <v>542</v>
       </c>
-      <c r="B180" t="s">
-        <v>543</v>
-      </c>
-      <c r="C180" t="s">
-        <v>544</v>
-      </c>
-      <c r="D180" t="s">
-        <v>541</v>
-      </c>
       <c r="F180" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B181" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C181" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D181" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F181" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B182" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C182" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D182" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F182" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B183" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C183" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D183" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F183" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B184" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C184" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D184" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F184" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B185" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C185" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D185" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F185" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B186" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C186" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D186" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F186" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B187" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C187" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D187" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F187" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
+        <v>570</v>
+      </c>
+      <c r="B188" t="s">
+        <v>571</v>
+      </c>
+      <c r="C188" t="s">
+        <v>572</v>
+      </c>
+      <c r="D188" t="s">
         <v>569</v>
       </c>
-      <c r="B188" t="s">
-        <v>570</v>
-      </c>
-      <c r="C188" t="s">
-        <v>571</v>
-      </c>
-      <c r="D188" t="s">
-        <v>568</v>
-      </c>
       <c r="F188" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B189" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C189" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D189" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F189" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B190" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C190" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D190" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F190" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B191" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C191" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D191" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F191" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B192" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D192" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F192" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B193" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C193" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D193" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F193" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B194" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C194" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D194" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F194" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
+        <v>591</v>
+      </c>
+      <c r="B195" t="s">
+        <v>592</v>
+      </c>
+      <c r="C195" t="s">
+        <v>593</v>
+      </c>
+      <c r="D195" t="s">
         <v>590</v>
       </c>
-      <c r="B195" t="s">
-        <v>591</v>
-      </c>
-      <c r="C195" t="s">
-        <v>592</v>
-      </c>
-      <c r="D195" t="s">
-        <v>589</v>
-      </c>
       <c r="F195" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B196" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C196" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D196" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F196" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B197" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C197" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D197" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F197" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B198" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C198" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D198" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F198" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B199" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D199" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F199" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B200" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C200" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D200" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F200" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
+        <v>609</v>
+      </c>
+      <c r="B201" t="s">
+        <v>610</v>
+      </c>
+      <c r="C201" t="s">
+        <v>611</v>
+      </c>
+      <c r="D201" t="s">
         <v>608</v>
       </c>
-      <c r="B201" t="s">
-        <v>609</v>
-      </c>
-      <c r="C201" t="s">
-        <v>610</v>
-      </c>
-      <c r="D201" t="s">
-        <v>607</v>
-      </c>
       <c r="F201" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B202" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C202" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D202" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F202" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B203" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C203" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D203" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F203" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B204" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C204" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D204" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F204" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
+        <v>622</v>
+      </c>
+      <c r="B205" t="s">
+        <v>623</v>
+      </c>
+      <c r="C205" t="s">
+        <v>624</v>
+      </c>
+      <c r="D205" t="s">
         <v>621</v>
       </c>
-      <c r="B205" t="s">
-        <v>622</v>
-      </c>
-      <c r="C205" t="s">
-        <v>623</v>
-      </c>
-      <c r="D205" t="s">
-        <v>620</v>
-      </c>
       <c r="F205" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B206" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D206" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F206" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B207" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C207" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D207" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F207" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B208" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C208" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D208" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F208" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B209" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C209" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D209" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F209" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B210" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C210" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D210" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F210" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B211" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C211" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D211" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F211" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B212" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C212" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D212" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F212" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B213" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C213" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D213" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F213" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B214" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C214" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D214" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F214" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B215" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D215" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F215" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B216" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C216" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D216" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F216" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B217" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C217" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D217" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F217" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B218" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C218" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D218" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F218" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B219" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C219" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D219" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F219" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B220" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C220" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D220" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F220" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B221" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C221" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D221" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F221" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B222" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C222" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D222" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F222" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
+        <v>676</v>
+      </c>
+      <c r="B223" t="s">
+        <v>677</v>
+      </c>
+      <c r="C223" t="s">
+        <v>678</v>
+      </c>
+      <c r="D223" t="s">
         <v>675</v>
       </c>
-      <c r="B223" t="s">
-        <v>676</v>
-      </c>
-      <c r="C223" t="s">
-        <v>677</v>
-      </c>
-      <c r="D223" t="s">
-        <v>674</v>
-      </c>
       <c r="F223" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B224" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C224" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D224" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F224" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B225" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D225" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F225" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B226" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C226" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D226" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F226" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B227" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D227" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F227" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B228" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C228" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D228" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F228" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
+        <v>693</v>
+      </c>
+      <c r="B229" t="s">
+        <v>694</v>
+      </c>
+      <c r="C229" t="s">
+        <v>695</v>
+      </c>
+      <c r="D229" t="s">
         <v>692</v>
       </c>
-      <c r="B229" t="s">
-        <v>693</v>
-      </c>
-      <c r="C229" t="s">
-        <v>694</v>
-      </c>
-      <c r="D229" t="s">
-        <v>691</v>
-      </c>
       <c r="F229" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B230" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D230" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F230" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B231" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C231" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D231" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F231" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B232" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C232" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D232" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F232" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B233" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C233" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D233" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F233" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
+        <v>708</v>
+      </c>
+      <c r="B234" t="s">
+        <v>709</v>
+      </c>
+      <c r="D234" t="s">
         <v>707</v>
       </c>
-      <c r="B234" t="s">
-        <v>708</v>
-      </c>
-      <c r="D234" t="s">
-        <v>706</v>
-      </c>
       <c r="F234" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B235" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C235" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D235" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F235" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B236" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D236" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F236" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B237" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C237" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D237" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F237" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B238" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C238" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D238" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F238" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B239" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C239" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D239" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F239" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B240" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C240" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D240" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F240" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B241" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D241" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F241" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B242" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D242" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F242" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B243" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C243" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D243" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F243" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B244" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C244" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D244" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F244" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B245" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C245" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D245" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F245" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B246" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D246" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F246" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B247" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C247" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D247" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F247" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B248" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C248" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D248" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F248" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B249" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C249" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D249" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F249" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B250" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C250" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D250" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F250" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B251" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C251" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D251" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F251" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B252" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C252" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D252" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F252" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
+        <v>761</v>
+      </c>
+      <c r="B253" t="s">
+        <v>762</v>
+      </c>
+      <c r="C253" t="s">
+        <v>763</v>
+      </c>
+      <c r="D253" t="s">
         <v>760</v>
       </c>
-      <c r="B253" t="s">
-        <v>761</v>
-      </c>
-      <c r="C253" t="s">
-        <v>762</v>
-      </c>
-      <c r="D253" t="s">
-        <v>759</v>
-      </c>
       <c r="F253" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B254" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C254" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D254" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F254" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B255" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C255" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D255" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F255" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B256" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C256" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D256" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F256" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B257" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C257" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D257" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F257" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B258" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C258" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D258" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F258" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B259" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C259" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D259" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F259" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B260" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C260" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D260" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F260" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B261" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C261" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D261" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F261" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B262" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C262" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D262" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F262" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B263" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C263" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D263" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F263" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
+        <v>796</v>
+      </c>
+      <c r="B264" t="s">
+        <v>797</v>
+      </c>
+      <c r="C264" t="s">
+        <v>798</v>
+      </c>
+      <c r="D264" t="s">
         <v>795</v>
       </c>
-      <c r="B264" t="s">
-        <v>796</v>
-      </c>
-      <c r="C264" t="s">
-        <v>797</v>
-      </c>
-      <c r="D264" t="s">
-        <v>794</v>
-      </c>
       <c r="F264" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B265" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C265" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D265" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F265" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B266" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C266" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D266" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F266" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B267" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C267" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D267" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F267" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B268" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C268" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D268" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F268" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B269" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D269" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F269" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B270" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C270" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D270" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F270" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
+        <v>818</v>
+      </c>
+      <c r="B271" t="s">
+        <v>819</v>
+      </c>
+      <c r="C271" t="s">
+        <v>820</v>
+      </c>
+      <c r="D271" t="s">
         <v>817</v>
       </c>
-      <c r="B271" t="s">
-        <v>818</v>
-      </c>
-      <c r="C271" t="s">
-        <v>819</v>
-      </c>
-      <c r="D271" t="s">
-        <v>816</v>
-      </c>
       <c r="F271" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B272" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C272" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D272" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F272" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
       <c r="A273" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B273" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C273" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D273" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F273" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
       <c r="A274" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B274" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C274" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D274" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F274" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
       <c r="A275" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B275" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D275" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F275" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
       <c r="A276" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B276" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C276" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D276" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F276" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
       <c r="A277" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B277" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D277" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F277" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G277" t="s">
+        <v>838</v>
+      </c>
+      <c r="H277" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" t="s">
+        <v>839</v>
+      </c>
+      <c r="B278" t="s">
+        <v>840</v>
+      </c>
+      <c r="C278" t="s">
+        <v>841</v>
+      </c>
+      <c r="D278" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="278" spans="1:7">
-      <c r="A278" t="s">
+      <c r="F278" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278" t="s">
+        <v>29</v>
+      </c>
+      <c r="H278" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" t="s">
+        <v>842</v>
+      </c>
+      <c r="B279" t="s">
+        <v>843</v>
+      </c>
+      <c r="C279" t="s">
+        <v>844</v>
+      </c>
+      <c r="D279" t="s">
+        <v>837</v>
+      </c>
+      <c r="F279" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" t="s">
+        <v>845</v>
+      </c>
+      <c r="B280" t="s">
+        <v>846</v>
+      </c>
+      <c r="C280" t="s">
+        <v>847</v>
+      </c>
+      <c r="D280" t="s">
+        <v>837</v>
+      </c>
+      <c r="F280" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" t="s">
+        <v>848</v>
+      </c>
+      <c r="B281" t="s">
+        <v>849</v>
+      </c>
+      <c r="C281" t="s">
+        <v>850</v>
+      </c>
+      <c r="D281" t="s">
+        <v>837</v>
+      </c>
+      <c r="F281" t="s">
+        <v>12</v>
+      </c>
+      <c r="G281" t="s">
+        <v>29</v>
+      </c>
+      <c r="H281" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" t="s">
+        <v>851</v>
+      </c>
+      <c r="B282" t="s">
+        <v>852</v>
+      </c>
+      <c r="C282" t="s">
+        <v>853</v>
+      </c>
+      <c r="D282" t="s">
+        <v>837</v>
+      </c>
+      <c r="F282" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" t="s">
+        <v>854</v>
+      </c>
+      <c r="B283" t="s">
+        <v>849</v>
+      </c>
+      <c r="C283" t="s">
+        <v>855</v>
+      </c>
+      <c r="D283" t="s">
+        <v>837</v>
+      </c>
+      <c r="F283" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" t="s">
+        <v>856</v>
+      </c>
+      <c r="B284" t="s">
+        <v>857</v>
+      </c>
+      <c r="C284" t="s">
+        <v>858</v>
+      </c>
+      <c r="D284" t="s">
+        <v>837</v>
+      </c>
+      <c r="F284" t="s">
+        <v>12</v>
+      </c>
+      <c r="G284" t="s">
         <v>838</v>
       </c>
-      <c r="B278" t="s">
-        <v>839</v>
-      </c>
-      <c r="C278" t="s">
-        <v>840</v>
-      </c>
-      <c r="D278" t="s">
-        <v>836</v>
-      </c>
-      <c r="F278" t="s">
-        <v>11</v>
-      </c>
-      <c r="G278" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
-      <c r="A279" t="s">
-        <v>841</v>
-      </c>
-      <c r="B279" t="s">
-        <v>842</v>
-      </c>
-      <c r="C279" t="s">
-        <v>843</v>
-      </c>
-      <c r="D279" t="s">
-        <v>836</v>
-      </c>
-      <c r="F279" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
-      <c r="A280" t="s">
-        <v>844</v>
-      </c>
-      <c r="B280" t="s">
-        <v>845</v>
-      </c>
-      <c r="C280" t="s">
-        <v>846</v>
-      </c>
-      <c r="D280" t="s">
-        <v>836</v>
-      </c>
-      <c r="F280" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
-      <c r="A281" t="s">
-        <v>847</v>
-      </c>
-      <c r="B281" t="s">
-        <v>848</v>
-      </c>
-      <c r="C281" t="s">
-        <v>849</v>
-      </c>
-      <c r="D281" t="s">
-        <v>836</v>
-      </c>
-      <c r="F281" t="s">
-        <v>11</v>
-      </c>
-      <c r="G281" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
-      <c r="A282" t="s">
-        <v>850</v>
-      </c>
-      <c r="B282" t="s">
-        <v>851</v>
-      </c>
-      <c r="C282" t="s">
-        <v>852</v>
-      </c>
-      <c r="D282" t="s">
-        <v>836</v>
-      </c>
-      <c r="F282" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
-      <c r="A283" t="s">
-        <v>853</v>
-      </c>
-      <c r="B283" t="s">
-        <v>848</v>
-      </c>
-      <c r="C283" t="s">
-        <v>854</v>
-      </c>
-      <c r="D283" t="s">
-        <v>836</v>
-      </c>
-      <c r="F283" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
-      <c r="A284" t="s">
-        <v>855</v>
-      </c>
-      <c r="B284" t="s">
-        <v>856</v>
-      </c>
-      <c r="C284" t="s">
-        <v>857</v>
-      </c>
-      <c r="D284" t="s">
-        <v>836</v>
-      </c>
-      <c r="F284" t="s">
-        <v>11</v>
-      </c>
-      <c r="G284" t="s">
+      <c r="H284" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" t="s">
+        <v>859</v>
+      </c>
+      <c r="B285" t="s">
+        <v>860</v>
+      </c>
+      <c r="C285" t="s">
+        <v>861</v>
+      </c>
+      <c r="D285" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="285" spans="1:7">
-      <c r="A285" t="s">
-        <v>858</v>
-      </c>
-      <c r="B285" t="s">
-        <v>859</v>
-      </c>
-      <c r="C285" t="s">
-        <v>860</v>
-      </c>
-      <c r="D285" t="s">
-        <v>836</v>
-      </c>
       <c r="F285" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
       <c r="A286" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B286" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C286" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D286" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F286" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
       <c r="A287" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B287" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C287" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D287" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F287" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
       <c r="A288" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B288" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C288" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D288" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F288" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
       <c r="A289" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B289" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C289" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D289" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F289" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G289" t="s">
+        <v>838</v>
+      </c>
+      <c r="H289" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" t="s">
+        <v>874</v>
+      </c>
+      <c r="B290" t="s">
+        <v>875</v>
+      </c>
+      <c r="C290" t="s">
+        <v>876</v>
+      </c>
+      <c r="D290" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="290" spans="1:7">
-      <c r="A290" t="s">
-        <v>873</v>
-      </c>
-      <c r="B290" t="s">
-        <v>874</v>
-      </c>
-      <c r="C290" t="s">
-        <v>875</v>
-      </c>
-      <c r="D290" t="s">
-        <v>836</v>
-      </c>
       <c r="F290" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G290" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+        <v>838</v>
+      </c>
+      <c r="H290" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
       <c r="A291" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B291" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C291" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D291" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F291" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
       <c r="A292" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B292" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C292" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D292" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F292" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G292" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+        <v>838</v>
+      </c>
+      <c r="H292" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
       <c r="A293" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B293" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C293" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D293" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F293" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
       <c r="A294" t="s">
+        <v>889</v>
+      </c>
+      <c r="B294" t="s">
+        <v>890</v>
+      </c>
+      <c r="C294" t="s">
+        <v>891</v>
+      </c>
+      <c r="D294" t="s">
         <v>888</v>
       </c>
-      <c r="B294" t="s">
-        <v>889</v>
-      </c>
-      <c r="C294" t="s">
-        <v>890</v>
-      </c>
-      <c r="D294" t="s">
-        <v>887</v>
-      </c>
       <c r="F294" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
       <c r="A295" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B295" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C295" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D295" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F295" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296" t="s">
+        <v>896</v>
+      </c>
+      <c r="B296" t="s">
+        <v>897</v>
+      </c>
+      <c r="D296" t="s">
         <v>895</v>
       </c>
-      <c r="B296" t="s">
-        <v>896</v>
-      </c>
-      <c r="D296" t="s">
-        <v>894</v>
-      </c>
       <c r="F296" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B297" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C297" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D297" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F297" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
       <c r="A298" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B298" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D298" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F298" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B299" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C299" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D299" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F299" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B300" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C300" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D300" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F300" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B301" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C301" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D301" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F301" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B302" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C302" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D302" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F302" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303" t="s">
+        <v>916</v>
+      </c>
+      <c r="B303" t="s">
+        <v>917</v>
+      </c>
+      <c r="C303" t="s">
+        <v>918</v>
+      </c>
+      <c r="D303" t="s">
         <v>915</v>
       </c>
-      <c r="B303" t="s">
-        <v>916</v>
-      </c>
-      <c r="C303" t="s">
-        <v>917</v>
-      </c>
-      <c r="D303" t="s">
-        <v>914</v>
-      </c>
       <c r="F303" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B304" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C304" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D304" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F304" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B305" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C305" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D305" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F305" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B306" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C306" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D306" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F306" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B307" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C307" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D307" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F307" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B308" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C308" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D308" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F308" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
+        <v>936</v>
+      </c>
+      <c r="B309" t="s">
+        <v>937</v>
+      </c>
+      <c r="C309" t="s">
+        <v>938</v>
+      </c>
+      <c r="D309" t="s">
         <v>935</v>
       </c>
-      <c r="B309" t="s">
-        <v>936</v>
-      </c>
-      <c r="C309" t="s">
-        <v>937</v>
-      </c>
-      <c r="D309" t="s">
-        <v>934</v>
-      </c>
       <c r="F309" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B310" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D310" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F310" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B311" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C311" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D311" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F311" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
+        <v>946</v>
+      </c>
+      <c r="B312" t="s">
+        <v>947</v>
+      </c>
+      <c r="D312" t="s">
         <v>945</v>
       </c>
-      <c r="B312" t="s">
-        <v>946</v>
-      </c>
-      <c r="D312" t="s">
-        <v>944</v>
-      </c>
       <c r="F312" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B313" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C313" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D313" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F313" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B314" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C314" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D314" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F314" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
+        <v>955</v>
+      </c>
+      <c r="B315" t="s">
+        <v>956</v>
+      </c>
+      <c r="C315" t="s">
+        <v>957</v>
+      </c>
+      <c r="D315" t="s">
         <v>954</v>
       </c>
-      <c r="B315" t="s">
-        <v>955</v>
-      </c>
-      <c r="C315" t="s">
-        <v>956</v>
-      </c>
-      <c r="D315" t="s">
-        <v>953</v>
-      </c>
       <c r="F315" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B316" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C316" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D316" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F316" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B317" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C317" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D317" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F317" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B318" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C318" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D318" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F318" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B319" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C319" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D319" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F319" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B320" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C320" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D320" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F320" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
       <c r="A321" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B321" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C321" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D321" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F321" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
       <c r="A322" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B322" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C322" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D322" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F322" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
       <c r="A323" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B323" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C323" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D323" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F323" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G323" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
+        <v>838</v>
+      </c>
+      <c r="H323" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
       <c r="A324" t="s">
+        <v>983</v>
+      </c>
+      <c r="B324" t="s">
+        <v>984</v>
+      </c>
+      <c r="C324" t="s">
+        <v>985</v>
+      </c>
+      <c r="D324" t="s">
         <v>982</v>
       </c>
-      <c r="B324" t="s">
-        <v>983</v>
-      </c>
-      <c r="C324" t="s">
-        <v>984</v>
-      </c>
-      <c r="D324" t="s">
-        <v>981</v>
-      </c>
       <c r="F324" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="985">
   <si>
     <t>code</t>
   </si>
@@ -28,16 +28,13 @@
     <t>category</t>
   </si>
   <si>
-    <t>url</t>
-  </si>
-  <si>
     <t>status</t>
   </si>
   <si>
+    <t>budget_alignment_guidance</t>
+  </si>
+  <si>
     <t>{http://iatistandard.org/activity-standard/overview/country-budget-alignment/}status</t>
-  </si>
-  <si>
-    <t>budget_alignment_guidance</t>
   </si>
   <si>
     <t>11110</t>
@@ -3303,10 +3300,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3328,5541 +3325,5538 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
       <c r="G7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>44</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>48</v>
       </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>53</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
         <v>54</v>
       </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>56</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>57</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
         <v>58</v>
       </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
-      <c r="D17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>63</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>64</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
         <v>65</v>
       </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>66</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
         <v>68</v>
       </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
         <v>71</v>
       </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>73</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
         <v>74</v>
       </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
         <v>77</v>
       </c>
-      <c r="D22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>78</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>80</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
         <v>81</v>
       </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>82</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>83</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
         <v>84</v>
       </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>85</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>86</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
         <v>87</v>
       </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>88</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
         <v>90</v>
       </c>
-      <c r="D26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>91</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
         <v>93</v>
       </c>
-      <c r="D27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>94</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>95</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
         <v>96</v>
       </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>97</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>98</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
         <v>99</v>
       </c>
-      <c r="D29" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>100</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>101</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
         <v>102</v>
       </c>
-      <c r="D30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>103</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
         <v>106</v>
       </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>107</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>108</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
         <v>109</v>
       </c>
-      <c r="D32" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>110</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>111</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
         <v>112</v>
       </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>113</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>114</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
         <v>115</v>
       </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>116</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>117</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
         <v>118</v>
       </c>
-      <c r="D35" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>119</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>120</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
         <v>121</v>
       </c>
-      <c r="D36" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>122</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>123</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>124</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
-      <c r="F37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>126</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>127</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
         <v>128</v>
       </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>129</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>130</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
         <v>131</v>
       </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>132</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>133</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
         <v>134</v>
       </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>135</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>136</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
         <v>137</v>
       </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="F41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>138</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>139</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
         <v>140</v>
       </c>
-      <c r="D42" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>141</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>142</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>143</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
         <v>144</v>
       </c>
-      <c r="F43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>145</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>146</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
         <v>147</v>
       </c>
-      <c r="D44" t="s">
-        <v>144</v>
-      </c>
-      <c r="F44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>148</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>149</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
+        <v>143</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
         <v>150</v>
       </c>
-      <c r="D45" t="s">
-        <v>144</v>
-      </c>
-      <c r="F45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>151</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>152</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
         <v>153</v>
       </c>
-      <c r="D46" t="s">
-        <v>144</v>
-      </c>
-      <c r="F46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>154</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>155</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>143</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
         <v>156</v>
       </c>
-      <c r="D47" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>157</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>158</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>143</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
         <v>159</v>
       </c>
-      <c r="D48" t="s">
-        <v>144</v>
-      </c>
-      <c r="F48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>160</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>161</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
         <v>162</v>
       </c>
-      <c r="D49" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>163</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>164</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>143</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
         <v>165</v>
       </c>
-      <c r="D50" t="s">
-        <v>144</v>
-      </c>
-      <c r="F50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>166</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>167</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
         <v>168</v>
       </c>
-      <c r="D51" t="s">
-        <v>144</v>
-      </c>
-      <c r="F51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>169</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>170</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
         <v>171</v>
       </c>
-      <c r="D52" t="s">
-        <v>144</v>
-      </c>
-      <c r="F52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>172</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>173</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
         <v>174</v>
       </c>
-      <c r="D53" t="s">
-        <v>144</v>
-      </c>
-      <c r="F53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>175</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>176</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>177</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
         <v>178</v>
       </c>
-      <c r="F54" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" t="s">
-        <v>29</v>
-      </c>
-      <c r="H54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>179</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>180</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
         <v>181</v>
       </c>
-      <c r="D55" t="s">
-        <v>178</v>
-      </c>
-      <c r="F55" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" t="s">
-        <v>29</v>
-      </c>
-      <c r="H55" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>182</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>183</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
         <v>184</v>
       </c>
-      <c r="D56" t="s">
-        <v>178</v>
-      </c>
-      <c r="F56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" t="s">
-        <v>29</v>
-      </c>
-      <c r="H56" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>185</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>186</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
         <v>187</v>
       </c>
-      <c r="D57" t="s">
-        <v>178</v>
-      </c>
-      <c r="F57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>188</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>189</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
         <v>190</v>
       </c>
-      <c r="D58" t="s">
-        <v>178</v>
-      </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" t="s">
-        <v>29</v>
-      </c>
-      <c r="H58" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>191</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>192</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
         <v>193</v>
       </c>
-      <c r="D59" t="s">
-        <v>178</v>
-      </c>
-      <c r="F59" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>194</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>195</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>177</v>
+      </c>
+      <c r="E60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
         <v>196</v>
       </c>
-      <c r="D60" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>197</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>198</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
         <v>199</v>
       </c>
-      <c r="D61" t="s">
-        <v>178</v>
-      </c>
-      <c r="F61" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>200</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>201</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
         <v>202</v>
       </c>
-      <c r="D62" t="s">
-        <v>178</v>
-      </c>
-      <c r="F62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>203</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>204</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" t="s">
         <v>205</v>
       </c>
-      <c r="D63" t="s">
-        <v>178</v>
-      </c>
-      <c r="F63" t="s">
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>207</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>208</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
         <v>209</v>
       </c>
-      <c r="D64" t="s">
-        <v>178</v>
-      </c>
-      <c r="F64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>210</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>211</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
         <v>212</v>
       </c>
-      <c r="D65" t="s">
-        <v>178</v>
-      </c>
-      <c r="F65" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>213</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>214</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>177</v>
+      </c>
+      <c r="E66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
         <v>215</v>
       </c>
-      <c r="D66" t="s">
-        <v>178</v>
-      </c>
-      <c r="F66" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>216</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>217</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
         <v>218</v>
       </c>
-      <c r="D67" t="s">
-        <v>178</v>
-      </c>
-      <c r="F67" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>219</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>220</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>177</v>
+      </c>
+      <c r="E68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
         <v>221</v>
       </c>
-      <c r="D68" t="s">
-        <v>178</v>
-      </c>
-      <c r="F68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>222</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>223</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
         <v>224</v>
       </c>
-      <c r="D69" t="s">
-        <v>178</v>
-      </c>
-      <c r="F69" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>225</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>226</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
+        <v>177</v>
+      </c>
+      <c r="E70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
         <v>227</v>
       </c>
-      <c r="D70" t="s">
-        <v>178</v>
-      </c>
-      <c r="F70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>228</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>229</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>177</v>
+      </c>
+      <c r="E71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
         <v>230</v>
       </c>
-      <c r="D71" t="s">
-        <v>178</v>
-      </c>
-      <c r="F71" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>231</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>232</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
+        <v>177</v>
+      </c>
+      <c r="E72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
         <v>233</v>
       </c>
-      <c r="D72" t="s">
-        <v>178</v>
-      </c>
-      <c r="F72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>234</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>235</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
+        <v>177</v>
+      </c>
+      <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
         <v>236</v>
       </c>
-      <c r="D73" t="s">
-        <v>178</v>
-      </c>
-      <c r="F73" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" t="s">
-        <v>29</v>
-      </c>
-      <c r="H73" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>237</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>238</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
         <v>239</v>
       </c>
-      <c r="D74" t="s">
-        <v>178</v>
-      </c>
-      <c r="F74" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>240</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>241</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
         <v>242</v>
       </c>
-      <c r="D75" t="s">
-        <v>178</v>
-      </c>
-      <c r="F75" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>243</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>244</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
         <v>245</v>
       </c>
-      <c r="D76" t="s">
-        <v>178</v>
-      </c>
-      <c r="F76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>246</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>247</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
         <v>248</v>
       </c>
-      <c r="D77" t="s">
-        <v>178</v>
-      </c>
-      <c r="F77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>249</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>250</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
         <v>251</v>
       </c>
-      <c r="D78" t="s">
-        <v>178</v>
-      </c>
-      <c r="F78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>252</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>253</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
         <v>254</v>
       </c>
-      <c r="D79" t="s">
-        <v>178</v>
-      </c>
-      <c r="F79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>255</v>
       </c>
-      <c r="B80" t="s">
+      <c r="D80" t="s">
+        <v>177</v>
+      </c>
+      <c r="E80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
         <v>256</v>
       </c>
-      <c r="D80" t="s">
-        <v>178</v>
-      </c>
-      <c r="F80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>257</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>258</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
         <v>259</v>
       </c>
-      <c r="D81" t="s">
-        <v>178</v>
-      </c>
-      <c r="F81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>260</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>261</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
+        <v>177</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
         <v>262</v>
       </c>
-      <c r="D82" t="s">
-        <v>178</v>
-      </c>
-      <c r="F82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>263</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>264</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>177</v>
+      </c>
+      <c r="E83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
         <v>265</v>
       </c>
-      <c r="D83" t="s">
-        <v>178</v>
-      </c>
-      <c r="F83" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>266</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>267</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>177</v>
+      </c>
+      <c r="E84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
         <v>268</v>
       </c>
-      <c r="D84" t="s">
-        <v>178</v>
-      </c>
-      <c r="F84" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>269</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>270</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>177</v>
+      </c>
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
         <v>271</v>
       </c>
-      <c r="D85" t="s">
-        <v>178</v>
-      </c>
-      <c r="F85" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>272</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>273</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>177</v>
+      </c>
+      <c r="E86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
         <v>274</v>
       </c>
-      <c r="D86" t="s">
-        <v>178</v>
-      </c>
-      <c r="F86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>275</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>276</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
         <v>277</v>
       </c>
-      <c r="D87" t="s">
-        <v>178</v>
-      </c>
-      <c r="F87" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>278</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>279</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
+        <v>177</v>
+      </c>
+      <c r="E88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
         <v>280</v>
       </c>
-      <c r="D88" t="s">
-        <v>178</v>
-      </c>
-      <c r="F88" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>281</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>282</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
+        <v>177</v>
+      </c>
+      <c r="E89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
         <v>283</v>
       </c>
-      <c r="D89" t="s">
-        <v>178</v>
-      </c>
-      <c r="F89" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>284</v>
       </c>
-      <c r="B90" t="s">
+      <c r="D90" t="s">
+        <v>177</v>
+      </c>
+      <c r="E90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
         <v>285</v>
       </c>
-      <c r="D90" t="s">
-        <v>178</v>
-      </c>
-      <c r="F90" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>286</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>287</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
+        <v>177</v>
+      </c>
+      <c r="E91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
         <v>288</v>
       </c>
-      <c r="D91" t="s">
-        <v>178</v>
-      </c>
-      <c r="F91" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>289</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>290</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
+        <v>177</v>
+      </c>
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
         <v>291</v>
       </c>
-      <c r="D92" t="s">
-        <v>178</v>
-      </c>
-      <c r="F92" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" t="s">
+      <c r="B93" t="s">
+        <v>272</v>
+      </c>
+      <c r="C93" t="s">
         <v>292</v>
       </c>
-      <c r="B93" t="s">
-        <v>273</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
+        <v>177</v>
+      </c>
+      <c r="E93" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
         <v>293</v>
       </c>
-      <c r="D93" t="s">
-        <v>178</v>
-      </c>
-      <c r="F93" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" t="s">
+      <c r="B94" t="s">
+        <v>289</v>
+      </c>
+      <c r="C94" t="s">
         <v>294</v>
       </c>
-      <c r="B94" t="s">
-        <v>290</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
+        <v>177</v>
+      </c>
+      <c r="E94" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
         <v>295</v>
       </c>
-      <c r="D94" t="s">
-        <v>178</v>
-      </c>
-      <c r="F94" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" t="s">
+      <c r="B95" t="s">
         <v>296</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>297</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
+        <v>177</v>
+      </c>
+      <c r="E95" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
         <v>298</v>
       </c>
-      <c r="D95" t="s">
-        <v>178</v>
-      </c>
-      <c r="F95" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
+      <c r="B96" t="s">
         <v>299</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>300</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
+        <v>177</v>
+      </c>
+      <c r="E96" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
         <v>301</v>
       </c>
-      <c r="D96" t="s">
-        <v>178</v>
-      </c>
-      <c r="F96" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
         <v>302</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>303</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
+        <v>177</v>
+      </c>
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
         <v>304</v>
       </c>
-      <c r="D97" t="s">
-        <v>178</v>
-      </c>
-      <c r="F97" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" t="s">
+      <c r="B98" t="s">
         <v>305</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>306</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
+        <v>177</v>
+      </c>
+      <c r="E98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
         <v>307</v>
       </c>
-      <c r="D98" t="s">
-        <v>178</v>
-      </c>
-      <c r="F98" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
         <v>308</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>309</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
+        <v>177</v>
+      </c>
+      <c r="E99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
         <v>310</v>
       </c>
-      <c r="D99" t="s">
-        <v>178</v>
-      </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>311</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>312</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
+        <v>177</v>
+      </c>
+      <c r="E100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
         <v>313</v>
       </c>
-      <c r="D100" t="s">
-        <v>178</v>
-      </c>
-      <c r="F100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>314</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>315</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
+        <v>177</v>
+      </c>
+      <c r="E101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
         <v>316</v>
       </c>
-      <c r="D101" t="s">
-        <v>178</v>
-      </c>
-      <c r="F101" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>317</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>318</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>319</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
         <v>320</v>
       </c>
-      <c r="F102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>321</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>322</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>319</v>
+      </c>
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
         <v>323</v>
       </c>
-      <c r="D103" t="s">
-        <v>320</v>
-      </c>
-      <c r="F103" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" t="s">
+      <c r="B104" t="s">
         <v>324</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>325</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
+        <v>319</v>
+      </c>
+      <c r="E104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
         <v>326</v>
       </c>
-      <c r="D104" t="s">
-        <v>320</v>
-      </c>
-      <c r="F104" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
         <v>327</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>328</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
+        <v>319</v>
+      </c>
+      <c r="E105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
         <v>329</v>
       </c>
-      <c r="D105" t="s">
-        <v>320</v>
-      </c>
-      <c r="F105" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
         <v>330</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>331</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
+        <v>319</v>
+      </c>
+      <c r="E106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
         <v>332</v>
       </c>
-      <c r="D106" t="s">
-        <v>320</v>
-      </c>
-      <c r="F106" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
         <v>333</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>334</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>319</v>
+      </c>
+      <c r="E107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
         <v>335</v>
       </c>
-      <c r="D107" t="s">
-        <v>320</v>
-      </c>
-      <c r="F107" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>336</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>337</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>338</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
         <v>339</v>
       </c>
-      <c r="F108" t="s">
-        <v>12</v>
-      </c>
-      <c r="G108" t="s">
-        <v>29</v>
-      </c>
-      <c r="H108" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
         <v>340</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>341</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>338</v>
+      </c>
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
         <v>342</v>
       </c>
-      <c r="D109" t="s">
-        <v>339</v>
-      </c>
-      <c r="F109" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>343</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>344</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>338</v>
+      </c>
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
         <v>345</v>
       </c>
-      <c r="D110" t="s">
-        <v>339</v>
-      </c>
-      <c r="F110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
         <v>346</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>347</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
+        <v>338</v>
+      </c>
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
         <v>348</v>
       </c>
-      <c r="D111" t="s">
-        <v>339</v>
-      </c>
-      <c r="F111" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>349</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>350</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>338</v>
+      </c>
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
         <v>351</v>
       </c>
-      <c r="D112" t="s">
-        <v>339</v>
-      </c>
-      <c r="F112" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>352</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>353</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>338</v>
+      </c>
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
         <v>354</v>
       </c>
-      <c r="D113" t="s">
-        <v>339</v>
-      </c>
-      <c r="F113" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
         <v>355</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>356</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>338</v>
+      </c>
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
         <v>357</v>
       </c>
-      <c r="D114" t="s">
-        <v>339</v>
-      </c>
-      <c r="F114" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" t="s">
+      <c r="B115" t="s">
         <v>358</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>359</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>338</v>
+      </c>
+      <c r="E115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
         <v>360</v>
       </c>
-      <c r="D115" t="s">
-        <v>339</v>
-      </c>
-      <c r="F115" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>361</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>362</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>338</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
         <v>363</v>
       </c>
-      <c r="D116" t="s">
-        <v>339</v>
-      </c>
-      <c r="F116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" t="s">
+      <c r="B117" t="s">
         <v>364</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>365</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>338</v>
+      </c>
+      <c r="E117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
         <v>366</v>
       </c>
-      <c r="D117" t="s">
-        <v>339</v>
-      </c>
-      <c r="F117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" t="s">
+      <c r="B118" t="s">
         <v>367</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>368</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>338</v>
+      </c>
+      <c r="E118" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
         <v>369</v>
       </c>
-      <c r="D118" t="s">
-        <v>339</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>29</v>
-      </c>
-      <c r="H118" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>370</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>371</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>338</v>
+      </c>
+      <c r="E119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
         <v>372</v>
       </c>
-      <c r="D119" t="s">
-        <v>339</v>
-      </c>
-      <c r="F119" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>373</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>374</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>338</v>
+      </c>
+      <c r="E120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
         <v>375</v>
       </c>
-      <c r="D120" t="s">
-        <v>339</v>
-      </c>
-      <c r="F120" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>376</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>377</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>338</v>
+      </c>
+      <c r="E121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
         <v>378</v>
       </c>
-      <c r="D121" t="s">
-        <v>339</v>
-      </c>
-      <c r="F121" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" t="s">
+      <c r="B122" t="s">
         <v>379</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>338</v>
+      </c>
+      <c r="E122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
         <v>380</v>
       </c>
-      <c r="D122" t="s">
-        <v>339</v>
-      </c>
-      <c r="F122" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" t="s">
+      <c r="B123" t="s">
         <v>381</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
+        <v>338</v>
+      </c>
+      <c r="E123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
         <v>382</v>
       </c>
-      <c r="D123" t="s">
-        <v>339</v>
-      </c>
-      <c r="F123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" t="s">
+      <c r="B124" t="s">
         <v>383</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>384</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>338</v>
+      </c>
+      <c r="E124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
         <v>385</v>
       </c>
-      <c r="D124" t="s">
-        <v>339</v>
-      </c>
-      <c r="F124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>386</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>387</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>338</v>
+      </c>
+      <c r="E125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
         <v>388</v>
       </c>
-      <c r="D125" t="s">
-        <v>339</v>
-      </c>
-      <c r="F125" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>389</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>390</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>391</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
         <v>392</v>
       </c>
-      <c r="F126" t="s">
-        <v>12</v>
-      </c>
-      <c r="G126" t="s">
-        <v>29</v>
-      </c>
-      <c r="H126" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>393</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>394</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>391</v>
+      </c>
+      <c r="E127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
         <v>395</v>
       </c>
-      <c r="D127" t="s">
-        <v>392</v>
-      </c>
-      <c r="F127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" t="s">
+      <c r="B128" t="s">
         <v>396</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>397</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>391</v>
+      </c>
+      <c r="E128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
         <v>398</v>
       </c>
-      <c r="D128" t="s">
-        <v>392</v>
-      </c>
-      <c r="F128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>399</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>400</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
+        <v>391</v>
+      </c>
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
         <v>401</v>
       </c>
-      <c r="D129" t="s">
-        <v>392</v>
-      </c>
-      <c r="F129" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
-      <c r="A130" t="s">
+      <c r="B130" t="s">
         <v>402</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>403</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>391</v>
+      </c>
+      <c r="E130" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
         <v>404</v>
       </c>
-      <c r="D130" t="s">
-        <v>392</v>
-      </c>
-      <c r="F130" t="s">
-        <v>12</v>
-      </c>
-      <c r="G130" t="s">
-        <v>29</v>
-      </c>
-      <c r="H130" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>405</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>406</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>391</v>
+      </c>
+      <c r="E131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
         <v>407</v>
       </c>
-      <c r="D131" t="s">
-        <v>392</v>
-      </c>
-      <c r="F131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>408</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>409</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>391</v>
+      </c>
+      <c r="E132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
         <v>410</v>
       </c>
-      <c r="D132" t="s">
-        <v>392</v>
-      </c>
-      <c r="F132" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>411</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>412</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>391</v>
+      </c>
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
         <v>413</v>
       </c>
-      <c r="D133" t="s">
-        <v>392</v>
-      </c>
-      <c r="F133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" t="s">
+      <c r="B134" t="s">
         <v>414</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>415</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>391</v>
+      </c>
+      <c r="E134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
         <v>416</v>
       </c>
-      <c r="D134" t="s">
-        <v>392</v>
-      </c>
-      <c r="F134" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>417</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>418</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>391</v>
+      </c>
+      <c r="E135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
         <v>419</v>
       </c>
-      <c r="D135" t="s">
-        <v>392</v>
-      </c>
-      <c r="F135" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>420</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>421</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>391</v>
+      </c>
+      <c r="E136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
         <v>422</v>
       </c>
-      <c r="D136" t="s">
-        <v>392</v>
-      </c>
-      <c r="F136" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>423</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>424</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>391</v>
+      </c>
+      <c r="E137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
         <v>425</v>
       </c>
-      <c r="D137" t="s">
-        <v>392</v>
-      </c>
-      <c r="F137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>426</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>427</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>391</v>
+      </c>
+      <c r="E138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
         <v>428</v>
       </c>
-      <c r="D138" t="s">
-        <v>392</v>
-      </c>
-      <c r="F138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
         <v>429</v>
       </c>
-      <c r="B139" t="s">
+      <c r="D139" t="s">
+        <v>391</v>
+      </c>
+      <c r="E139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
         <v>430</v>
       </c>
-      <c r="D139" t="s">
-        <v>392</v>
-      </c>
-      <c r="F139" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
         <v>431</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>432</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>433</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" t="s">
+        <v>28</v>
+      </c>
+      <c r="G140" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
         <v>434</v>
       </c>
-      <c r="F140" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" t="s">
-        <v>29</v>
-      </c>
-      <c r="H140" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>435</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D141" t="s">
+        <v>433</v>
+      </c>
+      <c r="E141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
         <v>436</v>
       </c>
-      <c r="D141" t="s">
-        <v>434</v>
-      </c>
-      <c r="F141" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
         <v>437</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>438</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
+        <v>433</v>
+      </c>
+      <c r="E142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
         <v>439</v>
       </c>
-      <c r="D142" t="s">
-        <v>434</v>
-      </c>
-      <c r="F142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" t="s">
+      <c r="B143" t="s">
         <v>440</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>441</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
+        <v>433</v>
+      </c>
+      <c r="E143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
         <v>442</v>
       </c>
-      <c r="D143" t="s">
-        <v>434</v>
-      </c>
-      <c r="F143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>443</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>444</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
+        <v>433</v>
+      </c>
+      <c r="E144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
         <v>445</v>
       </c>
-      <c r="D144" t="s">
-        <v>434</v>
-      </c>
-      <c r="F144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
         <v>446</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>447</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
+        <v>433</v>
+      </c>
+      <c r="E145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
         <v>448</v>
       </c>
-      <c r="D145" t="s">
-        <v>434</v>
-      </c>
-      <c r="F145" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
+      <c r="B146" t="s">
         <v>449</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>450</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
+        <v>433</v>
+      </c>
+      <c r="E146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
         <v>451</v>
       </c>
-      <c r="D146" t="s">
-        <v>434</v>
-      </c>
-      <c r="F146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
+      <c r="B147" t="s">
         <v>452</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>453</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>454</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
         <v>455</v>
       </c>
-      <c r="F147" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+      <c r="B148" t="s">
         <v>456</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>457</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
+        <v>454</v>
+      </c>
+      <c r="E148" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
         <v>458</v>
       </c>
-      <c r="D148" t="s">
-        <v>455</v>
-      </c>
-      <c r="F148" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
+      <c r="B149" t="s">
         <v>459</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>460</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
+        <v>454</v>
+      </c>
+      <c r="E149" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
         <v>461</v>
       </c>
-      <c r="D149" t="s">
-        <v>455</v>
-      </c>
-      <c r="F149" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+      <c r="B150" t="s">
         <v>462</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>463</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
+        <v>454</v>
+      </c>
+      <c r="E150" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
         <v>464</v>
       </c>
-      <c r="D150" t="s">
-        <v>455</v>
-      </c>
-      <c r="F150" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
+      <c r="B151" t="s">
         <v>465</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>466</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
+        <v>454</v>
+      </c>
+      <c r="E151" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
         <v>467</v>
       </c>
-      <c r="D151" t="s">
-        <v>455</v>
-      </c>
-      <c r="F151" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
+      <c r="B152" t="s">
         <v>468</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>469</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
+        <v>454</v>
+      </c>
+      <c r="E152" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
         <v>470</v>
       </c>
-      <c r="D152" t="s">
-        <v>455</v>
-      </c>
-      <c r="F152" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
+      <c r="B153" t="s">
         <v>471</v>
       </c>
-      <c r="B153" t="s">
+      <c r="D153" t="s">
+        <v>454</v>
+      </c>
+      <c r="E153" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
         <v>472</v>
       </c>
-      <c r="D153" t="s">
-        <v>455</v>
-      </c>
-      <c r="F153" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
+      <c r="B154" t="s">
         <v>473</v>
       </c>
-      <c r="B154" t="s">
+      <c r="D154" t="s">
+        <v>454</v>
+      </c>
+      <c r="E154" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
         <v>474</v>
       </c>
-      <c r="D154" t="s">
-        <v>455</v>
-      </c>
-      <c r="F154" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
+      <c r="B155" t="s">
         <v>475</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>476</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
+        <v>454</v>
+      </c>
+      <c r="E155" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
         <v>477</v>
       </c>
-      <c r="D155" t="s">
-        <v>455</v>
-      </c>
-      <c r="F155" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
+      <c r="B156" t="s">
         <v>478</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>479</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
+        <v>454</v>
+      </c>
+      <c r="E156" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
         <v>480</v>
       </c>
-      <c r="D156" t="s">
-        <v>455</v>
-      </c>
-      <c r="F156" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
+      <c r="B157" t="s">
         <v>481</v>
       </c>
-      <c r="B157" t="s">
+      <c r="D157" t="s">
+        <v>454</v>
+      </c>
+      <c r="E157" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
         <v>482</v>
       </c>
-      <c r="D157" t="s">
-        <v>455</v>
-      </c>
-      <c r="F157" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
+      <c r="B158" t="s">
         <v>483</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>484</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
+        <v>454</v>
+      </c>
+      <c r="E158" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
         <v>485</v>
       </c>
-      <c r="D158" t="s">
-        <v>455</v>
-      </c>
-      <c r="F158" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
+      <c r="B159" t="s">
         <v>486</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>487</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
+        <v>454</v>
+      </c>
+      <c r="E159" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
         <v>488</v>
       </c>
-      <c r="D159" t="s">
-        <v>455</v>
-      </c>
-      <c r="F159" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
+      <c r="B160" t="s">
         <v>489</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>490</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
+        <v>454</v>
+      </c>
+      <c r="E160" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
         <v>491</v>
       </c>
-      <c r="D160" t="s">
-        <v>455</v>
-      </c>
-      <c r="F160" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="A161" t="s">
+      <c r="B161" t="s">
         <v>492</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>493</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
+        <v>454</v>
+      </c>
+      <c r="E161" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
         <v>494</v>
       </c>
-      <c r="D161" t="s">
-        <v>455</v>
-      </c>
-      <c r="F161" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
         <v>495</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>496</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
+        <v>454</v>
+      </c>
+      <c r="E162" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
         <v>497</v>
       </c>
-      <c r="D162" t="s">
-        <v>455</v>
-      </c>
-      <c r="F162" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>498</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>499</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
+        <v>454</v>
+      </c>
+      <c r="E163" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
         <v>500</v>
       </c>
-      <c r="D163" t="s">
-        <v>455</v>
-      </c>
-      <c r="F163" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
+        <v>452</v>
+      </c>
+      <c r="C164" t="s">
         <v>501</v>
       </c>
-      <c r="B164" t="s">
-        <v>453</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>502</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" t="s">
+        <v>28</v>
+      </c>
+      <c r="G164" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
         <v>503</v>
       </c>
-      <c r="F164" t="s">
-        <v>12</v>
-      </c>
-      <c r="G164" t="s">
-        <v>29</v>
-      </c>
-      <c r="H164" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="A165" t="s">
+      <c r="B165" t="s">
         <v>504</v>
       </c>
-      <c r="B165" t="s">
+      <c r="D165" t="s">
+        <v>502</v>
+      </c>
+      <c r="E165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
         <v>505</v>
       </c>
-      <c r="D165" t="s">
-        <v>503</v>
-      </c>
-      <c r="F165" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
-      <c r="A166" t="s">
+      <c r="B166" t="s">
         <v>506</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>507</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
+        <v>502</v>
+      </c>
+      <c r="E166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
         <v>508</v>
       </c>
-      <c r="D166" t="s">
-        <v>503</v>
-      </c>
-      <c r="F166" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" t="s">
+      <c r="B167" t="s">
+        <v>495</v>
+      </c>
+      <c r="C167" t="s">
         <v>509</v>
       </c>
-      <c r="B167" t="s">
-        <v>496</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
+        <v>502</v>
+      </c>
+      <c r="E167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
         <v>510</v>
       </c>
-      <c r="D167" t="s">
-        <v>503</v>
-      </c>
-      <c r="F167" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" t="s">
+      <c r="B168" t="s">
+        <v>498</v>
+      </c>
+      <c r="C168" t="s">
+        <v>499</v>
+      </c>
+      <c r="D168" t="s">
+        <v>502</v>
+      </c>
+      <c r="E168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
         <v>511</v>
       </c>
-      <c r="B168" t="s">
-        <v>499</v>
-      </c>
-      <c r="C168" t="s">
-        <v>500</v>
-      </c>
-      <c r="D168" t="s">
-        <v>503</v>
-      </c>
-      <c r="F168" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="A169" t="s">
+      <c r="B169" t="s">
         <v>512</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>513</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
+        <v>502</v>
+      </c>
+      <c r="E169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
         <v>514</v>
       </c>
-      <c r="D169" t="s">
-        <v>503</v>
-      </c>
-      <c r="F169" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
-      <c r="A170" t="s">
+      <c r="B170" t="s">
         <v>515</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>516</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>517</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
         <v>518</v>
       </c>
-      <c r="F170" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
-      <c r="A171" t="s">
+      <c r="B171" t="s">
+        <v>478</v>
+      </c>
+      <c r="C171" t="s">
         <v>519</v>
       </c>
-      <c r="B171" t="s">
-        <v>479</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>517</v>
+      </c>
+      <c r="E171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
         <v>520</v>
       </c>
-      <c r="D171" t="s">
-        <v>518</v>
-      </c>
-      <c r="F171" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="A172" t="s">
+      <c r="B172" t="s">
         <v>521</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>522</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
+        <v>517</v>
+      </c>
+      <c r="E172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
         <v>523</v>
       </c>
-      <c r="D172" t="s">
-        <v>518</v>
-      </c>
-      <c r="F172" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
-      <c r="A173" t="s">
+      <c r="B173" t="s">
         <v>524</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>525</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
+        <v>517</v>
+      </c>
+      <c r="E173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
         <v>526</v>
       </c>
-      <c r="D173" t="s">
-        <v>518</v>
-      </c>
-      <c r="F173" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="A174" t="s">
+      <c r="B174" t="s">
         <v>527</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>528</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
+        <v>517</v>
+      </c>
+      <c r="E174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
         <v>529</v>
       </c>
-      <c r="D174" t="s">
-        <v>518</v>
-      </c>
-      <c r="F174" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" t="s">
+      <c r="B175" t="s">
         <v>530</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
+        <v>487</v>
+      </c>
+      <c r="D175" t="s">
+        <v>517</v>
+      </c>
+      <c r="E175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
         <v>531</v>
       </c>
-      <c r="C175" t="s">
-        <v>488</v>
-      </c>
-      <c r="D175" t="s">
-        <v>518</v>
-      </c>
-      <c r="F175" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="A176" t="s">
+      <c r="B176" t="s">
         <v>532</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
+        <v>490</v>
+      </c>
+      <c r="D176" t="s">
+        <v>517</v>
+      </c>
+      <c r="E176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
         <v>533</v>
       </c>
-      <c r="C176" t="s">
-        <v>491</v>
-      </c>
-      <c r="D176" t="s">
-        <v>518</v>
-      </c>
-      <c r="F176" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" t="s">
+      <c r="B177" t="s">
+        <v>481</v>
+      </c>
+      <c r="C177" t="s">
         <v>534</v>
       </c>
-      <c r="B177" t="s">
-        <v>482</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
+        <v>517</v>
+      </c>
+      <c r="E177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
         <v>535</v>
       </c>
-      <c r="D177" t="s">
-        <v>518</v>
-      </c>
-      <c r="F177" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178" t="s">
+      <c r="B178" t="s">
         <v>536</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>537</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
+        <v>517</v>
+      </c>
+      <c r="E178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
         <v>538</v>
       </c>
-      <c r="D178" t="s">
-        <v>518</v>
-      </c>
-      <c r="F178" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179" t="s">
+      <c r="B179" t="s">
         <v>539</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>540</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>541</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
         <v>542</v>
       </c>
-      <c r="F179" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180" t="s">
+      <c r="B180" t="s">
         <v>543</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>544</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
+        <v>541</v>
+      </c>
+      <c r="E180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
         <v>545</v>
       </c>
-      <c r="D180" t="s">
-        <v>542</v>
-      </c>
-      <c r="F180" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" t="s">
+      <c r="B181" t="s">
         <v>546</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>547</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
+        <v>541</v>
+      </c>
+      <c r="E181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
         <v>548</v>
       </c>
-      <c r="D181" t="s">
-        <v>542</v>
-      </c>
-      <c r="F181" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" t="s">
+      <c r="B182" t="s">
         <v>549</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>550</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
+        <v>541</v>
+      </c>
+      <c r="E182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
         <v>551</v>
       </c>
-      <c r="D182" t="s">
-        <v>542</v>
-      </c>
-      <c r="F182" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183" t="s">
+      <c r="B183" t="s">
         <v>552</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>553</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
+        <v>541</v>
+      </c>
+      <c r="E183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
         <v>554</v>
       </c>
-      <c r="D183" t="s">
-        <v>542</v>
-      </c>
-      <c r="F183" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" t="s">
+      <c r="B184" t="s">
         <v>555</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>556</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
+        <v>541</v>
+      </c>
+      <c r="E184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
         <v>557</v>
       </c>
-      <c r="D184" t="s">
-        <v>542</v>
-      </c>
-      <c r="F184" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" t="s">
+      <c r="B185" t="s">
         <v>558</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>559</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>560</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
         <v>561</v>
       </c>
-      <c r="F185" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186" t="s">
+      <c r="B186" t="s">
         <v>562</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>563</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>564</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
         <v>565</v>
       </c>
-      <c r="F186" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187" t="s">
+      <c r="B187" t="s">
         <v>566</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>567</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>568</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
         <v>569</v>
       </c>
-      <c r="F187" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188" t="s">
+      <c r="B188" t="s">
         <v>570</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>571</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
+        <v>568</v>
+      </c>
+      <c r="E188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
         <v>572</v>
       </c>
-      <c r="D188" t="s">
-        <v>569</v>
-      </c>
-      <c r="F188" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189" t="s">
+      <c r="B189" t="s">
         <v>573</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>574</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
+        <v>568</v>
+      </c>
+      <c r="E189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
         <v>575</v>
       </c>
-      <c r="D189" t="s">
-        <v>569</v>
-      </c>
-      <c r="F189" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" t="s">
+      <c r="B190" t="s">
         <v>576</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>577</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
+        <v>568</v>
+      </c>
+      <c r="E190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
         <v>578</v>
       </c>
-      <c r="D190" t="s">
-        <v>569</v>
-      </c>
-      <c r="F190" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" t="s">
+      <c r="B191" t="s">
         <v>579</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>580</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191" t="s">
+        <v>568</v>
+      </c>
+      <c r="E191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
         <v>581</v>
       </c>
-      <c r="D191" t="s">
-        <v>569</v>
-      </c>
-      <c r="F191" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" t="s">
+      <c r="B192" t="s">
         <v>582</v>
       </c>
-      <c r="B192" t="s">
+      <c r="D192" t="s">
+        <v>568</v>
+      </c>
+      <c r="E192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
         <v>583</v>
       </c>
-      <c r="D192" t="s">
-        <v>569</v>
-      </c>
-      <c r="F192" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" t="s">
+      <c r="B193" t="s">
         <v>584</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>585</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193" t="s">
+        <v>568</v>
+      </c>
+      <c r="E193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
         <v>586</v>
       </c>
-      <c r="D193" t="s">
-        <v>569</v>
-      </c>
-      <c r="F193" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" t="s">
+      <c r="B194" t="s">
         <v>587</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>588</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>589</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
         <v>590</v>
       </c>
-      <c r="F194" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195" t="s">
+      <c r="B195" t="s">
         <v>591</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>592</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
+        <v>589</v>
+      </c>
+      <c r="E195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
         <v>593</v>
       </c>
-      <c r="D195" t="s">
-        <v>590</v>
-      </c>
-      <c r="F195" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" t="s">
+      <c r="B196" t="s">
         <v>594</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>595</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
+        <v>589</v>
+      </c>
+      <c r="E196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
         <v>596</v>
       </c>
-      <c r="D196" t="s">
-        <v>590</v>
-      </c>
-      <c r="F196" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" t="s">
+      <c r="B197" t="s">
         <v>597</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>598</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197" t="s">
+        <v>589</v>
+      </c>
+      <c r="E197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
         <v>599</v>
       </c>
-      <c r="D197" t="s">
-        <v>590</v>
-      </c>
-      <c r="F197" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" t="s">
+      <c r="B198" t="s">
         <v>600</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>601</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
+        <v>589</v>
+      </c>
+      <c r="E198" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
         <v>602</v>
       </c>
-      <c r="D198" t="s">
-        <v>590</v>
-      </c>
-      <c r="F198" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199" t="s">
+      <c r="B199" t="s">
         <v>603</v>
       </c>
-      <c r="B199" t="s">
+      <c r="D199" t="s">
+        <v>589</v>
+      </c>
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
         <v>604</v>
       </c>
-      <c r="D199" t="s">
-        <v>590</v>
-      </c>
-      <c r="F199" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200" t="s">
+      <c r="B200" t="s">
         <v>605</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>606</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
         <v>607</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
         <v>608</v>
       </c>
-      <c r="F200" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201" t="s">
+      <c r="B201" t="s">
         <v>609</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>610</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201" t="s">
+        <v>607</v>
+      </c>
+      <c r="E201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
         <v>611</v>
       </c>
-      <c r="D201" t="s">
-        <v>608</v>
-      </c>
-      <c r="F201" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202" t="s">
+      <c r="B202" t="s">
         <v>612</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>613</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202" t="s">
+        <v>607</v>
+      </c>
+      <c r="E202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
         <v>614</v>
       </c>
-      <c r="D202" t="s">
-        <v>608</v>
-      </c>
-      <c r="F202" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203" t="s">
+      <c r="B203" t="s">
         <v>615</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>616</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203" t="s">
+        <v>607</v>
+      </c>
+      <c r="E203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
         <v>617</v>
       </c>
-      <c r="D203" t="s">
-        <v>608</v>
-      </c>
-      <c r="F203" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
+      <c r="B204" t="s">
         <v>618</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>619</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>620</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
         <v>621</v>
       </c>
-      <c r="F204" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" t="s">
+      <c r="B205" t="s">
         <v>622</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>623</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
+        <v>620</v>
+      </c>
+      <c r="E205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
         <v>624</v>
       </c>
-      <c r="D205" t="s">
-        <v>621</v>
-      </c>
-      <c r="F205" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206" t="s">
+      <c r="B206" t="s">
         <v>625</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>626</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
+        <v>620</v>
+      </c>
+      <c r="E206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
         <v>627</v>
       </c>
-      <c r="D206" t="s">
-        <v>621</v>
-      </c>
-      <c r="F206" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207" t="s">
+      <c r="B207" t="s">
         <v>628</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
         <v>629</v>
       </c>
-      <c r="C207" t="s">
+      <c r="D207" t="s">
+        <v>620</v>
+      </c>
+      <c r="E207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
         <v>630</v>
       </c>
-      <c r="D207" t="s">
-        <v>621</v>
-      </c>
-      <c r="F207" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208" t="s">
+      <c r="B208" t="s">
         <v>631</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>632</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208" t="s">
+        <v>620</v>
+      </c>
+      <c r="E208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
         <v>633</v>
       </c>
-      <c r="D208" t="s">
-        <v>621</v>
-      </c>
-      <c r="F208" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
+      <c r="B209" t="s">
         <v>634</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>635</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209" t="s">
+        <v>620</v>
+      </c>
+      <c r="E209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
         <v>636</v>
       </c>
-      <c r="D209" t="s">
-        <v>621</v>
-      </c>
-      <c r="F209" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
+      <c r="B210" t="s">
         <v>637</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>638</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210" t="s">
+        <v>620</v>
+      </c>
+      <c r="E210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
         <v>639</v>
       </c>
-      <c r="D210" t="s">
-        <v>621</v>
-      </c>
-      <c r="F210" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
+      <c r="B211" t="s">
         <v>640</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>641</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
+        <v>620</v>
+      </c>
+      <c r="E211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
         <v>642</v>
       </c>
-      <c r="D211" t="s">
-        <v>621</v>
-      </c>
-      <c r="F211" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
+      <c r="B212" t="s">
         <v>643</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>644</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
+        <v>620</v>
+      </c>
+      <c r="E212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
         <v>645</v>
       </c>
-      <c r="D212" t="s">
-        <v>621</v>
-      </c>
-      <c r="F212" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
+      <c r="B213" t="s">
         <v>646</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>647</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
+        <v>620</v>
+      </c>
+      <c r="E213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
         <v>648</v>
       </c>
-      <c r="D213" t="s">
-        <v>621</v>
-      </c>
-      <c r="F213" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
+      <c r="B214" t="s">
         <v>649</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>650</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
+        <v>620</v>
+      </c>
+      <c r="E214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
         <v>651</v>
       </c>
-      <c r="D214" t="s">
-        <v>621</v>
-      </c>
-      <c r="F214" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215" t="s">
+      <c r="B215" t="s">
         <v>652</v>
       </c>
-      <c r="B215" t="s">
+      <c r="D215" t="s">
+        <v>620</v>
+      </c>
+      <c r="E215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
         <v>653</v>
       </c>
-      <c r="D215" t="s">
-        <v>621</v>
-      </c>
-      <c r="F215" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216" t="s">
+      <c r="B216" t="s">
         <v>654</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>655</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
+        <v>620</v>
+      </c>
+      <c r="E216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
         <v>656</v>
       </c>
-      <c r="D216" t="s">
-        <v>621</v>
-      </c>
-      <c r="F216" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217" t="s">
+      <c r="B217" t="s">
         <v>657</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>658</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
+        <v>620</v>
+      </c>
+      <c r="E217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
         <v>659</v>
       </c>
-      <c r="D217" t="s">
-        <v>621</v>
-      </c>
-      <c r="F217" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218" t="s">
+      <c r="B218" t="s">
         <v>660</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>661</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
+        <v>620</v>
+      </c>
+      <c r="E218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
         <v>662</v>
       </c>
-      <c r="D218" t="s">
-        <v>621</v>
-      </c>
-      <c r="F218" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219" t="s">
+      <c r="B219" t="s">
         <v>663</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>664</v>
       </c>
-      <c r="C219" t="s">
+      <c r="D219" t="s">
+        <v>620</v>
+      </c>
+      <c r="E219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
         <v>665</v>
       </c>
-      <c r="D219" t="s">
-        <v>621</v>
-      </c>
-      <c r="F219" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220" t="s">
+      <c r="B220" t="s">
         <v>666</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>667</v>
       </c>
-      <c r="C220" t="s">
+      <c r="D220" t="s">
+        <v>620</v>
+      </c>
+      <c r="E220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
         <v>668</v>
       </c>
-      <c r="D220" t="s">
-        <v>621</v>
-      </c>
-      <c r="F220" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221" t="s">
+      <c r="B221" t="s">
         <v>669</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>670</v>
       </c>
-      <c r="C221" t="s">
+      <c r="D221" t="s">
+        <v>620</v>
+      </c>
+      <c r="E221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
         <v>671</v>
       </c>
-      <c r="D221" t="s">
-        <v>621</v>
-      </c>
-      <c r="F221" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222" t="s">
+      <c r="B222" t="s">
         <v>672</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>673</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
         <v>674</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
         <v>675</v>
       </c>
-      <c r="F222" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223" t="s">
+      <c r="B223" t="s">
         <v>676</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>677</v>
       </c>
-      <c r="C223" t="s">
+      <c r="D223" t="s">
+        <v>674</v>
+      </c>
+      <c r="E223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
         <v>678</v>
       </c>
-      <c r="D223" t="s">
-        <v>675</v>
-      </c>
-      <c r="F223" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224" t="s">
+      <c r="B224" t="s">
         <v>679</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>680</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
+        <v>674</v>
+      </c>
+      <c r="E224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
         <v>681</v>
       </c>
-      <c r="D224" t="s">
-        <v>675</v>
-      </c>
-      <c r="F224" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225" t="s">
+      <c r="B225" t="s">
         <v>682</v>
       </c>
-      <c r="B225" t="s">
+      <c r="D225" t="s">
+        <v>674</v>
+      </c>
+      <c r="E225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
         <v>683</v>
       </c>
-      <c r="D225" t="s">
-        <v>675</v>
-      </c>
-      <c r="F225" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226" t="s">
+      <c r="B226" t="s">
         <v>684</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
         <v>685</v>
       </c>
-      <c r="C226" t="s">
+      <c r="D226" t="s">
+        <v>674</v>
+      </c>
+      <c r="E226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
         <v>686</v>
       </c>
-      <c r="D226" t="s">
-        <v>675</v>
-      </c>
-      <c r="F226" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227" t="s">
+      <c r="B227" t="s">
         <v>687</v>
       </c>
-      <c r="B227" t="s">
+      <c r="D227" t="s">
+        <v>674</v>
+      </c>
+      <c r="E227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
         <v>688</v>
       </c>
-      <c r="D227" t="s">
-        <v>675</v>
-      </c>
-      <c r="F227" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228" t="s">
+      <c r="B228" t="s">
         <v>689</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>690</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D228" t="s">
         <v>691</v>
       </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
         <v>692</v>
       </c>
-      <c r="F228" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229" t="s">
+      <c r="B229" t="s">
         <v>693</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>694</v>
       </c>
-      <c r="C229" t="s">
+      <c r="D229" t="s">
+        <v>691</v>
+      </c>
+      <c r="E229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
         <v>695</v>
       </c>
-      <c r="D229" t="s">
-        <v>692</v>
-      </c>
-      <c r="F229" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230" t="s">
+      <c r="B230" t="s">
         <v>696</v>
       </c>
-      <c r="B230" t="s">
+      <c r="D230" t="s">
+        <v>691</v>
+      </c>
+      <c r="E230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
         <v>697</v>
       </c>
-      <c r="D230" t="s">
-        <v>692</v>
-      </c>
-      <c r="F230" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231" t="s">
+      <c r="B231" t="s">
         <v>698</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
         <v>699</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" t="s">
+        <v>691</v>
+      </c>
+      <c r="E231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
         <v>700</v>
       </c>
-      <c r="D231" t="s">
-        <v>692</v>
-      </c>
-      <c r="F231" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232" t="s">
+      <c r="B232" t="s">
         <v>701</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>702</v>
       </c>
-      <c r="C232" t="s">
+      <c r="D232" t="s">
+        <v>691</v>
+      </c>
+      <c r="E232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
         <v>703</v>
       </c>
-      <c r="D232" t="s">
-        <v>692</v>
-      </c>
-      <c r="F232" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233" t="s">
+      <c r="B233" t="s">
         <v>704</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>705</v>
       </c>
-      <c r="C233" t="s">
+      <c r="D233" t="s">
         <v>706</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
         <v>707</v>
       </c>
-      <c r="F233" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234" t="s">
+      <c r="B234" t="s">
         <v>708</v>
       </c>
-      <c r="B234" t="s">
+      <c r="D234" t="s">
+        <v>706</v>
+      </c>
+      <c r="E234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
         <v>709</v>
       </c>
-      <c r="D234" t="s">
-        <v>707</v>
-      </c>
-      <c r="F234" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235" t="s">
+      <c r="B235" t="s">
         <v>710</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>711</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D235" t="s">
+        <v>706</v>
+      </c>
+      <c r="E235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
         <v>712</v>
       </c>
-      <c r="D235" t="s">
-        <v>707</v>
-      </c>
-      <c r="F235" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236" t="s">
+      <c r="B236" t="s">
         <v>713</v>
       </c>
-      <c r="B236" t="s">
+      <c r="D236" t="s">
+        <v>706</v>
+      </c>
+      <c r="E236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
         <v>714</v>
       </c>
-      <c r="D236" t="s">
-        <v>707</v>
-      </c>
-      <c r="F236" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237" t="s">
+      <c r="B237" t="s">
         <v>715</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>716</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D237" t="s">
+        <v>706</v>
+      </c>
+      <c r="E237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
         <v>717</v>
       </c>
-      <c r="D237" t="s">
-        <v>707</v>
-      </c>
-      <c r="F237" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238" t="s">
+      <c r="B238" t="s">
         <v>718</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C238" t="s">
         <v>719</v>
       </c>
-      <c r="C238" t="s">
+      <c r="D238" t="s">
+        <v>706</v>
+      </c>
+      <c r="E238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
         <v>720</v>
       </c>
-      <c r="D238" t="s">
-        <v>707</v>
-      </c>
-      <c r="F238" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239" t="s">
+      <c r="B239" t="s">
         <v>721</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" t="s">
         <v>722</v>
       </c>
-      <c r="C239" t="s">
+      <c r="D239" t="s">
+        <v>706</v>
+      </c>
+      <c r="E239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
         <v>723</v>
       </c>
-      <c r="D239" t="s">
-        <v>707</v>
-      </c>
-      <c r="F239" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240" t="s">
+      <c r="B240" t="s">
         <v>724</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>725</v>
       </c>
-      <c r="C240" t="s">
+      <c r="D240" t="s">
+        <v>706</v>
+      </c>
+      <c r="E240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
         <v>726</v>
       </c>
-      <c r="D240" t="s">
-        <v>707</v>
-      </c>
-      <c r="F240" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241" t="s">
+      <c r="B241" t="s">
         <v>727</v>
       </c>
-      <c r="B241" t="s">
+      <c r="D241" t="s">
+        <v>706</v>
+      </c>
+      <c r="E241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
         <v>728</v>
       </c>
-      <c r="D241" t="s">
-        <v>707</v>
-      </c>
-      <c r="F241" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242" t="s">
+      <c r="B242" t="s">
         <v>729</v>
       </c>
-      <c r="B242" t="s">
+      <c r="D242" t="s">
+        <v>706</v>
+      </c>
+      <c r="E242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
         <v>730</v>
       </c>
-      <c r="D242" t="s">
-        <v>707</v>
-      </c>
-      <c r="F242" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243" t="s">
+      <c r="B243" t="s">
         <v>731</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>732</v>
       </c>
-      <c r="C243" t="s">
+      <c r="D243" t="s">
+        <v>706</v>
+      </c>
+      <c r="E243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
         <v>733</v>
       </c>
-      <c r="D243" t="s">
-        <v>707</v>
-      </c>
-      <c r="F243" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244" t="s">
+      <c r="B244" t="s">
         <v>734</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" t="s">
         <v>735</v>
       </c>
-      <c r="C244" t="s">
+      <c r="D244" t="s">
+        <v>706</v>
+      </c>
+      <c r="E244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
         <v>736</v>
       </c>
-      <c r="D244" t="s">
-        <v>707</v>
-      </c>
-      <c r="F244" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245" t="s">
+      <c r="B245" t="s">
         <v>737</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" t="s">
         <v>738</v>
       </c>
-      <c r="C245" t="s">
+      <c r="D245" t="s">
+        <v>706</v>
+      </c>
+      <c r="E245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
         <v>739</v>
       </c>
-      <c r="D245" t="s">
-        <v>707</v>
-      </c>
-      <c r="F245" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246" t="s">
+      <c r="B246" t="s">
         <v>740</v>
       </c>
-      <c r="B246" t="s">
+      <c r="D246" t="s">
+        <v>706</v>
+      </c>
+      <c r="E246" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
         <v>741</v>
       </c>
-      <c r="D246" t="s">
-        <v>707</v>
-      </c>
-      <c r="F246" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247" t="s">
+      <c r="B247" t="s">
         <v>742</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" t="s">
         <v>743</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
+        <v>706</v>
+      </c>
+      <c r="E247" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
         <v>744</v>
       </c>
-      <c r="D247" t="s">
-        <v>707</v>
-      </c>
-      <c r="F247" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248" t="s">
+      <c r="B248" t="s">
         <v>745</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>746</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
+        <v>706</v>
+      </c>
+      <c r="E248" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
         <v>747</v>
       </c>
-      <c r="D248" t="s">
-        <v>707</v>
-      </c>
-      <c r="F248" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249" t="s">
+      <c r="B249" t="s">
         <v>748</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>749</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
+        <v>706</v>
+      </c>
+      <c r="E249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
         <v>750</v>
       </c>
-      <c r="D249" t="s">
-        <v>707</v>
-      </c>
-      <c r="F249" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250" t="s">
+      <c r="B250" t="s">
         <v>751</v>
       </c>
-      <c r="B250" t="s">
+      <c r="C250" t="s">
         <v>752</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
+        <v>706</v>
+      </c>
+      <c r="E250" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
         <v>753</v>
       </c>
-      <c r="D250" t="s">
-        <v>707</v>
-      </c>
-      <c r="F250" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251" t="s">
+      <c r="B251" t="s">
         <v>754</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C251" t="s">
         <v>755</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
+        <v>706</v>
+      </c>
+      <c r="E251" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" t="s">
         <v>756</v>
       </c>
-      <c r="D251" t="s">
-        <v>707</v>
-      </c>
-      <c r="F251" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252" t="s">
+      <c r="B252" t="s">
         <v>757</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C252" t="s">
         <v>758</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>759</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" t="s">
         <v>760</v>
       </c>
-      <c r="F252" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253" t="s">
+      <c r="B253" t="s">
         <v>761</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C253" t="s">
         <v>762</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D253" t="s">
+        <v>759</v>
+      </c>
+      <c r="E253" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" t="s">
         <v>763</v>
       </c>
-      <c r="D253" t="s">
-        <v>760</v>
-      </c>
-      <c r="F253" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254" t="s">
+      <c r="B254" t="s">
         <v>764</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C254" t="s">
         <v>765</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
+        <v>759</v>
+      </c>
+      <c r="E254" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" t="s">
         <v>766</v>
       </c>
-      <c r="D254" t="s">
-        <v>760</v>
-      </c>
-      <c r="F254" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255" t="s">
+      <c r="B255" t="s">
         <v>767</v>
       </c>
-      <c r="B255" t="s">
+      <c r="C255" t="s">
         <v>768</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
+        <v>759</v>
+      </c>
+      <c r="E255" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" t="s">
         <v>769</v>
       </c>
-      <c r="D255" t="s">
-        <v>760</v>
-      </c>
-      <c r="F255" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256" t="s">
+      <c r="B256" t="s">
         <v>770</v>
       </c>
-      <c r="B256" t="s">
+      <c r="C256" t="s">
         <v>771</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
+        <v>759</v>
+      </c>
+      <c r="E256" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" t="s">
         <v>772</v>
       </c>
-      <c r="D256" t="s">
-        <v>760</v>
-      </c>
-      <c r="F256" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257" t="s">
+      <c r="B257" t="s">
         <v>773</v>
       </c>
-      <c r="B257" t="s">
+      <c r="C257" t="s">
         <v>774</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
+        <v>759</v>
+      </c>
+      <c r="E257" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" t="s">
         <v>775</v>
       </c>
-      <c r="D257" t="s">
-        <v>760</v>
-      </c>
-      <c r="F257" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258" t="s">
+      <c r="B258" t="s">
         <v>776</v>
       </c>
-      <c r="B258" t="s">
+      <c r="C258" t="s">
         <v>777</v>
       </c>
-      <c r="C258" t="s">
+      <c r="D258" t="s">
+        <v>759</v>
+      </c>
+      <c r="E258" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" t="s">
         <v>778</v>
       </c>
-      <c r="D258" t="s">
-        <v>760</v>
-      </c>
-      <c r="F258" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259" t="s">
+      <c r="B259" t="s">
         <v>779</v>
       </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
         <v>780</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
+        <v>759</v>
+      </c>
+      <c r="E259" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="s">
         <v>781</v>
       </c>
-      <c r="D259" t="s">
-        <v>760</v>
-      </c>
-      <c r="F259" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260" t="s">
+      <c r="B260" t="s">
         <v>782</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" t="s">
         <v>783</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
+        <v>759</v>
+      </c>
+      <c r="E260" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
         <v>784</v>
       </c>
-      <c r="D260" t="s">
-        <v>760</v>
-      </c>
-      <c r="F260" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261" t="s">
+      <c r="B261" t="s">
         <v>785</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" t="s">
         <v>786</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
+        <v>759</v>
+      </c>
+      <c r="E261" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" t="s">
         <v>787</v>
       </c>
-      <c r="D261" t="s">
-        <v>760</v>
-      </c>
-      <c r="F261" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262" t="s">
+      <c r="B262" t="s">
         <v>788</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" t="s">
         <v>789</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
         <v>790</v>
       </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" t="s">
         <v>791</v>
       </c>
-      <c r="F262" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263" t="s">
+      <c r="B263" t="s">
         <v>792</v>
       </c>
-      <c r="B263" t="s">
+      <c r="C263" t="s">
         <v>793</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>794</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" t="s">
         <v>795</v>
       </c>
-      <c r="F263" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" t="s">
+      <c r="B264" t="s">
         <v>796</v>
       </c>
-      <c r="B264" t="s">
+      <c r="C264" t="s">
         <v>797</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
+        <v>794</v>
+      </c>
+      <c r="E264" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" t="s">
         <v>798</v>
       </c>
-      <c r="D264" t="s">
-        <v>795</v>
-      </c>
-      <c r="F264" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265" t="s">
+      <c r="B265" t="s">
         <v>799</v>
       </c>
-      <c r="B265" t="s">
+      <c r="C265" t="s">
         <v>800</v>
       </c>
-      <c r="C265" t="s">
+      <c r="D265" t="s">
+        <v>794</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" t="s">
         <v>801</v>
       </c>
-      <c r="D265" t="s">
-        <v>795</v>
-      </c>
-      <c r="F265" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266" t="s">
+      <c r="B266" t="s">
         <v>802</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" t="s">
         <v>803</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D266" t="s">
+        <v>794</v>
+      </c>
+      <c r="E266" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" t="s">
         <v>804</v>
       </c>
-      <c r="D266" t="s">
-        <v>795</v>
-      </c>
-      <c r="F266" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267" t="s">
+      <c r="B267" t="s">
         <v>805</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C267" t="s">
         <v>806</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
+        <v>794</v>
+      </c>
+      <c r="E267" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" t="s">
         <v>807</v>
       </c>
-      <c r="D267" t="s">
-        <v>795</v>
-      </c>
-      <c r="F267" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
-      <c r="A268" t="s">
+      <c r="B268" t="s">
         <v>808</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" t="s">
         <v>809</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
+        <v>794</v>
+      </c>
+      <c r="E268" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" t="s">
         <v>810</v>
       </c>
-      <c r="D268" t="s">
-        <v>795</v>
-      </c>
-      <c r="F268" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
-      <c r="A269" t="s">
+      <c r="B269" t="s">
         <v>811</v>
       </c>
-      <c r="B269" t="s">
+      <c r="D269" t="s">
         <v>812</v>
       </c>
-      <c r="D269" t="s">
+      <c r="E269" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" t="s">
         <v>813</v>
       </c>
-      <c r="F269" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
-      <c r="A270" t="s">
+      <c r="B270" t="s">
         <v>814</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C270" t="s">
         <v>815</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
         <v>816</v>
       </c>
-      <c r="D270" t="s">
+      <c r="E270" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
         <v>817</v>
       </c>
-      <c r="F270" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
-      <c r="A271" t="s">
+      <c r="B271" t="s">
         <v>818</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C271" t="s">
         <v>819</v>
       </c>
-      <c r="C271" t="s">
+      <c r="D271" t="s">
+        <v>816</v>
+      </c>
+      <c r="E271" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
         <v>820</v>
       </c>
-      <c r="D271" t="s">
-        <v>817</v>
-      </c>
-      <c r="F271" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
-      <c r="A272" t="s">
+      <c r="B272" t="s">
         <v>821</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>822</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
+        <v>816</v>
+      </c>
+      <c r="E272" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273" t="s">
         <v>823</v>
       </c>
-      <c r="D272" t="s">
-        <v>817</v>
-      </c>
-      <c r="F272" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
-      <c r="A273" t="s">
+      <c r="B273" t="s">
         <v>824</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C273" t="s">
         <v>825</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" t="s">
+        <v>816</v>
+      </c>
+      <c r="E273" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274" t="s">
         <v>826</v>
       </c>
-      <c r="D273" t="s">
-        <v>817</v>
-      </c>
-      <c r="F273" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8">
-      <c r="A274" t="s">
+      <c r="B274" t="s">
         <v>827</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C274" t="s">
         <v>828</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
+        <v>816</v>
+      </c>
+      <c r="E274" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275" t="s">
         <v>829</v>
       </c>
-      <c r="D274" t="s">
-        <v>817</v>
-      </c>
-      <c r="F274" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8">
-      <c r="A275" t="s">
+      <c r="B275" t="s">
         <v>830</v>
       </c>
-      <c r="B275" t="s">
+      <c r="D275" t="s">
+        <v>816</v>
+      </c>
+      <c r="E275" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276" t="s">
         <v>831</v>
       </c>
-      <c r="D275" t="s">
-        <v>817</v>
-      </c>
-      <c r="F275" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8">
-      <c r="A276" t="s">
+      <c r="B276" t="s">
         <v>832</v>
       </c>
-      <c r="B276" t="s">
+      <c r="C276" t="s">
         <v>833</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
+        <v>816</v>
+      </c>
+      <c r="E276" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277" t="s">
         <v>834</v>
       </c>
-      <c r="D276" t="s">
-        <v>817</v>
-      </c>
-      <c r="F276" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8">
-      <c r="A277" t="s">
+      <c r="B277" t="s">
         <v>835</v>
       </c>
-      <c r="B277" t="s">
+      <c r="D277" t="s">
         <v>836</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
+        <v>11</v>
+      </c>
+      <c r="F277" t="s">
         <v>837</v>
       </c>
-      <c r="F277" t="s">
-        <v>12</v>
-      </c>
       <c r="G277" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278" t="s">
         <v>838</v>
       </c>
-      <c r="H277" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8">
-      <c r="A278" t="s">
+      <c r="B278" t="s">
         <v>839</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>840</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
+        <v>836</v>
+      </c>
+      <c r="E278" t="s">
+        <v>11</v>
+      </c>
+      <c r="F278" t="s">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279" t="s">
         <v>841</v>
       </c>
-      <c r="D278" t="s">
+      <c r="B279" t="s">
+        <v>842</v>
+      </c>
+      <c r="C279" t="s">
+        <v>843</v>
+      </c>
+      <c r="D279" t="s">
+        <v>836</v>
+      </c>
+      <c r="E279" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280" t="s">
+        <v>844</v>
+      </c>
+      <c r="B280" t="s">
+        <v>845</v>
+      </c>
+      <c r="C280" t="s">
+        <v>846</v>
+      </c>
+      <c r="D280" t="s">
+        <v>836</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281" t="s">
+        <v>847</v>
+      </c>
+      <c r="B281" t="s">
+        <v>848</v>
+      </c>
+      <c r="C281" t="s">
+        <v>849</v>
+      </c>
+      <c r="D281" t="s">
+        <v>836</v>
+      </c>
+      <c r="E281" t="s">
+        <v>11</v>
+      </c>
+      <c r="F281" t="s">
+        <v>28</v>
+      </c>
+      <c r="G281" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282" t="s">
+        <v>850</v>
+      </c>
+      <c r="B282" t="s">
+        <v>851</v>
+      </c>
+      <c r="C282" t="s">
+        <v>852</v>
+      </c>
+      <c r="D282" t="s">
+        <v>836</v>
+      </c>
+      <c r="E282" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283" t="s">
+        <v>853</v>
+      </c>
+      <c r="B283" t="s">
+        <v>848</v>
+      </c>
+      <c r="C283" t="s">
+        <v>854</v>
+      </c>
+      <c r="D283" t="s">
+        <v>836</v>
+      </c>
+      <c r="E283" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284" t="s">
+        <v>855</v>
+      </c>
+      <c r="B284" t="s">
+        <v>856</v>
+      </c>
+      <c r="C284" t="s">
+        <v>857</v>
+      </c>
+      <c r="D284" t="s">
+        <v>836</v>
+      </c>
+      <c r="E284" t="s">
+        <v>11</v>
+      </c>
+      <c r="F284" t="s">
         <v>837</v>
       </c>
-      <c r="F278" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278" t="s">
-        <v>29</v>
-      </c>
-      <c r="H278" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8">
-      <c r="A279" t="s">
-        <v>842</v>
-      </c>
-      <c r="B279" t="s">
-        <v>843</v>
-      </c>
-      <c r="C279" t="s">
-        <v>844</v>
-      </c>
-      <c r="D279" t="s">
+      <c r="G284" t="s">
         <v>837</v>
       </c>
-      <c r="F279" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8">
-      <c r="A280" t="s">
-        <v>845</v>
-      </c>
-      <c r="B280" t="s">
-        <v>846</v>
-      </c>
-      <c r="C280" t="s">
-        <v>847</v>
-      </c>
-      <c r="D280" t="s">
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285" t="s">
+        <v>858</v>
+      </c>
+      <c r="B285" t="s">
+        <v>859</v>
+      </c>
+      <c r="C285" t="s">
+        <v>860</v>
+      </c>
+      <c r="D285" t="s">
+        <v>836</v>
+      </c>
+      <c r="E285" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286" t="s">
+        <v>861</v>
+      </c>
+      <c r="B286" t="s">
+        <v>862</v>
+      </c>
+      <c r="C286" t="s">
+        <v>863</v>
+      </c>
+      <c r="D286" t="s">
+        <v>836</v>
+      </c>
+      <c r="E286" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287" t="s">
+        <v>864</v>
+      </c>
+      <c r="B287" t="s">
+        <v>865</v>
+      </c>
+      <c r="C287" t="s">
+        <v>866</v>
+      </c>
+      <c r="D287" t="s">
+        <v>836</v>
+      </c>
+      <c r="E287" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288" t="s">
+        <v>867</v>
+      </c>
+      <c r="B288" t="s">
+        <v>868</v>
+      </c>
+      <c r="C288" t="s">
+        <v>869</v>
+      </c>
+      <c r="D288" t="s">
+        <v>836</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289" t="s">
+        <v>870</v>
+      </c>
+      <c r="B289" t="s">
+        <v>871</v>
+      </c>
+      <c r="C289" t="s">
+        <v>872</v>
+      </c>
+      <c r="D289" t="s">
+        <v>836</v>
+      </c>
+      <c r="E289" t="s">
+        <v>11</v>
+      </c>
+      <c r="F289" t="s">
         <v>837</v>
       </c>
-      <c r="F280" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8">
-      <c r="A281" t="s">
-        <v>848</v>
-      </c>
-      <c r="B281" t="s">
-        <v>849</v>
-      </c>
-      <c r="C281" t="s">
-        <v>850</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="G289" t="s">
         <v>837</v>
       </c>
-      <c r="F281" t="s">
-        <v>12</v>
-      </c>
-      <c r="G281" t="s">
-        <v>29</v>
-      </c>
-      <c r="H281" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8">
-      <c r="A282" t="s">
-        <v>851</v>
-      </c>
-      <c r="B282" t="s">
-        <v>852</v>
-      </c>
-      <c r="C282" t="s">
-        <v>853</v>
-      </c>
-      <c r="D282" t="s">
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290" t="s">
+        <v>873</v>
+      </c>
+      <c r="B290" t="s">
+        <v>874</v>
+      </c>
+      <c r="C290" t="s">
+        <v>875</v>
+      </c>
+      <c r="D290" t="s">
+        <v>836</v>
+      </c>
+      <c r="E290" t="s">
+        <v>11</v>
+      </c>
+      <c r="F290" t="s">
         <v>837</v>
       </c>
-      <c r="F282" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8">
-      <c r="A283" t="s">
-        <v>854</v>
-      </c>
-      <c r="B283" t="s">
-        <v>849</v>
-      </c>
-      <c r="C283" t="s">
-        <v>855</v>
-      </c>
-      <c r="D283" t="s">
+      <c r="G290" t="s">
         <v>837</v>
       </c>
-      <c r="F283" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8">
-      <c r="A284" t="s">
-        <v>856</v>
-      </c>
-      <c r="B284" t="s">
-        <v>857</v>
-      </c>
-      <c r="C284" t="s">
-        <v>858</v>
-      </c>
-      <c r="D284" t="s">
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" t="s">
+        <v>876</v>
+      </c>
+      <c r="B291" t="s">
+        <v>877</v>
+      </c>
+      <c r="C291" t="s">
+        <v>878</v>
+      </c>
+      <c r="D291" t="s">
+        <v>879</v>
+      </c>
+      <c r="E291" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" t="s">
+        <v>880</v>
+      </c>
+      <c r="B292" t="s">
+        <v>881</v>
+      </c>
+      <c r="C292" t="s">
+        <v>882</v>
+      </c>
+      <c r="D292" t="s">
+        <v>883</v>
+      </c>
+      <c r="E292" t="s">
+        <v>11</v>
+      </c>
+      <c r="F292" t="s">
         <v>837</v>
       </c>
-      <c r="F284" t="s">
-        <v>12</v>
-      </c>
-      <c r="G284" t="s">
-        <v>838</v>
-      </c>
-      <c r="H284" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
-      <c r="A285" t="s">
-        <v>859</v>
-      </c>
-      <c r="B285" t="s">
-        <v>860</v>
-      </c>
-      <c r="C285" t="s">
-        <v>861</v>
-      </c>
-      <c r="D285" t="s">
+      <c r="G292" t="s">
         <v>837</v>
       </c>
-      <c r="F285" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8">
-      <c r="A286" t="s">
-        <v>862</v>
-      </c>
-      <c r="B286" t="s">
-        <v>863</v>
-      </c>
-      <c r="C286" t="s">
-        <v>864</v>
-      </c>
-      <c r="D286" t="s">
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>884</v>
+      </c>
+      <c r="B293" t="s">
+        <v>885</v>
+      </c>
+      <c r="C293" t="s">
+        <v>886</v>
+      </c>
+      <c r="D293" t="s">
+        <v>887</v>
+      </c>
+      <c r="E293" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>888</v>
+      </c>
+      <c r="B294" t="s">
+        <v>889</v>
+      </c>
+      <c r="C294" t="s">
+        <v>890</v>
+      </c>
+      <c r="D294" t="s">
+        <v>887</v>
+      </c>
+      <c r="E294" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>891</v>
+      </c>
+      <c r="B295" t="s">
+        <v>892</v>
+      </c>
+      <c r="C295" t="s">
+        <v>893</v>
+      </c>
+      <c r="D295" t="s">
+        <v>894</v>
+      </c>
+      <c r="E295" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>895</v>
+      </c>
+      <c r="B296" t="s">
+        <v>896</v>
+      </c>
+      <c r="D296" t="s">
+        <v>894</v>
+      </c>
+      <c r="E296" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>897</v>
+      </c>
+      <c r="B297" t="s">
+        <v>898</v>
+      </c>
+      <c r="C297" t="s">
+        <v>899</v>
+      </c>
+      <c r="D297" t="s">
+        <v>894</v>
+      </c>
+      <c r="E297" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>900</v>
+      </c>
+      <c r="B298" t="s">
+        <v>901</v>
+      </c>
+      <c r="D298" t="s">
+        <v>894</v>
+      </c>
+      <c r="E298" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>902</v>
+      </c>
+      <c r="B299" t="s">
+        <v>903</v>
+      </c>
+      <c r="C299" t="s">
+        <v>904</v>
+      </c>
+      <c r="D299" t="s">
+        <v>894</v>
+      </c>
+      <c r="E299" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>905</v>
+      </c>
+      <c r="B300" t="s">
+        <v>906</v>
+      </c>
+      <c r="C300" t="s">
+        <v>907</v>
+      </c>
+      <c r="D300" t="s">
+        <v>894</v>
+      </c>
+      <c r="E300" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>908</v>
+      </c>
+      <c r="B301" t="s">
+        <v>909</v>
+      </c>
+      <c r="C301" t="s">
+        <v>910</v>
+      </c>
+      <c r="D301" t="s">
+        <v>894</v>
+      </c>
+      <c r="E301" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302" t="s">
+        <v>911</v>
+      </c>
+      <c r="B302" t="s">
+        <v>912</v>
+      </c>
+      <c r="C302" t="s">
+        <v>913</v>
+      </c>
+      <c r="D302" t="s">
+        <v>914</v>
+      </c>
+      <c r="E302" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>915</v>
+      </c>
+      <c r="B303" t="s">
+        <v>916</v>
+      </c>
+      <c r="C303" t="s">
+        <v>917</v>
+      </c>
+      <c r="D303" t="s">
+        <v>914</v>
+      </c>
+      <c r="E303" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>918</v>
+      </c>
+      <c r="B304" t="s">
+        <v>919</v>
+      </c>
+      <c r="C304" t="s">
+        <v>920</v>
+      </c>
+      <c r="D304" t="s">
+        <v>914</v>
+      </c>
+      <c r="E304" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" t="s">
+        <v>921</v>
+      </c>
+      <c r="B305" t="s">
+        <v>922</v>
+      </c>
+      <c r="C305" t="s">
+        <v>923</v>
+      </c>
+      <c r="D305" t="s">
+        <v>914</v>
+      </c>
+      <c r="E305" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" t="s">
+        <v>924</v>
+      </c>
+      <c r="B306" t="s">
+        <v>925</v>
+      </c>
+      <c r="C306" t="s">
+        <v>926</v>
+      </c>
+      <c r="D306" t="s">
+        <v>914</v>
+      </c>
+      <c r="E306" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" t="s">
+        <v>927</v>
+      </c>
+      <c r="B307" t="s">
+        <v>928</v>
+      </c>
+      <c r="C307" t="s">
+        <v>929</v>
+      </c>
+      <c r="D307" t="s">
+        <v>930</v>
+      </c>
+      <c r="E307" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" t="s">
+        <v>931</v>
+      </c>
+      <c r="B308" t="s">
+        <v>932</v>
+      </c>
+      <c r="C308" t="s">
+        <v>933</v>
+      </c>
+      <c r="D308" t="s">
+        <v>934</v>
+      </c>
+      <c r="E308" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" t="s">
+        <v>935</v>
+      </c>
+      <c r="B309" t="s">
+        <v>936</v>
+      </c>
+      <c r="C309" t="s">
+        <v>937</v>
+      </c>
+      <c r="D309" t="s">
+        <v>934</v>
+      </c>
+      <c r="E309" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" t="s">
+        <v>938</v>
+      </c>
+      <c r="B310" t="s">
+        <v>939</v>
+      </c>
+      <c r="D310" t="s">
+        <v>940</v>
+      </c>
+      <c r="E310" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" t="s">
+        <v>941</v>
+      </c>
+      <c r="B311" t="s">
+        <v>942</v>
+      </c>
+      <c r="C311" t="s">
+        <v>943</v>
+      </c>
+      <c r="D311" t="s">
+        <v>944</v>
+      </c>
+      <c r="E311" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" t="s">
+        <v>945</v>
+      </c>
+      <c r="B312" t="s">
+        <v>946</v>
+      </c>
+      <c r="D312" t="s">
+        <v>944</v>
+      </c>
+      <c r="E312" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" t="s">
+        <v>947</v>
+      </c>
+      <c r="B313" t="s">
+        <v>948</v>
+      </c>
+      <c r="C313" t="s">
+        <v>949</v>
+      </c>
+      <c r="D313" t="s">
+        <v>944</v>
+      </c>
+      <c r="E313" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" t="s">
+        <v>950</v>
+      </c>
+      <c r="B314" t="s">
+        <v>951</v>
+      </c>
+      <c r="C314" t="s">
+        <v>952</v>
+      </c>
+      <c r="D314" t="s">
+        <v>953</v>
+      </c>
+      <c r="E314" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" t="s">
+        <v>954</v>
+      </c>
+      <c r="B315" t="s">
+        <v>955</v>
+      </c>
+      <c r="C315" t="s">
+        <v>956</v>
+      </c>
+      <c r="D315" t="s">
+        <v>953</v>
+      </c>
+      <c r="E315" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" t="s">
+        <v>957</v>
+      </c>
+      <c r="B316" t="s">
+        <v>958</v>
+      </c>
+      <c r="C316" t="s">
+        <v>959</v>
+      </c>
+      <c r="D316" t="s">
+        <v>953</v>
+      </c>
+      <c r="E316" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" t="s">
+        <v>960</v>
+      </c>
+      <c r="B317" t="s">
+        <v>961</v>
+      </c>
+      <c r="C317" t="s">
+        <v>962</v>
+      </c>
+      <c r="D317" t="s">
+        <v>953</v>
+      </c>
+      <c r="E317" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" t="s">
+        <v>963</v>
+      </c>
+      <c r="B318" t="s">
+        <v>964</v>
+      </c>
+      <c r="C318" t="s">
+        <v>965</v>
+      </c>
+      <c r="D318" t="s">
+        <v>953</v>
+      </c>
+      <c r="E318" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" t="s">
+        <v>966</v>
+      </c>
+      <c r="B319" t="s">
+        <v>967</v>
+      </c>
+      <c r="C319" t="s">
+        <v>968</v>
+      </c>
+      <c r="D319" t="s">
+        <v>953</v>
+      </c>
+      <c r="E319" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" t="s">
+        <v>969</v>
+      </c>
+      <c r="B320" t="s">
+        <v>970</v>
+      </c>
+      <c r="C320" t="s">
+        <v>971</v>
+      </c>
+      <c r="D320" t="s">
+        <v>953</v>
+      </c>
+      <c r="E320" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7">
+      <c r="A321" t="s">
+        <v>972</v>
+      </c>
+      <c r="B321" t="s">
+        <v>973</v>
+      </c>
+      <c r="C321" t="s">
+        <v>974</v>
+      </c>
+      <c r="D321" t="s">
+        <v>953</v>
+      </c>
+      <c r="E321" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7">
+      <c r="A322" t="s">
+        <v>975</v>
+      </c>
+      <c r="B322" t="s">
+        <v>976</v>
+      </c>
+      <c r="C322" t="s">
+        <v>977</v>
+      </c>
+      <c r="D322" t="s">
+        <v>953</v>
+      </c>
+      <c r="E322" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323" t="s">
+        <v>978</v>
+      </c>
+      <c r="B323" t="s">
+        <v>979</v>
+      </c>
+      <c r="C323" t="s">
+        <v>980</v>
+      </c>
+      <c r="D323" t="s">
+        <v>981</v>
+      </c>
+      <c r="E323" t="s">
+        <v>11</v>
+      </c>
+      <c r="F323" t="s">
         <v>837</v>
       </c>
-      <c r="F286" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8">
-      <c r="A287" t="s">
-        <v>865</v>
-      </c>
-      <c r="B287" t="s">
-        <v>866</v>
-      </c>
-      <c r="C287" t="s">
-        <v>867</v>
-      </c>
-      <c r="D287" t="s">
+      <c r="G323" t="s">
         <v>837</v>
       </c>
-      <c r="F287" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8">
-      <c r="A288" t="s">
-        <v>868</v>
-      </c>
-      <c r="B288" t="s">
-        <v>869</v>
-      </c>
-      <c r="C288" t="s">
-        <v>870</v>
-      </c>
-      <c r="D288" t="s">
-        <v>837</v>
-      </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8">
-      <c r="A289" t="s">
-        <v>871</v>
-      </c>
-      <c r="B289" t="s">
-        <v>872</v>
-      </c>
-      <c r="C289" t="s">
-        <v>873</v>
-      </c>
-      <c r="D289" t="s">
-        <v>837</v>
-      </c>
-      <c r="F289" t="s">
-        <v>12</v>
-      </c>
-      <c r="G289" t="s">
-        <v>838</v>
-      </c>
-      <c r="H289" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8">
-      <c r="A290" t="s">
-        <v>874</v>
-      </c>
-      <c r="B290" t="s">
-        <v>875</v>
-      </c>
-      <c r="C290" t="s">
-        <v>876</v>
-      </c>
-      <c r="D290" t="s">
-        <v>837</v>
-      </c>
-      <c r="F290" t="s">
-        <v>12</v>
-      </c>
-      <c r="G290" t="s">
-        <v>838</v>
-      </c>
-      <c r="H290" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8">
-      <c r="A291" t="s">
-        <v>877</v>
-      </c>
-      <c r="B291" t="s">
-        <v>878</v>
-      </c>
-      <c r="C291" t="s">
-        <v>879</v>
-      </c>
-      <c r="D291" t="s">
-        <v>880</v>
-      </c>
-      <c r="F291" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8">
-      <c r="A292" t="s">
-        <v>881</v>
-      </c>
-      <c r="B292" t="s">
-        <v>882</v>
-      </c>
-      <c r="C292" t="s">
-        <v>883</v>
-      </c>
-      <c r="D292" t="s">
-        <v>884</v>
-      </c>
-      <c r="F292" t="s">
-        <v>12</v>
-      </c>
-      <c r="G292" t="s">
-        <v>838</v>
-      </c>
-      <c r="H292" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8">
-      <c r="A293" t="s">
-        <v>885</v>
-      </c>
-      <c r="B293" t="s">
-        <v>886</v>
-      </c>
-      <c r="C293" t="s">
-        <v>887</v>
-      </c>
-      <c r="D293" t="s">
-        <v>888</v>
-      </c>
-      <c r="F293" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8">
-      <c r="A294" t="s">
-        <v>889</v>
-      </c>
-      <c r="B294" t="s">
-        <v>890</v>
-      </c>
-      <c r="C294" t="s">
-        <v>891</v>
-      </c>
-      <c r="D294" t="s">
-        <v>888</v>
-      </c>
-      <c r="F294" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8">
-      <c r="A295" t="s">
-        <v>892</v>
-      </c>
-      <c r="B295" t="s">
-        <v>893</v>
-      </c>
-      <c r="C295" t="s">
-        <v>894</v>
-      </c>
-      <c r="D295" t="s">
-        <v>895</v>
-      </c>
-      <c r="F295" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8">
-      <c r="A296" t="s">
-        <v>896</v>
-      </c>
-      <c r="B296" t="s">
-        <v>897</v>
-      </c>
-      <c r="D296" t="s">
-        <v>895</v>
-      </c>
-      <c r="F296" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8">
-      <c r="A297" t="s">
-        <v>898</v>
-      </c>
-      <c r="B297" t="s">
-        <v>899</v>
-      </c>
-      <c r="C297" t="s">
-        <v>900</v>
-      </c>
-      <c r="D297" t="s">
-        <v>895</v>
-      </c>
-      <c r="F297" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8">
-      <c r="A298" t="s">
-        <v>901</v>
-      </c>
-      <c r="B298" t="s">
-        <v>902</v>
-      </c>
-      <c r="D298" t="s">
-        <v>895</v>
-      </c>
-      <c r="F298" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8">
-      <c r="A299" t="s">
-        <v>903</v>
-      </c>
-      <c r="B299" t="s">
-        <v>904</v>
-      </c>
-      <c r="C299" t="s">
-        <v>905</v>
-      </c>
-      <c r="D299" t="s">
-        <v>895</v>
-      </c>
-      <c r="F299" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8">
-      <c r="A300" t="s">
-        <v>906</v>
-      </c>
-      <c r="B300" t="s">
-        <v>907</v>
-      </c>
-      <c r="C300" t="s">
-        <v>908</v>
-      </c>
-      <c r="D300" t="s">
-        <v>895</v>
-      </c>
-      <c r="F300" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8">
-      <c r="A301" t="s">
-        <v>909</v>
-      </c>
-      <c r="B301" t="s">
-        <v>910</v>
-      </c>
-      <c r="C301" t="s">
-        <v>911</v>
-      </c>
-      <c r="D301" t="s">
-        <v>895</v>
-      </c>
-      <c r="F301" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
-      <c r="A302" t="s">
-        <v>912</v>
-      </c>
-      <c r="B302" t="s">
-        <v>913</v>
-      </c>
-      <c r="C302" t="s">
-        <v>914</v>
-      </c>
-      <c r="D302" t="s">
-        <v>915</v>
-      </c>
-      <c r="F302" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8">
-      <c r="A303" t="s">
-        <v>916</v>
-      </c>
-      <c r="B303" t="s">
-        <v>917</v>
-      </c>
-      <c r="C303" t="s">
-        <v>918</v>
-      </c>
-      <c r="D303" t="s">
-        <v>915</v>
-      </c>
-      <c r="F303" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8">
-      <c r="A304" t="s">
-        <v>919</v>
-      </c>
-      <c r="B304" t="s">
-        <v>920</v>
-      </c>
-      <c r="C304" t="s">
-        <v>921</v>
-      </c>
-      <c r="D304" t="s">
-        <v>915</v>
-      </c>
-      <c r="F304" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
-      <c r="A305" t="s">
-        <v>922</v>
-      </c>
-      <c r="B305" t="s">
-        <v>923</v>
-      </c>
-      <c r="C305" t="s">
-        <v>924</v>
-      </c>
-      <c r="D305" t="s">
-        <v>915</v>
-      </c>
-      <c r="F305" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
-      <c r="A306" t="s">
-        <v>925</v>
-      </c>
-      <c r="B306" t="s">
-        <v>926</v>
-      </c>
-      <c r="C306" t="s">
-        <v>927</v>
-      </c>
-      <c r="D306" t="s">
-        <v>915</v>
-      </c>
-      <c r="F306" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
-      <c r="A307" t="s">
-        <v>928</v>
-      </c>
-      <c r="B307" t="s">
-        <v>929</v>
-      </c>
-      <c r="C307" t="s">
-        <v>930</v>
-      </c>
-      <c r="D307" t="s">
-        <v>931</v>
-      </c>
-      <c r="F307" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
-      <c r="A308" t="s">
-        <v>932</v>
-      </c>
-      <c r="B308" t="s">
-        <v>933</v>
-      </c>
-      <c r="C308" t="s">
-        <v>934</v>
-      </c>
-      <c r="D308" t="s">
-        <v>935</v>
-      </c>
-      <c r="F308" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309" t="s">
-        <v>936</v>
-      </c>
-      <c r="B309" t="s">
-        <v>937</v>
-      </c>
-      <c r="C309" t="s">
-        <v>938</v>
-      </c>
-      <c r="D309" t="s">
-        <v>935</v>
-      </c>
-      <c r="F309" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
-      <c r="A310" t="s">
-        <v>939</v>
-      </c>
-      <c r="B310" t="s">
-        <v>940</v>
-      </c>
-      <c r="D310" t="s">
-        <v>941</v>
-      </c>
-      <c r="F310" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
-      <c r="A311" t="s">
-        <v>942</v>
-      </c>
-      <c r="B311" t="s">
-        <v>943</v>
-      </c>
-      <c r="C311" t="s">
-        <v>944</v>
-      </c>
-      <c r="D311" t="s">
-        <v>945</v>
-      </c>
-      <c r="F311" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
-      <c r="A312" t="s">
-        <v>946</v>
-      </c>
-      <c r="B312" t="s">
-        <v>947</v>
-      </c>
-      <c r="D312" t="s">
-        <v>945</v>
-      </c>
-      <c r="F312" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
-      <c r="A313" t="s">
-        <v>948</v>
-      </c>
-      <c r="B313" t="s">
-        <v>949</v>
-      </c>
-      <c r="C313" t="s">
-        <v>950</v>
-      </c>
-      <c r="D313" t="s">
-        <v>945</v>
-      </c>
-      <c r="F313" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
-      <c r="A314" t="s">
-        <v>951</v>
-      </c>
-      <c r="B314" t="s">
-        <v>952</v>
-      </c>
-      <c r="C314" t="s">
-        <v>953</v>
-      </c>
-      <c r="D314" t="s">
-        <v>954</v>
-      </c>
-      <c r="F314" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
-      <c r="A315" t="s">
-        <v>955</v>
-      </c>
-      <c r="B315" t="s">
-        <v>956</v>
-      </c>
-      <c r="C315" t="s">
-        <v>957</v>
-      </c>
-      <c r="D315" t="s">
-        <v>954</v>
-      </c>
-      <c r="F315" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
-      <c r="A316" t="s">
-        <v>958</v>
-      </c>
-      <c r="B316" t="s">
-        <v>959</v>
-      </c>
-      <c r="C316" t="s">
-        <v>960</v>
-      </c>
-      <c r="D316" t="s">
-        <v>954</v>
-      </c>
-      <c r="F316" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6">
-      <c r="A317" t="s">
-        <v>961</v>
-      </c>
-      <c r="B317" t="s">
-        <v>962</v>
-      </c>
-      <c r="C317" t="s">
-        <v>963</v>
-      </c>
-      <c r="D317" t="s">
-        <v>954</v>
-      </c>
-      <c r="F317" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6">
-      <c r="A318" t="s">
-        <v>964</v>
-      </c>
-      <c r="B318" t="s">
-        <v>965</v>
-      </c>
-      <c r="C318" t="s">
-        <v>966</v>
-      </c>
-      <c r="D318" t="s">
-        <v>954</v>
-      </c>
-      <c r="F318" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
-      <c r="A319" t="s">
-        <v>967</v>
-      </c>
-      <c r="B319" t="s">
-        <v>968</v>
-      </c>
-      <c r="C319" t="s">
-        <v>969</v>
-      </c>
-      <c r="D319" t="s">
-        <v>954</v>
-      </c>
-      <c r="F319" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
-      <c r="A320" t="s">
-        <v>970</v>
-      </c>
-      <c r="B320" t="s">
-        <v>971</v>
-      </c>
-      <c r="C320" t="s">
-        <v>972</v>
-      </c>
-      <c r="D320" t="s">
-        <v>954</v>
-      </c>
-      <c r="F320" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8">
-      <c r="A321" t="s">
-        <v>973</v>
-      </c>
-      <c r="B321" t="s">
-        <v>974</v>
-      </c>
-      <c r="C321" t="s">
-        <v>975</v>
-      </c>
-      <c r="D321" t="s">
-        <v>954</v>
-      </c>
-      <c r="F321" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8">
-      <c r="A322" t="s">
-        <v>976</v>
-      </c>
-      <c r="B322" t="s">
-        <v>977</v>
-      </c>
-      <c r="C322" t="s">
-        <v>978</v>
-      </c>
-      <c r="D322" t="s">
-        <v>954</v>
-      </c>
-      <c r="F322" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8">
-      <c r="A323" t="s">
-        <v>979</v>
-      </c>
-      <c r="B323" t="s">
-        <v>980</v>
-      </c>
-      <c r="C323" t="s">
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324" t="s">
+        <v>982</v>
+      </c>
+      <c r="B324" t="s">
+        <v>983</v>
+      </c>
+      <c r="C324" t="s">
+        <v>984</v>
+      </c>
+      <c r="D324" t="s">
         <v>981</v>
       </c>
-      <c r="D323" t="s">
-        <v>982</v>
-      </c>
-      <c r="F323" t="s">
-        <v>12</v>
-      </c>
-      <c r="G323" t="s">
-        <v>838</v>
-      </c>
-      <c r="H323" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8">
-      <c r="A324" t="s">
-        <v>983</v>
-      </c>
-      <c r="B324" t="s">
-        <v>984</v>
-      </c>
-      <c r="C324" t="s">
-        <v>985</v>
-      </c>
-      <c r="D324" t="s">
-        <v>982</v>
-      </c>
-      <c r="F324" t="s">
-        <v>12</v>
+      <c r="E324" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="984">
   <si>
     <t>code</t>
   </si>
@@ -31,10 +31,7 @@
     <t>status</t>
   </si>
   <si>
-    <t>budget_alignment_guidance</t>
-  </si>
-  <si>
-    <t>{http://iatistandard.org/activity-standard/overview/country-budget-alignment/}status</t>
+    <t>budget-alignment:status</t>
   </si>
   <si>
     <t>11110</t>
@@ -3300,10 +3297,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:F324"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3322,5541 +3319,5475 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>47</v>
       </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>49</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>51</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>54</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>55</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>56</v>
       </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
         <v>58</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="D18" t="s">
-        <v>64</v>
-      </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
         <v>68</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>69</v>
       </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
         <v>71</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
         <v>74</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>75</v>
       </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>79</v>
       </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
         <v>81</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>82</v>
       </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
         <v>84</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>85</v>
       </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
         <v>87</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>88</v>
       </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
         <v>90</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>91</v>
       </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
         <v>93</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>94</v>
       </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>97</v>
       </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
         <v>99</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>100</v>
       </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>103</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>104</v>
       </c>
-      <c r="D31" t="s">
-        <v>105</v>
-      </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" t="s">
         <v>106</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
         <v>109</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>110</v>
       </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s">
         <v>112</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>113</v>
       </c>
-      <c r="C34" t="s">
-        <v>114</v>
-      </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" t="s">
         <v>115</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>116</v>
       </c>
-      <c r="C35" t="s">
-        <v>117</v>
-      </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s">
         <v>118</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>119</v>
       </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
         <v>121</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>122</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>123</v>
       </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" t="s">
         <v>125</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>126</v>
       </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
         <v>128</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>129</v>
       </c>
-      <c r="C39" t="s">
-        <v>130</v>
-      </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" t="s">
         <v>131</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>132</v>
       </c>
-      <c r="C40" t="s">
-        <v>133</v>
-      </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" t="s">
         <v>134</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>135</v>
       </c>
-      <c r="C41" t="s">
-        <v>136</v>
-      </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" t="s">
         <v>137</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>138</v>
       </c>
-      <c r="C42" t="s">
-        <v>139</v>
-      </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" t="s">
         <v>140</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>141</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>142</v>
       </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
         <v>144</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>145</v>
       </c>
-      <c r="C44" t="s">
-        <v>146</v>
-      </c>
       <c r="D44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
         <v>147</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>148</v>
       </c>
-      <c r="C45" t="s">
-        <v>149</v>
-      </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
         <v>150</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>151</v>
       </c>
-      <c r="C46" t="s">
-        <v>152</v>
-      </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
         <v>153</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>154</v>
       </c>
-      <c r="C47" t="s">
-        <v>155</v>
-      </c>
       <c r="D47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
         <v>156</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>157</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
         <v>158</v>
       </c>
-      <c r="D48" t="s">
-        <v>143</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>159</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>160</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
         <v>161</v>
       </c>
-      <c r="D49" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>162</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>163</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
         <v>164</v>
       </c>
-      <c r="D50" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>165</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>166</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
         <v>167</v>
       </c>
-      <c r="D51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>168</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>169</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
         <v>170</v>
       </c>
-      <c r="D52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>171</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>172</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
         <v>173</v>
       </c>
-      <c r="D53" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>174</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>175</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>176</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
         <v>177</v>
       </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>178</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>179</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
         <v>180</v>
       </c>
-      <c r="D55" t="s">
-        <v>177</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>28</v>
-      </c>
-      <c r="G55" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>181</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>182</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>176</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
         <v>183</v>
       </c>
-      <c r="D56" t="s">
-        <v>177</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>184</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>185</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
+        <v>176</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
         <v>186</v>
       </c>
-      <c r="D57" t="s">
-        <v>177</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>187</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>188</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
+        <v>176</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
         <v>189</v>
       </c>
-      <c r="D58" t="s">
-        <v>177</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>190</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>191</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>176</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
         <v>192</v>
       </c>
-      <c r="D59" t="s">
-        <v>177</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>193</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>194</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
         <v>195</v>
       </c>
-      <c r="D60" t="s">
-        <v>177</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>196</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>197</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
         <v>198</v>
       </c>
-      <c r="D61" t="s">
-        <v>177</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>199</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>200</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
         <v>201</v>
       </c>
-      <c r="D62" t="s">
-        <v>177</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>202</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>203</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63" t="s">
         <v>204</v>
       </c>
-      <c r="D63" t="s">
-        <v>177</v>
-      </c>
-      <c r="E63" t="s">
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>206</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>207</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
         <v>208</v>
       </c>
-      <c r="D64" t="s">
-        <v>177</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>209</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>210</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
         <v>211</v>
       </c>
-      <c r="D65" t="s">
-        <v>177</v>
-      </c>
-      <c r="E65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>212</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>213</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
         <v>214</v>
       </c>
-      <c r="D66" t="s">
-        <v>177</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>215</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>216</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>176</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
         <v>217</v>
       </c>
-      <c r="D67" t="s">
-        <v>177</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>218</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>219</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>176</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
         <v>220</v>
       </c>
-      <c r="D68" t="s">
-        <v>177</v>
-      </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>221</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>222</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
+        <v>176</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
         <v>223</v>
       </c>
-      <c r="D69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>224</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>225</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
         <v>226</v>
       </c>
-      <c r="D70" t="s">
-        <v>177</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>227</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>228</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
         <v>229</v>
       </c>
-      <c r="D71" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>230</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>231</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
         <v>232</v>
       </c>
-      <c r="D72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>233</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>234</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
         <v>235</v>
       </c>
-      <c r="D73" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>28</v>
-      </c>
-      <c r="G73" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>236</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>237</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>176</v>
+      </c>
+      <c r="E74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
         <v>238</v>
       </c>
-      <c r="D74" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>239</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>240</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>176</v>
+      </c>
+      <c r="E75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
         <v>241</v>
       </c>
-      <c r="D75" t="s">
-        <v>177</v>
-      </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>242</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>243</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>176</v>
+      </c>
+      <c r="E76" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
         <v>244</v>
       </c>
-      <c r="D76" t="s">
-        <v>177</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>245</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>246</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
+        <v>176</v>
+      </c>
+      <c r="E77" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
         <v>247</v>
       </c>
-      <c r="D77" t="s">
-        <v>177</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>248</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>249</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>176</v>
+      </c>
+      <c r="E78" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
         <v>250</v>
       </c>
-      <c r="D78" t="s">
-        <v>177</v>
-      </c>
-      <c r="E78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>251</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>252</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
+        <v>176</v>
+      </c>
+      <c r="E79" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
         <v>253</v>
       </c>
-      <c r="D79" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>254</v>
       </c>
-      <c r="B80" t="s">
-        <v>255</v>
-      </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
+        <v>255</v>
+      </c>
+      <c r="B81" t="s">
         <v>256</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>257</v>
       </c>
-      <c r="C81" t="s">
-        <v>258</v>
-      </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
+        <v>258</v>
+      </c>
+      <c r="B82" t="s">
         <v>259</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>260</v>
       </c>
-      <c r="C82" t="s">
-        <v>261</v>
-      </c>
       <c r="D82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
+        <v>261</v>
+      </c>
+      <c r="B83" t="s">
         <v>262</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>263</v>
       </c>
-      <c r="C83" t="s">
-        <v>264</v>
-      </c>
       <c r="D83" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
+        <v>264</v>
+      </c>
+      <c r="B84" t="s">
         <v>265</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>266</v>
       </c>
-      <c r="C84" t="s">
-        <v>267</v>
-      </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
+        <v>267</v>
+      </c>
+      <c r="B85" t="s">
         <v>268</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>269</v>
       </c>
-      <c r="C85" t="s">
-        <v>270</v>
-      </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
+        <v>270</v>
+      </c>
+      <c r="B86" t="s">
         <v>271</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>272</v>
       </c>
-      <c r="C86" t="s">
-        <v>273</v>
-      </c>
       <c r="D86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
+        <v>273</v>
+      </c>
+      <c r="B87" t="s">
         <v>274</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>275</v>
       </c>
-      <c r="C87" t="s">
-        <v>276</v>
-      </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
+        <v>276</v>
+      </c>
+      <c r="B88" t="s">
         <v>277</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>278</v>
       </c>
-      <c r="C88" t="s">
-        <v>279</v>
-      </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
+        <v>279</v>
+      </c>
+      <c r="B89" t="s">
         <v>280</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>281</v>
       </c>
-      <c r="C89" t="s">
-        <v>282</v>
-      </c>
       <c r="D89" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
+        <v>282</v>
+      </c>
+      <c r="B90" t="s">
         <v>283</v>
       </c>
-      <c r="B90" t="s">
-        <v>284</v>
-      </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" t="s">
         <v>285</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>286</v>
       </c>
-      <c r="C91" t="s">
-        <v>287</v>
-      </c>
       <c r="D91" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
+        <v>287</v>
+      </c>
+      <c r="B92" t="s">
         <v>288</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>289</v>
       </c>
-      <c r="C92" t="s">
-        <v>290</v>
-      </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" t="s">
         <v>291</v>
       </c>
-      <c r="B93" t="s">
-        <v>272</v>
-      </c>
-      <c r="C93" t="s">
-        <v>292</v>
-      </c>
       <c r="D93" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E93" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
+        <v>292</v>
+      </c>
+      <c r="B94" t="s">
+        <v>288</v>
+      </c>
+      <c r="C94" t="s">
         <v>293</v>
       </c>
-      <c r="B94" t="s">
-        <v>289</v>
-      </c>
-      <c r="C94" t="s">
-        <v>294</v>
-      </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
+        <v>294</v>
+      </c>
+      <c r="B95" t="s">
         <v>295</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>296</v>
       </c>
-      <c r="C95" t="s">
-        <v>297</v>
-      </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
+        <v>297</v>
+      </c>
+      <c r="B96" t="s">
         <v>298</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>299</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
+        <v>176</v>
+      </c>
+      <c r="E96" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
         <v>300</v>
       </c>
-      <c r="D96" t="s">
-        <v>177</v>
-      </c>
-      <c r="E96" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" t="s">
+      <c r="B97" t="s">
         <v>301</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>302</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
+        <v>176</v>
+      </c>
+      <c r="E97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
         <v>303</v>
       </c>
-      <c r="D97" t="s">
-        <v>177</v>
-      </c>
-      <c r="E97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" t="s">
+      <c r="B98" t="s">
         <v>304</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>305</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
+        <v>176</v>
+      </c>
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
         <v>306</v>
       </c>
-      <c r="D98" t="s">
-        <v>177</v>
-      </c>
-      <c r="E98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" t="s">
+      <c r="B99" t="s">
         <v>307</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>308</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
+        <v>176</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
         <v>309</v>
       </c>
-      <c r="D99" t="s">
-        <v>177</v>
-      </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>310</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>311</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
+        <v>176</v>
+      </c>
+      <c r="E100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
         <v>312</v>
       </c>
-      <c r="D100" t="s">
-        <v>177</v>
-      </c>
-      <c r="E100" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
         <v>313</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>314</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
+        <v>176</v>
+      </c>
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
         <v>315</v>
       </c>
-      <c r="D101" t="s">
-        <v>177</v>
-      </c>
-      <c r="E101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" t="s">
+      <c r="B102" t="s">
         <v>316</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>317</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>318</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
         <v>319</v>
       </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" t="s">
+      <c r="B103" t="s">
         <v>320</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>321</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>318</v>
+      </c>
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
         <v>322</v>
       </c>
-      <c r="D103" t="s">
-        <v>319</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" t="s">
+      <c r="B104" t="s">
         <v>323</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>324</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
+        <v>318</v>
+      </c>
+      <c r="E104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
         <v>325</v>
       </c>
-      <c r="D104" t="s">
-        <v>319</v>
-      </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" t="s">
+      <c r="B105" t="s">
         <v>326</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>327</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
+        <v>318</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
         <v>328</v>
       </c>
-      <c r="D105" t="s">
-        <v>319</v>
-      </c>
-      <c r="E105" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" t="s">
+      <c r="B106" t="s">
         <v>329</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>330</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
+        <v>318</v>
+      </c>
+      <c r="E106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
         <v>331</v>
       </c>
-      <c r="D106" t="s">
-        <v>319</v>
-      </c>
-      <c r="E106" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" t="s">
+      <c r="B107" t="s">
         <v>332</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>333</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>318</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
         <v>334</v>
       </c>
-      <c r="D107" t="s">
-        <v>319</v>
-      </c>
-      <c r="E107" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" t="s">
+      <c r="B108" t="s">
         <v>335</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>336</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>337</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
         <v>338</v>
       </c>
-      <c r="E108" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" t="s">
-        <v>28</v>
-      </c>
-      <c r="G108" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" t="s">
+      <c r="B109" t="s">
         <v>339</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>340</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>337</v>
+      </c>
+      <c r="E109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
         <v>341</v>
       </c>
-      <c r="D109" t="s">
-        <v>338</v>
-      </c>
-      <c r="E109" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" t="s">
+      <c r="B110" t="s">
         <v>342</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>343</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>337</v>
+      </c>
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
         <v>344</v>
       </c>
-      <c r="D110" t="s">
-        <v>338</v>
-      </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
         <v>345</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>346</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
+        <v>337</v>
+      </c>
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
         <v>347</v>
       </c>
-      <c r="D111" t="s">
-        <v>338</v>
-      </c>
-      <c r="E111" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
         <v>348</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>349</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>337</v>
+      </c>
+      <c r="E112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
         <v>350</v>
       </c>
-      <c r="D112" t="s">
-        <v>338</v>
-      </c>
-      <c r="E112" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>351</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>352</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>337</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
         <v>353</v>
       </c>
-      <c r="D113" t="s">
-        <v>338</v>
-      </c>
-      <c r="E113" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
         <v>354</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>355</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>337</v>
+      </c>
+      <c r="E114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
         <v>356</v>
       </c>
-      <c r="D114" t="s">
-        <v>338</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" t="s">
+      <c r="B115" t="s">
         <v>357</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>358</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>337</v>
+      </c>
+      <c r="E115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
         <v>359</v>
       </c>
-      <c r="D115" t="s">
-        <v>338</v>
-      </c>
-      <c r="E115" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" t="s">
+      <c r="B116" t="s">
         <v>360</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>361</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>337</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
         <v>362</v>
       </c>
-      <c r="D116" t="s">
-        <v>338</v>
-      </c>
-      <c r="E116" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" t="s">
+      <c r="B117" t="s">
         <v>363</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>364</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>337</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
         <v>365</v>
       </c>
-      <c r="D117" t="s">
-        <v>338</v>
-      </c>
-      <c r="E117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" t="s">
+      <c r="B118" t="s">
         <v>366</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>367</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>337</v>
+      </c>
+      <c r="E118" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
         <v>368</v>
       </c>
-      <c r="D118" t="s">
-        <v>338</v>
-      </c>
-      <c r="E118" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" t="s">
-        <v>28</v>
-      </c>
-      <c r="G118" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" t="s">
+      <c r="B119" t="s">
         <v>369</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>370</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>337</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
         <v>371</v>
       </c>
-      <c r="D119" t="s">
-        <v>338</v>
-      </c>
-      <c r="E119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" t="s">
+      <c r="B120" t="s">
         <v>372</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>373</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>337</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
         <v>374</v>
       </c>
-      <c r="D120" t="s">
-        <v>338</v>
-      </c>
-      <c r="E120" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" t="s">
+      <c r="B121" t="s">
         <v>375</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>376</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>337</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
         <v>377</v>
       </c>
-      <c r="D121" t="s">
-        <v>338</v>
-      </c>
-      <c r="E121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" t="s">
+      <c r="B122" t="s">
         <v>378</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>337</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
         <v>379</v>
       </c>
-      <c r="D122" t="s">
-        <v>338</v>
-      </c>
-      <c r="E122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" t="s">
+      <c r="B123" t="s">
         <v>380</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
+        <v>337</v>
+      </c>
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
         <v>381</v>
       </c>
-      <c r="D123" t="s">
-        <v>338</v>
-      </c>
-      <c r="E123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" t="s">
+      <c r="B124" t="s">
         <v>382</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>383</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>337</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
         <v>384</v>
       </c>
-      <c r="D124" t="s">
-        <v>338</v>
-      </c>
-      <c r="E124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" t="s">
+      <c r="B125" t="s">
         <v>385</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>386</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>337</v>
+      </c>
+      <c r="E125" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
         <v>387</v>
       </c>
-      <c r="D125" t="s">
-        <v>338</v>
-      </c>
-      <c r="E125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
+      <c r="B126" t="s">
         <v>388</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>389</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>390</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
         <v>391</v>
       </c>
-      <c r="E126" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" t="s">
-        <v>28</v>
-      </c>
-      <c r="G126" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" t="s">
+      <c r="B127" t="s">
         <v>392</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>393</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>390</v>
+      </c>
+      <c r="E127" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
         <v>394</v>
       </c>
-      <c r="D127" t="s">
-        <v>391</v>
-      </c>
-      <c r="E127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" t="s">
+      <c r="B128" t="s">
         <v>395</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>396</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>390</v>
+      </c>
+      <c r="E128" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
         <v>397</v>
       </c>
-      <c r="D128" t="s">
-        <v>391</v>
-      </c>
-      <c r="E128" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
+      <c r="B129" t="s">
         <v>398</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>399</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
+        <v>390</v>
+      </c>
+      <c r="E129" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
         <v>400</v>
       </c>
-      <c r="D129" t="s">
-        <v>391</v>
-      </c>
-      <c r="E129" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
+      <c r="B130" t="s">
         <v>401</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>402</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>390</v>
+      </c>
+      <c r="E130" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
         <v>403</v>
       </c>
-      <c r="D130" t="s">
-        <v>391</v>
-      </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" t="s">
-        <v>28</v>
-      </c>
-      <c r="G130" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
+      <c r="B131" t="s">
         <v>404</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>405</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>390</v>
+      </c>
+      <c r="E131" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
         <v>406</v>
       </c>
-      <c r="D131" t="s">
-        <v>391</v>
-      </c>
-      <c r="E131" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
+      <c r="B132" t="s">
         <v>407</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>408</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>390</v>
+      </c>
+      <c r="E132" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
         <v>409</v>
       </c>
-      <c r="D132" t="s">
-        <v>391</v>
-      </c>
-      <c r="E132" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
+      <c r="B133" t="s">
         <v>410</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>411</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>390</v>
+      </c>
+      <c r="E133" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
         <v>412</v>
       </c>
-      <c r="D133" t="s">
-        <v>391</v>
-      </c>
-      <c r="E133" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
+      <c r="B134" t="s">
         <v>413</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>414</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>390</v>
+      </c>
+      <c r="E134" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
         <v>415</v>
       </c>
-      <c r="D134" t="s">
-        <v>391</v>
-      </c>
-      <c r="E134" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
+      <c r="B135" t="s">
         <v>416</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>417</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>390</v>
+      </c>
+      <c r="E135" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
         <v>418</v>
       </c>
-      <c r="D135" t="s">
-        <v>391</v>
-      </c>
-      <c r="E135" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
+      <c r="B136" t="s">
         <v>419</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>420</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>390</v>
+      </c>
+      <c r="E136" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
         <v>421</v>
       </c>
-      <c r="D136" t="s">
-        <v>391</v>
-      </c>
-      <c r="E136" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
+      <c r="B137" t="s">
         <v>422</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>423</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>390</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
         <v>424</v>
       </c>
-      <c r="D137" t="s">
-        <v>391</v>
-      </c>
-      <c r="E137" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" t="s">
+      <c r="B138" t="s">
         <v>425</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>426</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>390</v>
+      </c>
+      <c r="E138" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
         <v>427</v>
       </c>
-      <c r="D138" t="s">
-        <v>391</v>
-      </c>
-      <c r="E138" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
+      <c r="B139" t="s">
         <v>428</v>
       </c>
-      <c r="B139" t="s">
+      <c r="D139" t="s">
+        <v>390</v>
+      </c>
+      <c r="E139" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
         <v>429</v>
       </c>
-      <c r="D139" t="s">
-        <v>391</v>
-      </c>
-      <c r="E139" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
+      <c r="B140" t="s">
         <v>430</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>431</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>432</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
         <v>433</v>
       </c>
-      <c r="E140" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" t="s">
-        <v>28</v>
-      </c>
-      <c r="G140" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
+      <c r="B141" t="s">
         <v>434</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D141" t="s">
+        <v>432</v>
+      </c>
+      <c r="E141" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
         <v>435</v>
       </c>
-      <c r="D141" t="s">
-        <v>433</v>
-      </c>
-      <c r="E141" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
+      <c r="B142" t="s">
         <v>436</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>437</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
+        <v>432</v>
+      </c>
+      <c r="E142" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
         <v>438</v>
       </c>
-      <c r="D142" t="s">
-        <v>433</v>
-      </c>
-      <c r="E142" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" t="s">
+      <c r="B143" t="s">
         <v>439</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>440</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
+        <v>432</v>
+      </c>
+      <c r="E143" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
         <v>441</v>
       </c>
-      <c r="D143" t="s">
-        <v>433</v>
-      </c>
-      <c r="E143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" t="s">
+      <c r="B144" t="s">
         <v>442</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>443</v>
       </c>
-      <c r="C144" t="s">
-        <v>444</v>
-      </c>
       <c r="D144" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E144" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
+        <v>444</v>
+      </c>
+      <c r="B145" t="s">
         <v>445</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>446</v>
       </c>
-      <c r="C145" t="s">
-        <v>447</v>
-      </c>
       <c r="D145" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E145" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
+        <v>447</v>
+      </c>
+      <c r="B146" t="s">
         <v>448</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>449</v>
       </c>
-      <c r="C146" t="s">
-        <v>450</v>
-      </c>
       <c r="D146" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
+        <v>450</v>
+      </c>
+      <c r="B147" t="s">
         <v>451</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>452</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>453</v>
       </c>
-      <c r="D147" t="s">
-        <v>454</v>
-      </c>
       <c r="E147" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
+        <v>454</v>
+      </c>
+      <c r="B148" t="s">
         <v>455</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>456</v>
       </c>
-      <c r="C148" t="s">
-        <v>457</v>
-      </c>
       <c r="D148" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E148" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
+        <v>457</v>
+      </c>
+      <c r="B149" t="s">
         <v>458</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>459</v>
       </c>
-      <c r="C149" t="s">
-        <v>460</v>
-      </c>
       <c r="D149" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
+        <v>460</v>
+      </c>
+      <c r="B150" t="s">
         <v>461</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>462</v>
       </c>
-      <c r="C150" t="s">
-        <v>463</v>
-      </c>
       <c r="D150" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E150" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
+        <v>463</v>
+      </c>
+      <c r="B151" t="s">
         <v>464</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>465</v>
       </c>
-      <c r="C151" t="s">
-        <v>466</v>
-      </c>
       <c r="D151" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E151" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
+        <v>466</v>
+      </c>
+      <c r="B152" t="s">
         <v>467</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>468</v>
       </c>
-      <c r="C152" t="s">
-        <v>469</v>
-      </c>
       <c r="D152" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
+        <v>469</v>
+      </c>
+      <c r="B153" t="s">
         <v>470</v>
       </c>
-      <c r="B153" t="s">
-        <v>471</v>
-      </c>
       <c r="D153" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E153" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
+        <v>471</v>
+      </c>
+      <c r="B154" t="s">
         <v>472</v>
       </c>
-      <c r="B154" t="s">
-        <v>473</v>
-      </c>
       <c r="D154" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
+        <v>473</v>
+      </c>
+      <c r="B155" t="s">
         <v>474</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>475</v>
       </c>
-      <c r="C155" t="s">
-        <v>476</v>
-      </c>
       <c r="D155" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
+        <v>476</v>
+      </c>
+      <c r="B156" t="s">
         <v>477</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>478</v>
       </c>
-      <c r="C156" t="s">
-        <v>479</v>
-      </c>
       <c r="D156" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E156" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
+        <v>479</v>
+      </c>
+      <c r="B157" t="s">
         <v>480</v>
       </c>
-      <c r="B157" t="s">
-        <v>481</v>
-      </c>
       <c r="D157" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E157" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
+        <v>481</v>
+      </c>
+      <c r="B158" t="s">
         <v>482</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>483</v>
       </c>
-      <c r="C158" t="s">
-        <v>484</v>
-      </c>
       <c r="D158" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E158" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
+        <v>484</v>
+      </c>
+      <c r="B159" t="s">
         <v>485</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>486</v>
       </c>
-      <c r="C159" t="s">
-        <v>487</v>
-      </c>
       <c r="D159" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
+        <v>487</v>
+      </c>
+      <c r="B160" t="s">
         <v>488</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>489</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
+        <v>453</v>
+      </c>
+      <c r="E160" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
         <v>490</v>
       </c>
-      <c r="D160" t="s">
-        <v>454</v>
-      </c>
-      <c r="E160" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
+      <c r="B161" t="s">
         <v>491</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>492</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
+        <v>453</v>
+      </c>
+      <c r="E161" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
         <v>493</v>
       </c>
-      <c r="D161" t="s">
-        <v>454</v>
-      </c>
-      <c r="E161" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
+      <c r="B162" t="s">
         <v>494</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>495</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
+        <v>453</v>
+      </c>
+      <c r="E162" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
         <v>496</v>
       </c>
-      <c r="D162" t="s">
-        <v>454</v>
-      </c>
-      <c r="E162" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
+      <c r="B163" t="s">
         <v>497</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>498</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
+        <v>453</v>
+      </c>
+      <c r="E163" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
         <v>499</v>
       </c>
-      <c r="D163" t="s">
-        <v>454</v>
-      </c>
-      <c r="E163" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
+      <c r="B164" t="s">
+        <v>451</v>
+      </c>
+      <c r="C164" t="s">
         <v>500</v>
       </c>
-      <c r="B164" t="s">
-        <v>452</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>501</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
         <v>502</v>
       </c>
-      <c r="E164" t="s">
-        <v>11</v>
-      </c>
-      <c r="F164" t="s">
-        <v>28</v>
-      </c>
-      <c r="G164" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
+      <c r="B165" t="s">
         <v>503</v>
       </c>
-      <c r="B165" t="s">
+      <c r="D165" t="s">
+        <v>501</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
         <v>504</v>
       </c>
-      <c r="D165" t="s">
-        <v>502</v>
-      </c>
-      <c r="E165" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
+      <c r="B166" t="s">
         <v>505</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>506</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
+        <v>501</v>
+      </c>
+      <c r="E166" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
         <v>507</v>
       </c>
-      <c r="D166" t="s">
-        <v>502</v>
-      </c>
-      <c r="E166" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
+      <c r="B167" t="s">
+        <v>494</v>
+      </c>
+      <c r="C167" t="s">
         <v>508</v>
       </c>
-      <c r="B167" t="s">
-        <v>495</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
+        <v>501</v>
+      </c>
+      <c r="E167" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
         <v>509</v>
       </c>
-      <c r="D167" t="s">
-        <v>502</v>
-      </c>
-      <c r="E167" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
+      <c r="B168" t="s">
+        <v>497</v>
+      </c>
+      <c r="C168" t="s">
+        <v>498</v>
+      </c>
+      <c r="D168" t="s">
+        <v>501</v>
+      </c>
+      <c r="E168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
         <v>510</v>
       </c>
-      <c r="B168" t="s">
-        <v>498</v>
-      </c>
-      <c r="C168" t="s">
-        <v>499</v>
-      </c>
-      <c r="D168" t="s">
-        <v>502</v>
-      </c>
-      <c r="E168" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
+      <c r="B169" t="s">
         <v>511</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>512</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
+        <v>501</v>
+      </c>
+      <c r="E169" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
         <v>513</v>
       </c>
-      <c r="D169" t="s">
-        <v>502</v>
-      </c>
-      <c r="E169" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
+      <c r="B170" t="s">
         <v>514</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>515</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>516</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
         <v>517</v>
       </c>
-      <c r="E170" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
+      <c r="B171" t="s">
+        <v>477</v>
+      </c>
+      <c r="C171" t="s">
         <v>518</v>
       </c>
-      <c r="B171" t="s">
-        <v>478</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>516</v>
+      </c>
+      <c r="E171" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
         <v>519</v>
       </c>
-      <c r="D171" t="s">
-        <v>517</v>
-      </c>
-      <c r="E171" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
+      <c r="B172" t="s">
         <v>520</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>521</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
+        <v>516</v>
+      </c>
+      <c r="E172" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
         <v>522</v>
       </c>
-      <c r="D172" t="s">
-        <v>517</v>
-      </c>
-      <c r="E172" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
+      <c r="B173" t="s">
         <v>523</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>524</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
+        <v>516</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
         <v>525</v>
       </c>
-      <c r="D173" t="s">
-        <v>517</v>
-      </c>
-      <c r="E173" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
+      <c r="B174" t="s">
         <v>526</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>527</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
+        <v>516</v>
+      </c>
+      <c r="E174" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
         <v>528</v>
       </c>
-      <c r="D174" t="s">
-        <v>517</v>
-      </c>
-      <c r="E174" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
+      <c r="B175" t="s">
         <v>529</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
+        <v>486</v>
+      </c>
+      <c r="D175" t="s">
+        <v>516</v>
+      </c>
+      <c r="E175" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
         <v>530</v>
       </c>
-      <c r="C175" t="s">
-        <v>487</v>
-      </c>
-      <c r="D175" t="s">
-        <v>517</v>
-      </c>
-      <c r="E175" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
+      <c r="B176" t="s">
         <v>531</v>
       </c>
-      <c r="B176" t="s">
-        <v>532</v>
-      </c>
       <c r="C176" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D176" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E176" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
+        <v>532</v>
+      </c>
+      <c r="B177" t="s">
+        <v>480</v>
+      </c>
+      <c r="C177" t="s">
         <v>533</v>
       </c>
-      <c r="B177" t="s">
-        <v>481</v>
-      </c>
-      <c r="C177" t="s">
-        <v>534</v>
-      </c>
       <c r="D177" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E177" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
+        <v>534</v>
+      </c>
+      <c r="B178" t="s">
         <v>535</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>536</v>
       </c>
-      <c r="C178" t="s">
-        <v>537</v>
-      </c>
       <c r="D178" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E178" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
+        <v>537</v>
+      </c>
+      <c r="B179" t="s">
         <v>538</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>539</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>540</v>
       </c>
-      <c r="D179" t="s">
-        <v>541</v>
-      </c>
       <c r="E179" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
+        <v>541</v>
+      </c>
+      <c r="B180" t="s">
         <v>542</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>543</v>
       </c>
-      <c r="C180" t="s">
-        <v>544</v>
-      </c>
       <c r="D180" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E180" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
+        <v>544</v>
+      </c>
+      <c r="B181" t="s">
         <v>545</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>546</v>
       </c>
-      <c r="C181" t="s">
-        <v>547</v>
-      </c>
       <c r="D181" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E181" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
+        <v>547</v>
+      </c>
+      <c r="B182" t="s">
         <v>548</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>549</v>
       </c>
-      <c r="C182" t="s">
-        <v>550</v>
-      </c>
       <c r="D182" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E182" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
+        <v>550</v>
+      </c>
+      <c r="B183" t="s">
         <v>551</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>552</v>
       </c>
-      <c r="C183" t="s">
-        <v>553</v>
-      </c>
       <c r="D183" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E183" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
+        <v>553</v>
+      </c>
+      <c r="B184" t="s">
         <v>554</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>555</v>
       </c>
-      <c r="C184" t="s">
-        <v>556</v>
-      </c>
       <c r="D184" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E184" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
+        <v>556</v>
+      </c>
+      <c r="B185" t="s">
         <v>557</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>558</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>559</v>
       </c>
-      <c r="D185" t="s">
-        <v>560</v>
-      </c>
       <c r="E185" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
+        <v>560</v>
+      </c>
+      <c r="B186" t="s">
         <v>561</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>562</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>563</v>
       </c>
-      <c r="D186" t="s">
-        <v>564</v>
-      </c>
       <c r="E186" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
+        <v>564</v>
+      </c>
+      <c r="B187" t="s">
         <v>565</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>566</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>567</v>
       </c>
-      <c r="D187" t="s">
-        <v>568</v>
-      </c>
       <c r="E187" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
+        <v>568</v>
+      </c>
+      <c r="B188" t="s">
         <v>569</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>570</v>
       </c>
-      <c r="C188" t="s">
-        <v>571</v>
-      </c>
       <c r="D188" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E188" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
+        <v>571</v>
+      </c>
+      <c r="B189" t="s">
         <v>572</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>573</v>
       </c>
-      <c r="C189" t="s">
-        <v>574</v>
-      </c>
       <c r="D189" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E189" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
+        <v>574</v>
+      </c>
+      <c r="B190" t="s">
         <v>575</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>576</v>
       </c>
-      <c r="C190" t="s">
-        <v>577</v>
-      </c>
       <c r="D190" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E190" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
+        <v>577</v>
+      </c>
+      <c r="B191" t="s">
         <v>578</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>579</v>
       </c>
-      <c r="C191" t="s">
-        <v>580</v>
-      </c>
       <c r="D191" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E191" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
+        <v>580</v>
+      </c>
+      <c r="B192" t="s">
         <v>581</v>
       </c>
-      <c r="B192" t="s">
-        <v>582</v>
-      </c>
       <c r="D192" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E192" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
+        <v>582</v>
+      </c>
+      <c r="B193" t="s">
         <v>583</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>584</v>
       </c>
-      <c r="C193" t="s">
-        <v>585</v>
-      </c>
       <c r="D193" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E193" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
+        <v>585</v>
+      </c>
+      <c r="B194" t="s">
         <v>586</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>587</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>588</v>
       </c>
-      <c r="D194" t="s">
-        <v>589</v>
-      </c>
       <c r="E194" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
+        <v>589</v>
+      </c>
+      <c r="B195" t="s">
         <v>590</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>591</v>
       </c>
-      <c r="C195" t="s">
-        <v>592</v>
-      </c>
       <c r="D195" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E195" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
+        <v>592</v>
+      </c>
+      <c r="B196" t="s">
         <v>593</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>594</v>
       </c>
-      <c r="C196" t="s">
-        <v>595</v>
-      </c>
       <c r="D196" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E196" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
+        <v>595</v>
+      </c>
+      <c r="B197" t="s">
         <v>596</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>597</v>
       </c>
-      <c r="C197" t="s">
-        <v>598</v>
-      </c>
       <c r="D197" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E197" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
+        <v>598</v>
+      </c>
+      <c r="B198" t="s">
         <v>599</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>600</v>
       </c>
-      <c r="C198" t="s">
-        <v>601</v>
-      </c>
       <c r="D198" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E198" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
+        <v>601</v>
+      </c>
+      <c r="B199" t="s">
         <v>602</v>
       </c>
-      <c r="B199" t="s">
-        <v>603</v>
-      </c>
       <c r="D199" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E199" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
+        <v>603</v>
+      </c>
+      <c r="B200" t="s">
         <v>604</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>605</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
         <v>606</v>
       </c>
-      <c r="D200" t="s">
-        <v>607</v>
-      </c>
       <c r="E200" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
+        <v>607</v>
+      </c>
+      <c r="B201" t="s">
         <v>608</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>609</v>
       </c>
-      <c r="C201" t="s">
-        <v>610</v>
-      </c>
       <c r="D201" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E201" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
+        <v>610</v>
+      </c>
+      <c r="B202" t="s">
         <v>611</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>612</v>
       </c>
-      <c r="C202" t="s">
-        <v>613</v>
-      </c>
       <c r="D202" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E202" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
+        <v>613</v>
+      </c>
+      <c r="B203" t="s">
         <v>614</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>615</v>
       </c>
-      <c r="C203" t="s">
-        <v>616</v>
-      </c>
       <c r="D203" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E203" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
+        <v>616</v>
+      </c>
+      <c r="B204" t="s">
         <v>617</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>618</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>619</v>
       </c>
-      <c r="D204" t="s">
-        <v>620</v>
-      </c>
       <c r="E204" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
+        <v>620</v>
+      </c>
+      <c r="B205" t="s">
         <v>621</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>622</v>
       </c>
-      <c r="C205" t="s">
-        <v>623</v>
-      </c>
       <c r="D205" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E205" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
+        <v>623</v>
+      </c>
+      <c r="B206" t="s">
         <v>624</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>625</v>
       </c>
-      <c r="C206" t="s">
-        <v>626</v>
-      </c>
       <c r="D206" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E206" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
+        <v>626</v>
+      </c>
+      <c r="B207" t="s">
         <v>627</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
         <v>628</v>
       </c>
-      <c r="C207" t="s">
-        <v>629</v>
-      </c>
       <c r="D207" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E207" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
+        <v>629</v>
+      </c>
+      <c r="B208" t="s">
         <v>630</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>631</v>
       </c>
-      <c r="C208" t="s">
-        <v>632</v>
-      </c>
       <c r="D208" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E208" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
+        <v>632</v>
+      </c>
+      <c r="B209" t="s">
         <v>633</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>634</v>
       </c>
-      <c r="C209" t="s">
-        <v>635</v>
-      </c>
       <c r="D209" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E209" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
+        <v>635</v>
+      </c>
+      <c r="B210" t="s">
         <v>636</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>637</v>
       </c>
-      <c r="C210" t="s">
-        <v>638</v>
-      </c>
       <c r="D210" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E210" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
+        <v>638</v>
+      </c>
+      <c r="B211" t="s">
         <v>639</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>640</v>
       </c>
-      <c r="C211" t="s">
-        <v>641</v>
-      </c>
       <c r="D211" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E211" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
+        <v>641</v>
+      </c>
+      <c r="B212" t="s">
         <v>642</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>643</v>
       </c>
-      <c r="C212" t="s">
-        <v>644</v>
-      </c>
       <c r="D212" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E212" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
+        <v>644</v>
+      </c>
+      <c r="B213" t="s">
         <v>645</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>646</v>
       </c>
-      <c r="C213" t="s">
-        <v>647</v>
-      </c>
       <c r="D213" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E213" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
+        <v>647</v>
+      </c>
+      <c r="B214" t="s">
         <v>648</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>649</v>
       </c>
-      <c r="C214" t="s">
-        <v>650</v>
-      </c>
       <c r="D214" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E214" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
+        <v>650</v>
+      </c>
+      <c r="B215" t="s">
         <v>651</v>
       </c>
-      <c r="B215" t="s">
-        <v>652</v>
-      </c>
       <c r="D215" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E215" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
+        <v>652</v>
+      </c>
+      <c r="B216" t="s">
         <v>653</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>654</v>
       </c>
-      <c r="C216" t="s">
-        <v>655</v>
-      </c>
       <c r="D216" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E216" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
+        <v>655</v>
+      </c>
+      <c r="B217" t="s">
         <v>656</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>657</v>
       </c>
-      <c r="C217" t="s">
-        <v>658</v>
-      </c>
       <c r="D217" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E217" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
+        <v>658</v>
+      </c>
+      <c r="B218" t="s">
         <v>659</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>660</v>
       </c>
-      <c r="C218" t="s">
-        <v>661</v>
-      </c>
       <c r="D218" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E218" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
+        <v>661</v>
+      </c>
+      <c r="B219" t="s">
         <v>662</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>663</v>
       </c>
-      <c r="C219" t="s">
-        <v>664</v>
-      </c>
       <c r="D219" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E219" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
+        <v>664</v>
+      </c>
+      <c r="B220" t="s">
         <v>665</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>666</v>
       </c>
-      <c r="C220" t="s">
-        <v>667</v>
-      </c>
       <c r="D220" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E220" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
+        <v>667</v>
+      </c>
+      <c r="B221" t="s">
         <v>668</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>669</v>
       </c>
-      <c r="C221" t="s">
-        <v>670</v>
-      </c>
       <c r="D221" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E221" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
+        <v>670</v>
+      </c>
+      <c r="B222" t="s">
         <v>671</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>672</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
         <v>673</v>
       </c>
-      <c r="D222" t="s">
-        <v>674</v>
-      </c>
       <c r="E222" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
+        <v>674</v>
+      </c>
+      <c r="B223" t="s">
         <v>675</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>676</v>
       </c>
-      <c r="C223" t="s">
-        <v>677</v>
-      </c>
       <c r="D223" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E223" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
+        <v>677</v>
+      </c>
+      <c r="B224" t="s">
         <v>678</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>679</v>
       </c>
-      <c r="C224" t="s">
-        <v>680</v>
-      </c>
       <c r="D224" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E224" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
+        <v>680</v>
+      </c>
+      <c r="B225" t="s">
         <v>681</v>
       </c>
-      <c r="B225" t="s">
-        <v>682</v>
-      </c>
       <c r="D225" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E225" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
+        <v>682</v>
+      </c>
+      <c r="B226" t="s">
         <v>683</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
         <v>684</v>
       </c>
-      <c r="C226" t="s">
-        <v>685</v>
-      </c>
       <c r="D226" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E226" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
+        <v>685</v>
+      </c>
+      <c r="B227" t="s">
         <v>686</v>
       </c>
-      <c r="B227" t="s">
-        <v>687</v>
-      </c>
       <c r="D227" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E227" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
+        <v>687</v>
+      </c>
+      <c r="B228" t="s">
         <v>688</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>689</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D228" t="s">
         <v>690</v>
       </c>
-      <c r="D228" t="s">
-        <v>691</v>
-      </c>
       <c r="E228" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
+        <v>691</v>
+      </c>
+      <c r="B229" t="s">
         <v>692</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>693</v>
       </c>
-      <c r="C229" t="s">
-        <v>694</v>
-      </c>
       <c r="D229" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E229" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
+        <v>694</v>
+      </c>
+      <c r="B230" t="s">
         <v>695</v>
       </c>
-      <c r="B230" t="s">
-        <v>696</v>
-      </c>
       <c r="D230" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E230" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
+        <v>696</v>
+      </c>
+      <c r="B231" t="s">
         <v>697</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
         <v>698</v>
       </c>
-      <c r="C231" t="s">
-        <v>699</v>
-      </c>
       <c r="D231" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E231" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
+        <v>699</v>
+      </c>
+      <c r="B232" t="s">
         <v>700</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>701</v>
       </c>
-      <c r="C232" t="s">
-        <v>702</v>
-      </c>
       <c r="D232" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E232" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
+        <v>702</v>
+      </c>
+      <c r="B233" t="s">
         <v>703</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>704</v>
       </c>
-      <c r="C233" t="s">
+      <c r="D233" t="s">
         <v>705</v>
       </c>
-      <c r="D233" t="s">
-        <v>706</v>
-      </c>
       <c r="E233" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
+        <v>706</v>
+      </c>
+      <c r="B234" t="s">
         <v>707</v>
       </c>
-      <c r="B234" t="s">
-        <v>708</v>
-      </c>
       <c r="D234" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E234" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
+        <v>708</v>
+      </c>
+      <c r="B235" t="s">
         <v>709</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>710</v>
       </c>
-      <c r="C235" t="s">
-        <v>711</v>
-      </c>
       <c r="D235" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E235" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
+        <v>711</v>
+      </c>
+      <c r="B236" t="s">
         <v>712</v>
       </c>
-      <c r="B236" t="s">
-        <v>713</v>
-      </c>
       <c r="D236" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E236" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
+        <v>713</v>
+      </c>
+      <c r="B237" t="s">
         <v>714</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>715</v>
       </c>
-      <c r="C237" t="s">
-        <v>716</v>
-      </c>
       <c r="D237" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E237" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
+        <v>716</v>
+      </c>
+      <c r="B238" t="s">
         <v>717</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C238" t="s">
         <v>718</v>
       </c>
-      <c r="C238" t="s">
-        <v>719</v>
-      </c>
       <c r="D238" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E238" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
+        <v>719</v>
+      </c>
+      <c r="B239" t="s">
         <v>720</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" t="s">
         <v>721</v>
       </c>
-      <c r="C239" t="s">
-        <v>722</v>
-      </c>
       <c r="D239" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E239" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
+        <v>722</v>
+      </c>
+      <c r="B240" t="s">
         <v>723</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>724</v>
       </c>
-      <c r="C240" t="s">
-        <v>725</v>
-      </c>
       <c r="D240" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E240" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
+        <v>725</v>
+      </c>
+      <c r="B241" t="s">
         <v>726</v>
       </c>
-      <c r="B241" t="s">
-        <v>727</v>
-      </c>
       <c r="D241" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E241" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
+        <v>727</v>
+      </c>
+      <c r="B242" t="s">
         <v>728</v>
       </c>
-      <c r="B242" t="s">
-        <v>729</v>
-      </c>
       <c r="D242" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E242" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
+        <v>729</v>
+      </c>
+      <c r="B243" t="s">
         <v>730</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>731</v>
       </c>
-      <c r="C243" t="s">
-        <v>732</v>
-      </c>
       <c r="D243" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E243" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
+        <v>732</v>
+      </c>
+      <c r="B244" t="s">
         <v>733</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" t="s">
         <v>734</v>
       </c>
-      <c r="C244" t="s">
-        <v>735</v>
-      </c>
       <c r="D244" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E244" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
+        <v>735</v>
+      </c>
+      <c r="B245" t="s">
         <v>736</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" t="s">
         <v>737</v>
       </c>
-      <c r="C245" t="s">
-        <v>738</v>
-      </c>
       <c r="D245" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E245" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
+        <v>738</v>
+      </c>
+      <c r="B246" t="s">
         <v>739</v>
       </c>
-      <c r="B246" t="s">
-        <v>740</v>
-      </c>
       <c r="D246" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E246" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
+        <v>740</v>
+      </c>
+      <c r="B247" t="s">
         <v>741</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" t="s">
         <v>742</v>
       </c>
-      <c r="C247" t="s">
-        <v>743</v>
-      </c>
       <c r="D247" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E247" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
+        <v>743</v>
+      </c>
+      <c r="B248" t="s">
         <v>744</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>745</v>
       </c>
-      <c r="C248" t="s">
-        <v>746</v>
-      </c>
       <c r="D248" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E248" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
+        <v>746</v>
+      </c>
+      <c r="B249" t="s">
         <v>747</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>748</v>
       </c>
-      <c r="C249" t="s">
-        <v>749</v>
-      </c>
       <c r="D249" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E249" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
+        <v>749</v>
+      </c>
+      <c r="B250" t="s">
         <v>750</v>
       </c>
-      <c r="B250" t="s">
+      <c r="C250" t="s">
         <v>751</v>
       </c>
-      <c r="C250" t="s">
-        <v>752</v>
-      </c>
       <c r="D250" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E250" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
+        <v>752</v>
+      </c>
+      <c r="B251" t="s">
         <v>753</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C251" t="s">
         <v>754</v>
       </c>
-      <c r="C251" t="s">
-        <v>755</v>
-      </c>
       <c r="D251" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E251" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
+        <v>755</v>
+      </c>
+      <c r="B252" t="s">
         <v>756</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C252" t="s">
         <v>757</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>758</v>
       </c>
-      <c r="D252" t="s">
-        <v>759</v>
-      </c>
       <c r="E252" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
+        <v>759</v>
+      </c>
+      <c r="B253" t="s">
         <v>760</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C253" t="s">
         <v>761</v>
       </c>
-      <c r="C253" t="s">
-        <v>762</v>
-      </c>
       <c r="D253" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E253" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
+        <v>762</v>
+      </c>
+      <c r="B254" t="s">
         <v>763</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C254" t="s">
         <v>764</v>
       </c>
-      <c r="C254" t="s">
-        <v>765</v>
-      </c>
       <c r="D254" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E254" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
+        <v>765</v>
+      </c>
+      <c r="B255" t="s">
         <v>766</v>
       </c>
-      <c r="B255" t="s">
+      <c r="C255" t="s">
         <v>767</v>
       </c>
-      <c r="C255" t="s">
-        <v>768</v>
-      </c>
       <c r="D255" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E255" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
+        <v>768</v>
+      </c>
+      <c r="B256" t="s">
         <v>769</v>
       </c>
-      <c r="B256" t="s">
+      <c r="C256" t="s">
         <v>770</v>
       </c>
-      <c r="C256" t="s">
-        <v>771</v>
-      </c>
       <c r="D256" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E256" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
+        <v>771</v>
+      </c>
+      <c r="B257" t="s">
         <v>772</v>
       </c>
-      <c r="B257" t="s">
+      <c r="C257" t="s">
         <v>773</v>
       </c>
-      <c r="C257" t="s">
-        <v>774</v>
-      </c>
       <c r="D257" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E257" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
+        <v>774</v>
+      </c>
+      <c r="B258" t="s">
         <v>775</v>
       </c>
-      <c r="B258" t="s">
+      <c r="C258" t="s">
         <v>776</v>
       </c>
-      <c r="C258" t="s">
-        <v>777</v>
-      </c>
       <c r="D258" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E258" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
+        <v>777</v>
+      </c>
+      <c r="B259" t="s">
         <v>778</v>
       </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
         <v>779</v>
       </c>
-      <c r="C259" t="s">
-        <v>780</v>
-      </c>
       <c r="D259" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E259" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
+        <v>780</v>
+      </c>
+      <c r="B260" t="s">
         <v>781</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" t="s">
         <v>782</v>
       </c>
-      <c r="C260" t="s">
-        <v>783</v>
-      </c>
       <c r="D260" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E260" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
+        <v>783</v>
+      </c>
+      <c r="B261" t="s">
         <v>784</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" t="s">
         <v>785</v>
       </c>
-      <c r="C261" t="s">
-        <v>786</v>
-      </c>
       <c r="D261" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E261" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
+        <v>786</v>
+      </c>
+      <c r="B262" t="s">
         <v>787</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" t="s">
         <v>788</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
         <v>789</v>
       </c>
-      <c r="D262" t="s">
-        <v>790</v>
-      </c>
       <c r="E262" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
+        <v>790</v>
+      </c>
+      <c r="B263" t="s">
         <v>791</v>
       </c>
-      <c r="B263" t="s">
+      <c r="C263" t="s">
         <v>792</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>793</v>
       </c>
-      <c r="D263" t="s">
-        <v>794</v>
-      </c>
       <c r="E263" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
+        <v>794</v>
+      </c>
+      <c r="B264" t="s">
         <v>795</v>
       </c>
-      <c r="B264" t="s">
+      <c r="C264" t="s">
         <v>796</v>
       </c>
-      <c r="C264" t="s">
-        <v>797</v>
-      </c>
       <c r="D264" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E264" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
+        <v>797</v>
+      </c>
+      <c r="B265" t="s">
         <v>798</v>
       </c>
-      <c r="B265" t="s">
+      <c r="C265" t="s">
         <v>799</v>
       </c>
-      <c r="C265" t="s">
-        <v>800</v>
-      </c>
       <c r="D265" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E265" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
+        <v>800</v>
+      </c>
+      <c r="B266" t="s">
         <v>801</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" t="s">
         <v>802</v>
       </c>
-      <c r="C266" t="s">
-        <v>803</v>
-      </c>
       <c r="D266" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E266" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
+        <v>803</v>
+      </c>
+      <c r="B267" t="s">
         <v>804</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C267" t="s">
         <v>805</v>
       </c>
-      <c r="C267" t="s">
-        <v>806</v>
-      </c>
       <c r="D267" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E267" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
+        <v>806</v>
+      </c>
+      <c r="B268" t="s">
         <v>807</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" t="s">
         <v>808</v>
       </c>
-      <c r="C268" t="s">
-        <v>809</v>
-      </c>
       <c r="D268" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E268" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
+        <v>809</v>
+      </c>
+      <c r="B269" t="s">
         <v>810</v>
       </c>
-      <c r="B269" t="s">
+      <c r="D269" t="s">
         <v>811</v>
       </c>
-      <c r="D269" t="s">
-        <v>812</v>
-      </c>
       <c r="E269" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
+        <v>812</v>
+      </c>
+      <c r="B270" t="s">
         <v>813</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C270" t="s">
         <v>814</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
         <v>815</v>
       </c>
-      <c r="D270" t="s">
-        <v>816</v>
-      </c>
       <c r="E270" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" t="s">
+        <v>816</v>
+      </c>
+      <c r="B271" t="s">
         <v>817</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C271" t="s">
         <v>818</v>
       </c>
-      <c r="C271" t="s">
-        <v>819</v>
-      </c>
       <c r="D271" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E271" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
+        <v>819</v>
+      </c>
+      <c r="B272" t="s">
         <v>820</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>821</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
+        <v>815</v>
+      </c>
+      <c r="E272" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
         <v>822</v>
       </c>
-      <c r="D272" t="s">
-        <v>816</v>
-      </c>
-      <c r="E272" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
-      <c r="A273" t="s">
+      <c r="B273" t="s">
         <v>823</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C273" t="s">
         <v>824</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" t="s">
+        <v>815</v>
+      </c>
+      <c r="E273" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
         <v>825</v>
       </c>
-      <c r="D273" t="s">
-        <v>816</v>
-      </c>
-      <c r="E273" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
-      <c r="A274" t="s">
+      <c r="B274" t="s">
         <v>826</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C274" t="s">
         <v>827</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
+        <v>815</v>
+      </c>
+      <c r="E274" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
         <v>828</v>
       </c>
-      <c r="D274" t="s">
-        <v>816</v>
-      </c>
-      <c r="E274" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
-      <c r="A275" t="s">
+      <c r="B275" t="s">
         <v>829</v>
       </c>
-      <c r="B275" t="s">
+      <c r="D275" t="s">
+        <v>815</v>
+      </c>
+      <c r="E275" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
         <v>830</v>
       </c>
-      <c r="D275" t="s">
-        <v>816</v>
-      </c>
-      <c r="E275" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
-      <c r="A276" t="s">
+      <c r="B276" t="s">
         <v>831</v>
       </c>
-      <c r="B276" t="s">
+      <c r="C276" t="s">
         <v>832</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
+        <v>815</v>
+      </c>
+      <c r="E276" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
         <v>833</v>
       </c>
-      <c r="D276" t="s">
-        <v>816</v>
-      </c>
-      <c r="E276" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
-      <c r="A277" t="s">
+      <c r="B277" t="s">
         <v>834</v>
       </c>
-      <c r="B277" t="s">
+      <c r="D277" t="s">
         <v>835</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
+        <v>10</v>
+      </c>
+      <c r="F277" t="s">
         <v>836</v>
       </c>
-      <c r="E277" t="s">
-        <v>11</v>
-      </c>
-      <c r="F277" t="s">
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
         <v>837</v>
       </c>
-      <c r="G277" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
-      <c r="A278" t="s">
+      <c r="B278" t="s">
         <v>838</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>839</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
+        <v>835</v>
+      </c>
+      <c r="E278" t="s">
+        <v>10</v>
+      </c>
+      <c r="F278" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
         <v>840</v>
       </c>
-      <c r="D278" t="s">
+      <c r="B279" t="s">
+        <v>841</v>
+      </c>
+      <c r="C279" t="s">
+        <v>842</v>
+      </c>
+      <c r="D279" t="s">
+        <v>835</v>
+      </c>
+      <c r="E279" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>843</v>
+      </c>
+      <c r="B280" t="s">
+        <v>844</v>
+      </c>
+      <c r="C280" t="s">
+        <v>845</v>
+      </c>
+      <c r="D280" t="s">
+        <v>835</v>
+      </c>
+      <c r="E280" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>846</v>
+      </c>
+      <c r="B281" t="s">
+        <v>847</v>
+      </c>
+      <c r="C281" t="s">
+        <v>848</v>
+      </c>
+      <c r="D281" t="s">
+        <v>835</v>
+      </c>
+      <c r="E281" t="s">
+        <v>10</v>
+      </c>
+      <c r="F281" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>849</v>
+      </c>
+      <c r="B282" t="s">
+        <v>850</v>
+      </c>
+      <c r="C282" t="s">
+        <v>851</v>
+      </c>
+      <c r="D282" t="s">
+        <v>835</v>
+      </c>
+      <c r="E282" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>852</v>
+      </c>
+      <c r="B283" t="s">
+        <v>847</v>
+      </c>
+      <c r="C283" t="s">
+        <v>853</v>
+      </c>
+      <c r="D283" t="s">
+        <v>835</v>
+      </c>
+      <c r="E283" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>854</v>
+      </c>
+      <c r="B284" t="s">
+        <v>855</v>
+      </c>
+      <c r="C284" t="s">
+        <v>856</v>
+      </c>
+      <c r="D284" t="s">
+        <v>835</v>
+      </c>
+      <c r="E284" t="s">
+        <v>10</v>
+      </c>
+      <c r="F284" t="s">
         <v>836</v>
       </c>
-      <c r="E278" t="s">
-        <v>11</v>
-      </c>
-      <c r="F278" t="s">
-        <v>28</v>
-      </c>
-      <c r="G278" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
-      <c r="A279" t="s">
-        <v>841</v>
-      </c>
-      <c r="B279" t="s">
-        <v>842</v>
-      </c>
-      <c r="C279" t="s">
-        <v>843</v>
-      </c>
-      <c r="D279" t="s">
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>857</v>
+      </c>
+      <c r="B285" t="s">
+        <v>858</v>
+      </c>
+      <c r="C285" t="s">
+        <v>859</v>
+      </c>
+      <c r="D285" t="s">
+        <v>835</v>
+      </c>
+      <c r="E285" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>860</v>
+      </c>
+      <c r="B286" t="s">
+        <v>861</v>
+      </c>
+      <c r="C286" t="s">
+        <v>862</v>
+      </c>
+      <c r="D286" t="s">
+        <v>835</v>
+      </c>
+      <c r="E286" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>863</v>
+      </c>
+      <c r="B287" t="s">
+        <v>864</v>
+      </c>
+      <c r="C287" t="s">
+        <v>865</v>
+      </c>
+      <c r="D287" t="s">
+        <v>835</v>
+      </c>
+      <c r="E287" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>866</v>
+      </c>
+      <c r="B288" t="s">
+        <v>867</v>
+      </c>
+      <c r="C288" t="s">
+        <v>868</v>
+      </c>
+      <c r="D288" t="s">
+        <v>835</v>
+      </c>
+      <c r="E288" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>869</v>
+      </c>
+      <c r="B289" t="s">
+        <v>870</v>
+      </c>
+      <c r="C289" t="s">
+        <v>871</v>
+      </c>
+      <c r="D289" t="s">
+        <v>835</v>
+      </c>
+      <c r="E289" t="s">
+        <v>10</v>
+      </c>
+      <c r="F289" t="s">
         <v>836</v>
       </c>
-      <c r="E279" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
-      <c r="A280" t="s">
-        <v>844</v>
-      </c>
-      <c r="B280" t="s">
-        <v>845</v>
-      </c>
-      <c r="C280" t="s">
-        <v>846</v>
-      </c>
-      <c r="D280" t="s">
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>872</v>
+      </c>
+      <c r="B290" t="s">
+        <v>873</v>
+      </c>
+      <c r="C290" t="s">
+        <v>874</v>
+      </c>
+      <c r="D290" t="s">
+        <v>835</v>
+      </c>
+      <c r="E290" t="s">
+        <v>10</v>
+      </c>
+      <c r="F290" t="s">
         <v>836</v>
       </c>
-      <c r="E280" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
-      <c r="A281" t="s">
-        <v>847</v>
-      </c>
-      <c r="B281" t="s">
-        <v>848</v>
-      </c>
-      <c r="C281" t="s">
-        <v>849</v>
-      </c>
-      <c r="D281" t="s">
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>875</v>
+      </c>
+      <c r="B291" t="s">
+        <v>876</v>
+      </c>
+      <c r="C291" t="s">
+        <v>877</v>
+      </c>
+      <c r="D291" t="s">
+        <v>878</v>
+      </c>
+      <c r="E291" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>879</v>
+      </c>
+      <c r="B292" t="s">
+        <v>880</v>
+      </c>
+      <c r="C292" t="s">
+        <v>881</v>
+      </c>
+      <c r="D292" t="s">
+        <v>882</v>
+      </c>
+      <c r="E292" t="s">
+        <v>10</v>
+      </c>
+      <c r="F292" t="s">
         <v>836</v>
       </c>
-      <c r="E281" t="s">
-        <v>11</v>
-      </c>
-      <c r="F281" t="s">
-        <v>28</v>
-      </c>
-      <c r="G281" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
-      <c r="A282" t="s">
-        <v>850</v>
-      </c>
-      <c r="B282" t="s">
-        <v>851</v>
-      </c>
-      <c r="C282" t="s">
-        <v>852</v>
-      </c>
-      <c r="D282" t="s">
-        <v>836</v>
-      </c>
-      <c r="E282" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
-      <c r="A283" t="s">
-        <v>853</v>
-      </c>
-      <c r="B283" t="s">
-        <v>848</v>
-      </c>
-      <c r="C283" t="s">
-        <v>854</v>
-      </c>
-      <c r="D283" t="s">
-        <v>836</v>
-      </c>
-      <c r="E283" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
-      <c r="A284" t="s">
-        <v>855</v>
-      </c>
-      <c r="B284" t="s">
-        <v>856</v>
-      </c>
-      <c r="C284" t="s">
-        <v>857</v>
-      </c>
-      <c r="D284" t="s">
-        <v>836</v>
-      </c>
-      <c r="E284" t="s">
-        <v>11</v>
-      </c>
-      <c r="F284" t="s">
-        <v>837</v>
-      </c>
-      <c r="G284" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
-      <c r="A285" t="s">
-        <v>858</v>
-      </c>
-      <c r="B285" t="s">
-        <v>859</v>
-      </c>
-      <c r="C285" t="s">
-        <v>860</v>
-      </c>
-      <c r="D285" t="s">
-        <v>836</v>
-      </c>
-      <c r="E285" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
-      <c r="A286" t="s">
-        <v>861</v>
-      </c>
-      <c r="B286" t="s">
-        <v>862</v>
-      </c>
-      <c r="C286" t="s">
-        <v>863</v>
-      </c>
-      <c r="D286" t="s">
-        <v>836</v>
-      </c>
-      <c r="E286" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
-      <c r="A287" t="s">
-        <v>864</v>
-      </c>
-      <c r="B287" t="s">
-        <v>865</v>
-      </c>
-      <c r="C287" t="s">
-        <v>866</v>
-      </c>
-      <c r="D287" t="s">
-        <v>836</v>
-      </c>
-      <c r="E287" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
-      <c r="A288" t="s">
-        <v>867</v>
-      </c>
-      <c r="B288" t="s">
-        <v>868</v>
-      </c>
-      <c r="C288" t="s">
-        <v>869</v>
-      </c>
-      <c r="D288" t="s">
-        <v>836</v>
-      </c>
-      <c r="E288" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
-      <c r="A289" t="s">
-        <v>870</v>
-      </c>
-      <c r="B289" t="s">
-        <v>871</v>
-      </c>
-      <c r="C289" t="s">
-        <v>872</v>
-      </c>
-      <c r="D289" t="s">
-        <v>836</v>
-      </c>
-      <c r="E289" t="s">
-        <v>11</v>
-      </c>
-      <c r="F289" t="s">
-        <v>837</v>
-      </c>
-      <c r="G289" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
-      <c r="A290" t="s">
-        <v>873</v>
-      </c>
-      <c r="B290" t="s">
-        <v>874</v>
-      </c>
-      <c r="C290" t="s">
-        <v>875</v>
-      </c>
-      <c r="D290" t="s">
-        <v>836</v>
-      </c>
-      <c r="E290" t="s">
-        <v>11</v>
-      </c>
-      <c r="F290" t="s">
-        <v>837</v>
-      </c>
-      <c r="G290" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
-      <c r="A291" t="s">
-        <v>876</v>
-      </c>
-      <c r="B291" t="s">
-        <v>877</v>
-      </c>
-      <c r="C291" t="s">
-        <v>878</v>
-      </c>
-      <c r="D291" t="s">
-        <v>879</v>
-      </c>
-      <c r="E291" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
-      <c r="A292" t="s">
-        <v>880</v>
-      </c>
-      <c r="B292" t="s">
-        <v>881</v>
-      </c>
-      <c r="C292" t="s">
-        <v>882</v>
-      </c>
-      <c r="D292" t="s">
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
         <v>883</v>
       </c>
-      <c r="E292" t="s">
-        <v>11</v>
-      </c>
-      <c r="F292" t="s">
-        <v>837</v>
-      </c>
-      <c r="G292" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
-      <c r="A293" t="s">
+      <c r="B293" t="s">
         <v>884</v>
       </c>
-      <c r="B293" t="s">
+      <c r="C293" t="s">
         <v>885</v>
       </c>
-      <c r="C293" t="s">
+      <c r="D293" t="s">
         <v>886</v>
       </c>
-      <c r="D293" t="s">
+      <c r="E293" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
         <v>887</v>
       </c>
-      <c r="E293" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
-      <c r="A294" t="s">
+      <c r="B294" t="s">
         <v>888</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C294" t="s">
         <v>889</v>
       </c>
-      <c r="C294" t="s">
+      <c r="D294" t="s">
+        <v>886</v>
+      </c>
+      <c r="E294" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
         <v>890</v>
       </c>
-      <c r="D294" t="s">
-        <v>887</v>
-      </c>
-      <c r="E294" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
-      <c r="A295" t="s">
+      <c r="B295" t="s">
         <v>891</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" t="s">
         <v>892</v>
       </c>
-      <c r="C295" t="s">
+      <c r="D295" t="s">
         <v>893</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
         <v>894</v>
       </c>
-      <c r="E295" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
-      <c r="A296" t="s">
+      <c r="B296" t="s">
         <v>895</v>
       </c>
-      <c r="B296" t="s">
+      <c r="D296" t="s">
+        <v>893</v>
+      </c>
+      <c r="E296" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
         <v>896</v>
       </c>
-      <c r="D296" t="s">
-        <v>894</v>
-      </c>
-      <c r="E296" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7">
-      <c r="A297" t="s">
+      <c r="B297" t="s">
         <v>897</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" t="s">
         <v>898</v>
       </c>
-      <c r="C297" t="s">
+      <c r="D297" t="s">
+        <v>893</v>
+      </c>
+      <c r="E297" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
         <v>899</v>
       </c>
-      <c r="D297" t="s">
-        <v>894</v>
-      </c>
-      <c r="E297" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7">
-      <c r="A298" t="s">
+      <c r="B298" t="s">
         <v>900</v>
       </c>
-      <c r="B298" t="s">
+      <c r="D298" t="s">
+        <v>893</v>
+      </c>
+      <c r="E298" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
         <v>901</v>
       </c>
-      <c r="D298" t="s">
-        <v>894</v>
-      </c>
-      <c r="E298" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7">
-      <c r="A299" t="s">
+      <c r="B299" t="s">
         <v>902</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C299" t="s">
         <v>903</v>
       </c>
-      <c r="C299" t="s">
+      <c r="D299" t="s">
+        <v>893</v>
+      </c>
+      <c r="E299" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
         <v>904</v>
       </c>
-      <c r="D299" t="s">
-        <v>894</v>
-      </c>
-      <c r="E299" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7">
-      <c r="A300" t="s">
+      <c r="B300" t="s">
         <v>905</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C300" t="s">
         <v>906</v>
       </c>
-      <c r="C300" t="s">
+      <c r="D300" t="s">
+        <v>893</v>
+      </c>
+      <c r="E300" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
         <v>907</v>
       </c>
-      <c r="D300" t="s">
-        <v>894</v>
-      </c>
-      <c r="E300" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7">
-      <c r="A301" t="s">
+      <c r="B301" t="s">
         <v>908</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" t="s">
         <v>909</v>
       </c>
-      <c r="C301" t="s">
+      <c r="D301" t="s">
+        <v>893</v>
+      </c>
+      <c r="E301" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
         <v>910</v>
       </c>
-      <c r="D301" t="s">
-        <v>894</v>
-      </c>
-      <c r="E301" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
-      <c r="A302" t="s">
+      <c r="B302" t="s">
         <v>911</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>912</v>
       </c>
-      <c r="C302" t="s">
+      <c r="D302" t="s">
         <v>913</v>
       </c>
-      <c r="D302" t="s">
+      <c r="E302" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
         <v>914</v>
       </c>
-      <c r="E302" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
-      <c r="A303" t="s">
+      <c r="B303" t="s">
         <v>915</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" t="s">
         <v>916</v>
       </c>
-      <c r="C303" t="s">
+      <c r="D303" t="s">
+        <v>913</v>
+      </c>
+      <c r="E303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
         <v>917</v>
       </c>
-      <c r="D303" t="s">
-        <v>914</v>
-      </c>
-      <c r="E303" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7">
-      <c r="A304" t="s">
+      <c r="B304" t="s">
         <v>918</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C304" t="s">
         <v>919</v>
       </c>
-      <c r="C304" t="s">
-        <v>920</v>
-      </c>
       <c r="D304" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E304" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:5">
       <c r="A305" t="s">
+        <v>920</v>
+      </c>
+      <c r="B305" t="s">
         <v>921</v>
       </c>
-      <c r="B305" t="s">
+      <c r="C305" t="s">
         <v>922</v>
       </c>
-      <c r="C305" t="s">
-        <v>923</v>
-      </c>
       <c r="D305" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E305" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306" t="s">
+        <v>923</v>
+      </c>
+      <c r="B306" t="s">
         <v>924</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C306" t="s">
         <v>925</v>
       </c>
-      <c r="C306" t="s">
-        <v>926</v>
-      </c>
       <c r="D306" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E306" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
+        <v>926</v>
+      </c>
+      <c r="B307" t="s">
         <v>927</v>
       </c>
-      <c r="B307" t="s">
+      <c r="C307" t="s">
         <v>928</v>
       </c>
-      <c r="C307" t="s">
+      <c r="D307" t="s">
         <v>929</v>
       </c>
-      <c r="D307" t="s">
-        <v>930</v>
-      </c>
       <c r="E307" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
+        <v>930</v>
+      </c>
+      <c r="B308" t="s">
         <v>931</v>
       </c>
-      <c r="B308" t="s">
+      <c r="C308" t="s">
         <v>932</v>
       </c>
-      <c r="C308" t="s">
+      <c r="D308" t="s">
         <v>933</v>
       </c>
-      <c r="D308" t="s">
-        <v>934</v>
-      </c>
       <c r="E308" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
+        <v>934</v>
+      </c>
+      <c r="B309" t="s">
         <v>935</v>
       </c>
-      <c r="B309" t="s">
+      <c r="C309" t="s">
         <v>936</v>
       </c>
-      <c r="C309" t="s">
-        <v>937</v>
-      </c>
       <c r="D309" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E309" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
+        <v>937</v>
+      </c>
+      <c r="B310" t="s">
         <v>938</v>
       </c>
-      <c r="B310" t="s">
+      <c r="D310" t="s">
         <v>939</v>
       </c>
-      <c r="D310" t="s">
-        <v>940</v>
-      </c>
       <c r="E310" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
+        <v>940</v>
+      </c>
+      <c r="B311" t="s">
         <v>941</v>
       </c>
-      <c r="B311" t="s">
+      <c r="C311" t="s">
         <v>942</v>
       </c>
-      <c r="C311" t="s">
+      <c r="D311" t="s">
         <v>943</v>
       </c>
-      <c r="D311" t="s">
-        <v>944</v>
-      </c>
       <c r="E311" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
+        <v>944</v>
+      </c>
+      <c r="B312" t="s">
         <v>945</v>
       </c>
-      <c r="B312" t="s">
-        <v>946</v>
-      </c>
       <c r="D312" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E312" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
+        <v>946</v>
+      </c>
+      <c r="B313" t="s">
         <v>947</v>
       </c>
-      <c r="B313" t="s">
+      <c r="C313" t="s">
         <v>948</v>
       </c>
-      <c r="C313" t="s">
-        <v>949</v>
-      </c>
       <c r="D313" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E313" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
+        <v>949</v>
+      </c>
+      <c r="B314" t="s">
         <v>950</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C314" t="s">
         <v>951</v>
       </c>
-      <c r="C314" t="s">
+      <c r="D314" t="s">
         <v>952</v>
       </c>
-      <c r="D314" t="s">
-        <v>953</v>
-      </c>
       <c r="E314" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="315" spans="1:5">
       <c r="A315" t="s">
+        <v>953</v>
+      </c>
+      <c r="B315" t="s">
         <v>954</v>
       </c>
-      <c r="B315" t="s">
+      <c r="C315" t="s">
         <v>955</v>
       </c>
-      <c r="C315" t="s">
-        <v>956</v>
-      </c>
       <c r="D315" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E315" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
+        <v>956</v>
+      </c>
+      <c r="B316" t="s">
         <v>957</v>
       </c>
-      <c r="B316" t="s">
+      <c r="C316" t="s">
         <v>958</v>
       </c>
-      <c r="C316" t="s">
-        <v>959</v>
-      </c>
       <c r="D316" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E316" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
+        <v>959</v>
+      </c>
+      <c r="B317" t="s">
         <v>960</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C317" t="s">
         <v>961</v>
       </c>
-      <c r="C317" t="s">
-        <v>962</v>
-      </c>
       <c r="D317" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E317" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
+        <v>962</v>
+      </c>
+      <c r="B318" t="s">
         <v>963</v>
       </c>
-      <c r="B318" t="s">
+      <c r="C318" t="s">
         <v>964</v>
       </c>
-      <c r="C318" t="s">
-        <v>965</v>
-      </c>
       <c r="D318" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E318" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="319" spans="1:5">
       <c r="A319" t="s">
+        <v>965</v>
+      </c>
+      <c r="B319" t="s">
         <v>966</v>
       </c>
-      <c r="B319" t="s">
+      <c r="C319" t="s">
         <v>967</v>
       </c>
-      <c r="C319" t="s">
-        <v>968</v>
-      </c>
       <c r="D319" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E319" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
+        <v>968</v>
+      </c>
+      <c r="B320" t="s">
         <v>969</v>
       </c>
-      <c r="B320" t="s">
+      <c r="C320" t="s">
         <v>970</v>
       </c>
-      <c r="C320" t="s">
+      <c r="D320" t="s">
+        <v>952</v>
+      </c>
+      <c r="E320" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" t="s">
         <v>971</v>
       </c>
-      <c r="D320" t="s">
-        <v>953</v>
-      </c>
-      <c r="E320" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
-      <c r="A321" t="s">
+      <c r="B321" t="s">
         <v>972</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C321" t="s">
         <v>973</v>
       </c>
-      <c r="C321" t="s">
+      <c r="D321" t="s">
+        <v>952</v>
+      </c>
+      <c r="E321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" t="s">
         <v>974</v>
       </c>
-      <c r="D321" t="s">
-        <v>953</v>
-      </c>
-      <c r="E321" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
-      <c r="A322" t="s">
+      <c r="B322" t="s">
         <v>975</v>
       </c>
-      <c r="B322" t="s">
+      <c r="C322" t="s">
         <v>976</v>
       </c>
-      <c r="C322" t="s">
+      <c r="D322" t="s">
+        <v>952</v>
+      </c>
+      <c r="E322" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" t="s">
         <v>977</v>
       </c>
-      <c r="D322" t="s">
-        <v>953</v>
-      </c>
-      <c r="E322" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7">
-      <c r="A323" t="s">
+      <c r="B323" t="s">
         <v>978</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323" t="s">
         <v>979</v>
       </c>
-      <c r="C323" t="s">
+      <c r="D323" t="s">
         <v>980</v>
       </c>
-      <c r="D323" t="s">
+      <c r="E323" t="s">
+        <v>10</v>
+      </c>
+      <c r="F323" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" t="s">
         <v>981</v>
       </c>
-      <c r="E323" t="s">
-        <v>11</v>
-      </c>
-      <c r="F323" t="s">
-        <v>837</v>
-      </c>
-      <c r="G323" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
-      <c r="A324" t="s">
+      <c r="B324" t="s">
         <v>982</v>
       </c>
-      <c r="B324" t="s">
+      <c r="C324" t="s">
         <v>983</v>
       </c>
-      <c r="C324" t="s">
-        <v>984</v>
-      </c>
       <c r="D324" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E324" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="988">
   <si>
     <t>code</t>
   </si>
@@ -91,10 +91,10 @@
     <t>11230</t>
   </si>
   <si>
-    <t>Basic life skills for youth and adults</t>
-  </si>
-  <si>
-    <t>Formal and non-formal education for basic life skills for young people and adults (adults education); literacy and numeracy training. Excludes health education (12261) and activities related to prevention of noncommunicable diseases. (123xx).</t>
+    <t>Basic life skills for adults</t>
+  </si>
+  <si>
+    <t>Formal and non-formal education for basic life skills for adults (adults education); literacy and numeracy training. Excludes health education (12261) and activities related to prevention of noncommunicable diseases. (123xx).</t>
   </si>
   <si>
     <t>Insufficiently granular</t>
@@ -133,16 +133,25 @@
     <t>School feeding</t>
   </si>
   <si>
-    <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including “take-home” food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child’s regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children’s hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
+    <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
+  </si>
+  <si>
+    <t>11260</t>
+  </si>
+  <si>
+    <t>Lower secondary education</t>
+  </si>
+  <si>
+    <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
     <t>11320</t>
   </si>
   <si>
-    <t>Secondary education</t>
-  </si>
-  <si>
-    <t>Second cycle systematic instruction at both junior and senior levels.</t>
+    <t>Upper Secondary Education (modified and includes data from 11322)</t>
+  </si>
+  <si>
+    <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
     <t>113</t>
@@ -151,10 +160,7 @@
     <t>11321</t>
   </si>
   <si>
-    <t>Lower secondary education</t>
-  </si>
-  <si>
-    <t>Second cycle systematic instruction at junior level.</t>
+    <t>withdrawn</t>
   </si>
   <si>
     <t>11322</t>
@@ -280,7 +286,7 @@
     <t>Infectious disease control</t>
   </si>
   <si>
-    <t>Immunisation; prevention and control of infectious and parasite diseases, except malaria (12262), tuberculosis (12263), HIV/AIDS and other STDs (13040). It includes diarrheal diseases, vector-borne diseases (e.g. river blindness and guinea worm), viral diseases, mycosis, helminthiasis, zoonosis, diseases by other bacteria and viruses, pediculosis, etc.</t>
+    <t>Immunisation; prevention and control of infectious and parasite diseases, except malaria (12262), tuberculosis (12263), COVID-19 (12264), HIV/AIDS and other STDs (13040). It includes diarrheal diseases, vector-borne diseases (e.g. river blindness and guinea worm), viral diseases, mycosis, helminthiasis, zoonosis, diseases by other bacteria and viruses, pediculosis, etc.</t>
   </si>
   <si>
     <t>12261</t>
@@ -310,6 +316,15 @@
     <t>Immunisation, prevention and control of tuberculosis.</t>
   </si>
   <si>
+    <t>12264</t>
+  </si>
+  <si>
+    <t>COVID-19 control</t>
+  </si>
+  <si>
+    <t>All activities related to COVID-19 control e.g. information, education and communication; testing; prevention; immunisation, treatment, care.</t>
+  </si>
+  <si>
     <t>12281</t>
   </si>
   <si>
@@ -571,7 +586,7 @@
     <t>Anti-corruption organisations and institutions</t>
   </si>
   <si>
-    <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens’ organisations directly concerned with corruption.</t>
+    <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
     <t>15114</t>
@@ -628,9 +643,6 @@
     <t>Strengthening financial and managerial accountability; public expenditure management; improving financial management systems; tax assessment procedures; budget drafting; field auditing; measures against waste, fraud and corruption.</t>
   </si>
   <si>
-    <t>withdrawn</t>
-  </si>
-  <si>
     <t>15121</t>
   </si>
   <si>
@@ -823,7 +835,7 @@
     <t>Democratic participation and civil society</t>
   </si>
   <si>
-    <t>Support to the exercise of democracy and diverse forms of participation of citizens beyond elections (15151); direct democracy instruments such as referenda and citizens’ initiatives; support to organisations to represent and advocate for their members, to monitor, engage and hold governments to account, and to help citizens learn to act in the public sphere; curricula and teaching for civic education at various levels. (This purpose code is restricted to activities targeting governance issues. When assistance to civil society is for non-governance purposes use other appropriate purpose codes.)</t>
+    <t>Support to the exercise of democracy and diverse forms of participation of citizens beyond elections (15151); direct democracy instruments such as referenda and citizens' initiatives; support to organisations to represent and advocate for their members, to monitor, engage and hold governments to account, and to help citizens learn to act in the public sphere; curricula and teaching for civic education at various levels. (This purpose code is restricted to activities targeting governance issues. When assistance to civil society is for non-governance purposes use other appropriate purpose codes.)</t>
   </si>
   <si>
     <t>15151</t>
@@ -841,7 +853,7 @@
     <t>Legislatures and political parties</t>
   </si>
   <si>
-    <t>Assistance to strengthen key functions of legislatures/ parliaments including subnational assemblies and councils (representation; oversight; legislation), such as improving the capacity of legislative bodies, improving legislatures’ committees and administrative procedures,; research and information management systems; providing training programmes for legislators and support personnel. Assistance to political parties and strengthening of party systems.</t>
+    <t>Assistance to strengthen key functions of legislatures/ parliaments including subnational assemblies and councils (representation; oversight; legislation), such as improving the capacity of legislative bodies, improving legislatures' committees and administrative procedures,; research and information management systems; providing training programmes for legislators and support personnel. Assistance to political parties and strengthening of party systems.</t>
   </si>
   <si>
     <t>15153</t>
@@ -919,10 +931,10 @@
     <t>15170</t>
   </si>
   <si>
-    <t>Women’s rights organisations and movements, and government institutions</t>
-  </si>
-  <si>
-    <t>Support for feminist, women-led and women’s rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
+    <t>Women's rights organisations and movements, and government institutions</t>
+  </si>
+  <si>
+    <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
     <t>15180</t>
@@ -949,7 +961,7 @@
     <t>Facilitation of orderly, safe, regular and responsible migration and mobility</t>
   </si>
   <si>
-    <t>Assistance to developing countries that facilitates the orderly, safe, regular and responsible migration and mobility of people. This includes:• Capacity building in migration and mobility policy, analysis, planning and management. This includes support to facilitate safe and regular migration and address irregular migration, engagement with diaspora and programmes enhancing the development impact of remittances and/or their use for developmental projects in developing countries.• Measures to improve migrant labour recruitment systems in developing countries.• Capacity building for strategy and policy development as well as legal and judicial development (including border management) in developing countries. This includes support to address and reduce vulnerabilities in migration, and strengthen the transnational response to smuggling of migrants and preventing and combating trafficking in human beings.• Support to effective strategies to ensure international protection and the right to asylum.• Support to effective strategies to ensure access to justice and assistance for displaced persons.• Assistance to migrants for their safe, dignified, informed and voluntary return to their country of origin (covers only returns from another developing country; assistance to forced returns is excluded from ODA).• Assistance to migrants for their sustainable reintegration in their country of origin (use code 93010 for pre-departure assistance provided in donor countries in the context of voluntary returns). Activities that pursue first and foremost providers’ interest are excluded from ODA. Activities addressing the root causes of forced displacement and irregular migration should not be coded here, but under their relevant sector of intervention. In addition, use code 15136 for support to countries' authorities for immigration affairs and services (optional), code 24050 for programmes aiming at reducing the sending costs of remittances, code 72010 for humanitarian aspects of assistance to refugees and internally displaced persons (IDPs) such as delivery of emergency services and humanitarian protection. Use code 93010 when expenditure is for the temporary sustenance of refugees in the donor country, including for their voluntary return and for their reintegration when support is provided in a donor country in connection with the return from that donor country (i.e. pre-departure assistance), or voluntary resettlement in a third developed country.</t>
+    <t>Assistance to developing countries that facilitates the orderly, safe, regular and responsible migration and mobility of people. This includes:• Capacity building in migration and mobility policy, analysis, planning and management. This includes support to facilitate safe and regular migration and address irregular migration, engagement with diaspora and programmes enhancing the development impact of remittances and/or their use for developmental projects in developing countries.• Measures to improve migrant labour recruitment systems in developing countries.• Capacity building for strategy and policy development as well as legal and judicial development (including border management) in developing countries. This includes support to address and reduce vulnerabilities in migration, and strengthen the transnational response to smuggling of migrants and preventing and combating trafficking in human beings.• Support to effective strategies to ensure international protection and the right to asylum.• Support to effective strategies to ensure access to justice and assistance for displaced persons.• Assistance to migrants for their safe, dignified, informed and voluntary return to their country of origin (covers only returns from another developing country; assistance to forced returns is excluded from ODA).• Assistance to migrants for their sustainable reintegration in their country of origin (use code 93010 for pre-departure assistance provided in donor countries in the context of voluntary returns). Activities that pursue first and foremost providers' interest are excluded from ODA. Activities addressing the root causes of forced displacement and irregular migration should not be coded here, but under their relevant sector of intervention. In addition, use code 15136 for support to countries' authorities for immigration affairs and services (optional), code 24050 for programmes aiming at reducing the sending costs of remittances, code 72010 for humanitarian aspects of assistance to refugees and internally displaced persons (IDPs) such as delivery of emergency services and humanitarian protection. Use code 93010 when expenditure is for the temporary sustenance of refugees in the donor country, including for their voluntary return and for their reintegration when support is provided in a donor country in connection with the return from that donor country (i.e. pre-departure assistance), or voluntary resettlement in a third developed country.</t>
   </si>
   <si>
     <t>15196</t>
@@ -1162,7 +1174,7 @@
     <t>16070</t>
   </si>
   <si>
-    <t>Labour Rights</t>
+    <t>Labour rights</t>
   </si>
   <si>
     <t>Advocacy for international labour standards, labour law, fundamental principles and rights at work (child labour, forced labour, non-discrimination in the workplace, freedom of association and collective bargaining); formalisation of informal work, occupational safety and health.</t>
@@ -1171,7 +1183,7 @@
     <t>16080</t>
   </si>
   <si>
-    <t>Social Dialogue</t>
+    <t>Social dialogue</t>
   </si>
   <si>
     <t>Capacity building and advice in support of social dialogue; support to social dialogue institutions, bodies and mechanisms; capacity building of workers' and employers' organisations.</t>
@@ -1828,7 +1840,7 @@
     <t>25010</t>
   </si>
   <si>
-    <t>Business Policy and Administration</t>
+    <t>Business policy and administration</t>
   </si>
   <si>
     <t>Public sector policies and institution support to the business environment and investment climate, including business regulations, property rights, non-discrimination, investment promotion, competition policy, enterprises law, private-public partnerships.</t>
@@ -1858,10 +1870,10 @@
     <t>25040</t>
   </si>
   <si>
-    <t>Responsible Business Conduct</t>
-  </si>
-  <si>
-    <t>Support to policy reform, implementation and enforcement of responsible business conduct (RBC) principles and standards as well as facilitation of responsible business practices by companies. Includes establishing and enforcing a legal and regulatory framework to protect stakeholder rights and the environment, rewarding best performers; exemplifying RBC in government economic activities, such as state-owned enterprises’ operations or public procurement; support to the implementation of the OECD Guidelines for MNEs, including disclosure, human rights, employment and industrial relations, environment, combating bribery, consumer interests, science and technology, competition and taxation.</t>
+    <t>Responsible business conduct</t>
+  </si>
+  <si>
+    <t>Support to policy reform, implementation and enforcement of responsible business conduct (RBC) principles and standards as well as facilitation of responsible business practices by companies. Includes establishing and enforcing a legal and regulatory framework to protect stakeholder rights and the environment, rewarding best performers; exemplifying RBC in government economic activities, such as state-owned enterprises' operations or public procurement; support to the implementation of the OECD Guidelines for MNEs, including disclosure, human rights, employment and industrial relations, environment, combating bribery, consumer interests, science and technology, competition and taxation.</t>
   </si>
   <si>
     <t>31110</t>
@@ -2014,7 +2026,7 @@
     <t>Agricultural co-operatives</t>
   </si>
   <si>
-    <t>Including farmers’ organisations.</t>
+    <t>Including farmers' organisations.</t>
   </si>
   <si>
     <t>31195</t>
@@ -2422,7 +2434,7 @@
     <t>Multilateral trade negotiations</t>
   </si>
   <si>
-    <t>Support developing countries’ effective participation in multilateral trade negotiations, including training of negotiators, assessing impacts of negotiations; accession to the World Trade Organisation (WTO) and other multilateral trade-related organisations.</t>
+    <t>Support developing countries' effective participation in multilateral trade negotiations, including training of negotiators, assessing impacts of negotiations; accession to the World Trade Organisation (WTO) and other multilateral trade-related organisations.</t>
   </si>
   <si>
     <t>33150</t>
@@ -2476,7 +2488,7 @@
     <t>41030</t>
   </si>
   <si>
-    <t>Bio-diversity</t>
+    <t>Biodiversity</t>
   </si>
   <si>
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
@@ -2800,7 +2812,7 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
-    <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction (“build back better”) which is reportable against relevant sectors.</t>
+    <t>Social and economic rehabilitation in the aftermath of emergencies to facilitate recovery and resilience building and enable populations to restore their livelihoods in the wake of an emergency situation (e.g. trauma counselling and treatment, employment programmes). Includes infrastructure necessary for the delivery of humanitarian aid; restoring pre-existing essential infrastructure and facilities (e.g. water and sanitation, shelter, health care services, education); rehabilitation of basic agricultural inputs and livestock. Excludes longer-term reconstruction ('build back better') which is reportable against relevant sectors.</t>
   </si>
   <si>
     <t>730</t>
@@ -2908,7 +2920,7 @@
     <t>Refugees/asylum seekers in donor countries - other temporary sustenance</t>
   </si>
   <si>
-    <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months: temporary sustenance other than food and shelter (code 93011), training (93012) and health (93013), i.e. cash “pocket money” to cover subsistence costs and assistance in the asylum procedure: translation of documents, legal and administrative counselling, interpretation services.</t>
+    <t>Costs incurred in donor countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months: temporary sustenance other than food and shelter (code 93011), training (93012) and health (93013), i.e. cash 'pocket money' to cover subsistence costs and assistance in the asylum procedure: translation of documents, legal and administrative counselling, interpretation services.</t>
   </si>
   <si>
     <t>93015</t>
@@ -3297,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F324"/>
+  <dimension ref="A1:F328"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3504,30 +3516,30 @@
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="D13" t="s">
-        <v>43</v>
-      </c>
       <c r="E13" t="s">
         <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3535,47 +3547,47 @@
         <v>47</v>
       </c>
       <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
         <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
         <v>53</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -3583,16 +3595,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -3600,16 +3612,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
         <v>60</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>61</v>
       </c>
-      <c r="C18" t="s">
-        <v>62</v>
-      </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -3617,16 +3629,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" t="s">
-        <v>63</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -3634,16 +3646,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
         <v>67</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>68</v>
       </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -3651,16 +3663,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
         <v>70</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>71</v>
       </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -3668,16 +3680,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>74</v>
       </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -3685,16 +3697,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
         <v>76</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>77</v>
       </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -3702,16 +3714,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -3719,16 +3731,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -3736,16 +3748,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -3753,16 +3765,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -3770,16 +3782,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -3787,16 +3799,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -3804,16 +3816,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -3821,16 +3833,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -3838,16 +3850,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -3855,16 +3867,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -3872,16 +3884,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -3889,16 +3901,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -3906,16 +3918,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -3923,16 +3935,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -3940,16 +3952,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -3957,16 +3969,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -3974,16 +3986,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -3991,16 +4003,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -4008,16 +4020,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -4025,16 +4037,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -4042,16 +4054,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -4059,16 +4071,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -4076,16 +4088,16 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -4093,16 +4105,16 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -4110,16 +4122,16 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -4127,16 +4139,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B49" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -4144,16 +4156,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -4161,16 +4173,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -4178,16 +4190,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D52" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -4195,16 +4207,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -4212,93 +4224,87 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B54" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D54" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B56" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D56" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B57" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -4309,33 +4315,36 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D59" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B60" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C60" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D60" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -4343,33 +4352,36 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B61" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D61" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D62" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -4377,33 +4389,33 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B63" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D63" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E63" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D64" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -4411,16 +4423,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C65" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D65" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -4428,33 +4440,33 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B66" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B67" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C67" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -4462,16 +4474,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -4479,16 +4491,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B69" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C69" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -4496,16 +4508,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C70" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -4513,16 +4525,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -4530,16 +4542,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B72" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C72" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -4547,36 +4559,33 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B73" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C73" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D73" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C74" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -4584,16 +4593,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -4601,33 +4610,36 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B76" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C76" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
+      </c>
+      <c r="F76" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C77" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -4635,16 +4647,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C78" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D78" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -4652,16 +4664,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B79" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D79" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -4669,13 +4681,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>249</v>
+      </c>
+      <c r="C80" t="s">
+        <v>250</v>
       </c>
       <c r="D80" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -4683,33 +4698,33 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D81" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E81" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C82" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -4717,16 +4732,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
-        <v>262</v>
-      </c>
-      <c r="C83" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D83" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -4734,33 +4746,33 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B85" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -4768,16 +4780,16 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B86" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -4785,16 +4797,16 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B87" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -4802,16 +4814,16 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B88" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C88" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D88" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -4819,16 +4831,16 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B89" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C89" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -4836,13 +4848,16 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B90" t="s">
-        <v>283</v>
+        <v>278</v>
+      </c>
+      <c r="C90" t="s">
+        <v>279</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -4850,16 +4865,16 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B91" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -4867,16 +4882,16 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B92" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C92" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -4884,135 +4899,132 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B93" t="s">
-        <v>271</v>
-      </c>
-      <c r="C93" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D93" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E93" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D94" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E94" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B95" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C95" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E95" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B96" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="C96" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D96" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E96" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B97" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C97" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D97" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B98" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C98" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C99" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D99" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C100" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D100" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -5020,16 +5032,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B101" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C101" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D101" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -5037,16 +5049,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B102" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D102" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -5054,16 +5066,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B103" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C103" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D103" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -5071,16 +5083,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B104" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C104" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D104" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -5088,16 +5100,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B105" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C105" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D105" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -5105,16 +5117,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B106" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C106" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D106" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -5122,16 +5134,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B107" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C107" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D107" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -5139,36 +5151,33 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C108" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D108" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
-      </c>
-      <c r="F108" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B109" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C109" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D109" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -5176,16 +5185,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B110" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C110" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D110" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -5193,16 +5202,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B111" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="D111" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -5210,33 +5219,36 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B112" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C112" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="D112" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
+      </c>
+      <c r="F112" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B113" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C113" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D113" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -5244,16 +5256,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B114" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C114" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D114" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -5261,16 +5273,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C115" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D115" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -5278,16 +5290,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C116" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D116" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -5295,16 +5307,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B117" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C117" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D117" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -5312,36 +5324,33 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B118" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C118" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="D118" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
-      </c>
-      <c r="F118" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B119" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C119" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D119" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -5349,16 +5358,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B120" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C120" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D120" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
@@ -5366,16 +5375,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C121" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D121" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
@@ -5383,27 +5392,36 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B122" t="s">
-        <v>378</v>
+        <v>370</v>
+      </c>
+      <c r="C122" t="s">
+        <v>371</v>
       </c>
       <c r="D122" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
+      </c>
+      <c r="F122" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B123" t="s">
-        <v>380</v>
+        <v>373</v>
+      </c>
+      <c r="C123" t="s">
+        <v>374</v>
       </c>
       <c r="D123" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
@@ -5411,16 +5429,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B124" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C124" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D124" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
@@ -5428,16 +5446,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B125" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C125" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D125" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
@@ -5445,36 +5463,27 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B126" t="s">
-        <v>388</v>
-      </c>
-      <c r="C126" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
-      </c>
-      <c r="F126" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B127" t="s">
-        <v>392</v>
-      </c>
-      <c r="C127" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
@@ -5482,16 +5491,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B128" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C128" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -5499,16 +5508,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B129" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C129" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
@@ -5516,16 +5525,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B130" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C130" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D130" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -5536,16 +5545,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C131" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D131" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -5553,16 +5562,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B132" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C132" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D132" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -5570,16 +5579,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B133" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C133" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -5587,33 +5596,36 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C134" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D134" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
+      </c>
+      <c r="F134" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B135" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D135" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -5621,16 +5633,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C136" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D136" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -5638,16 +5650,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B137" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C137" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D137" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -5655,16 +5667,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B138" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C138" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D138" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -5672,13 +5684,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B139" t="s">
-        <v>428</v>
+        <v>420</v>
+      </c>
+      <c r="C139" t="s">
+        <v>421</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -5686,33 +5701,33 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B140" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C140" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="D140" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
-      </c>
-      <c r="F140" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>434</v>
+        <v>426</v>
+      </c>
+      <c r="C141" t="s">
+        <v>427</v>
       </c>
       <c r="D141" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -5720,16 +5735,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C142" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D142" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -5737,16 +5752,13 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="B143" t="s">
-        <v>439</v>
-      </c>
-      <c r="C143" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D143" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -5754,33 +5766,33 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B144" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="C144" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D144" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B145" t="s">
-        <v>445</v>
-      </c>
-      <c r="C145" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="D145" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -5788,16 +5800,16 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B146" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C146" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D146" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -5805,381 +5817,381 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B147" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C147" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D147" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E147" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B148" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C148" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D148" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E148" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B149" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C149" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D149" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E149" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B150" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C150" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D150" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="E150" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B151" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C151" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D151" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E151" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B152" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C152" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D152" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E152" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B153" t="s">
-        <v>470</v>
+        <v>462</v>
+      </c>
+      <c r="C153" t="s">
+        <v>463</v>
       </c>
       <c r="D153" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E153" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B154" t="s">
-        <v>472</v>
+        <v>465</v>
+      </c>
+      <c r="C154" t="s">
+        <v>466</v>
       </c>
       <c r="D154" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E154" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B155" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C155" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D155" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E155" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B156" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C156" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="D156" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E156" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B157" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D157" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E157" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B158" t="s">
-        <v>482</v>
-      </c>
-      <c r="C158" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D158" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E158" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B159" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C159" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="D159" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E159" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B160" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C160" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="D160" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E160" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B161" t="s">
-        <v>491</v>
-      </c>
-      <c r="C161" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D161" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E161" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B162" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C162" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D162" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E162" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B163" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C163" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="D163" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E163" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B164" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="C164" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D164" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="E164" t="s">
-        <v>10</v>
-      </c>
-      <c r="F164" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B165" t="s">
-        <v>503</v>
+        <v>495</v>
+      </c>
+      <c r="C165" t="s">
+        <v>496</v>
       </c>
       <c r="D165" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="E165" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B166" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C166" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D166" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="E166" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B167" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C167" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D167" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="E167" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B168" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="C168" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D168" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
+      </c>
+      <c r="F168" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B169" t="s">
-        <v>511</v>
-      </c>
-      <c r="C169" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D169" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -6187,16 +6199,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B170" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C170" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D170" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
@@ -6204,16 +6216,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B171" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="C171" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D171" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
@@ -6221,16 +6233,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B172" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="C172" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="D172" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -6238,16 +6250,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B173" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C173" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D173" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
@@ -6255,16 +6267,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B174" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C174" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="D174" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
@@ -6272,16 +6284,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B175" t="s">
-        <v>529</v>
+        <v>481</v>
       </c>
       <c r="C175" t="s">
-        <v>486</v>
+        <v>522</v>
       </c>
       <c r="D175" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E175" t="s">
         <v>10</v>
@@ -6289,16 +6301,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B176" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C176" t="s">
-        <v>489</v>
+        <v>525</v>
       </c>
       <c r="D176" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -6306,16 +6318,16 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B177" t="s">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="C177" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D177" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E177" t="s">
         <v>10</v>
@@ -6323,16 +6335,16 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B178" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C178" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D178" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E178" t="s">
         <v>10</v>
@@ -6340,16 +6352,16 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B179" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C179" t="s">
-        <v>539</v>
+        <v>490</v>
       </c>
       <c r="D179" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E179" t="s">
         <v>10</v>
@@ -6357,16 +6369,16 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B180" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C180" t="s">
-        <v>543</v>
+        <v>493</v>
       </c>
       <c r="D180" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E180" t="s">
         <v>10</v>
@@ -6374,16 +6386,16 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B181" t="s">
-        <v>545</v>
+        <v>484</v>
       </c>
       <c r="C181" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D181" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E181" t="s">
         <v>10</v>
@@ -6391,16 +6403,16 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B182" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="C182" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D182" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E182" t="s">
         <v>10</v>
@@ -6408,16 +6420,16 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="B183" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="C183" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D183" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E183" t="s">
         <v>10</v>
@@ -6425,16 +6437,16 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B184" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C184" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="D184" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E184" t="s">
         <v>10</v>
@@ -6442,16 +6454,16 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B185" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C185" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D185" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
@@ -6459,16 +6471,16 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B186" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="C186" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="D186" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
@@ -6476,16 +6488,16 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="B187" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C187" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D187" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="E187" t="s">
         <v>10</v>
@@ -6493,16 +6505,16 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="B188" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C188" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="D188" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
@@ -6510,16 +6522,16 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B189" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C189" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D189" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E189" t="s">
         <v>10</v>
@@ -6527,13 +6539,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="B190" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C190" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D190" t="s">
         <v>567</v>
@@ -6544,16 +6556,16 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B191" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="C191" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="D191" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
@@ -6561,13 +6573,16 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B192" t="s">
-        <v>581</v>
+        <v>573</v>
+      </c>
+      <c r="C192" t="s">
+        <v>574</v>
       </c>
       <c r="D192" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
@@ -6575,16 +6590,16 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B193" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C193" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D193" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
@@ -6592,16 +6607,16 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B194" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C194" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="D194" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
@@ -6609,16 +6624,16 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B195" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C195" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D195" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
@@ -6626,16 +6641,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B196" t="s">
-        <v>593</v>
-      </c>
-      <c r="C196" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="D196" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
@@ -6643,16 +6655,16 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B197" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C197" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D197" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
@@ -6660,16 +6672,16 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B198" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="C198" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D198" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -6677,13 +6689,16 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B199" t="s">
-        <v>602</v>
+        <v>594</v>
+      </c>
+      <c r="C199" t="s">
+        <v>595</v>
       </c>
       <c r="D199" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -6691,16 +6706,16 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B200" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C200" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="D200" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
@@ -6708,16 +6723,16 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B201" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C201" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="D201" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -6725,16 +6740,16 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B202" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C202" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="D202" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E202" t="s">
         <v>10</v>
@@ -6742,16 +6757,13 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="B203" t="s">
-        <v>614</v>
-      </c>
-      <c r="C203" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D203" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -6759,16 +6771,16 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B204" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="C204" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D204" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E204" t="s">
         <v>10</v>
@@ -6776,16 +6788,16 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B205" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="C205" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="D205" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E205" t="s">
         <v>10</v>
@@ -6793,16 +6805,16 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B206" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="C206" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="D206" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
@@ -6810,16 +6822,16 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B207" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="C207" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="D207" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -6827,16 +6839,16 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B208" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="C208" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="D208" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -6844,16 +6856,16 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B209" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C209" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D209" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -6861,16 +6873,16 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B210" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C210" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="D210" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -6878,16 +6890,16 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B211" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C211" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="D211" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E211" t="s">
         <v>10</v>
@@ -6895,16 +6907,16 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B212" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C212" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="D212" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
@@ -6912,16 +6924,16 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B213" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C213" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D213" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -6929,16 +6941,16 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B214" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C214" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="D214" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -6946,13 +6958,16 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="B215" t="s">
-        <v>651</v>
+        <v>643</v>
+      </c>
+      <c r="C215" t="s">
+        <v>644</v>
       </c>
       <c r="D215" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -6960,16 +6975,16 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B216" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C216" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="D216" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
@@ -6977,16 +6992,16 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B217" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C217" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D217" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
@@ -6994,16 +7009,16 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="B218" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="C218" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D218" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
@@ -7011,16 +7026,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="B219" t="s">
-        <v>662</v>
-      </c>
-      <c r="C219" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D219" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
@@ -7028,16 +7040,16 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="B220" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="C220" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D220" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
@@ -7045,16 +7057,16 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="B221" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C221" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="D221" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
@@ -7062,16 +7074,16 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B222" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C222" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="D222" t="s">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
@@ -7079,16 +7091,16 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="B223" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="C223" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="D223" t="s">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="E223" t="s">
         <v>10</v>
@@ -7096,16 +7108,16 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="B224" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="C224" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D224" t="s">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="E224" t="s">
         <v>10</v>
@@ -7113,13 +7125,16 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B225" t="s">
-        <v>681</v>
+        <v>672</v>
+      </c>
+      <c r="C225" t="s">
+        <v>673</v>
       </c>
       <c r="D225" t="s">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="E225" t="s">
         <v>10</v>
@@ -7127,16 +7142,16 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B226" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C226" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D226" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E226" t="s">
         <v>10</v>
@@ -7144,13 +7159,16 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B227" t="s">
-        <v>686</v>
+        <v>679</v>
+      </c>
+      <c r="C227" t="s">
+        <v>680</v>
       </c>
       <c r="D227" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="E227" t="s">
         <v>10</v>
@@ -7158,16 +7176,16 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B228" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C228" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D228" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="E228" t="s">
         <v>10</v>
@@ -7175,16 +7193,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B229" t="s">
-        <v>692</v>
-      </c>
-      <c r="C229" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="D229" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="E229" t="s">
         <v>10</v>
@@ -7192,13 +7207,16 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B230" t="s">
-        <v>695</v>
+        <v>687</v>
+      </c>
+      <c r="C230" t="s">
+        <v>688</v>
       </c>
       <c r="D230" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
@@ -7206,16 +7224,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B231" t="s">
-        <v>697</v>
-      </c>
-      <c r="C231" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D231" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="E231" t="s">
         <v>10</v>
@@ -7223,16 +7238,16 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B232" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="C232" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="D232" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E232" t="s">
         <v>10</v>
@@ -7240,16 +7255,16 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B233" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C233" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="D233" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
@@ -7257,13 +7272,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B234" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="D234" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
@@ -7271,16 +7286,16 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B235" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="C235" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="D235" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E235" t="s">
         <v>10</v>
@@ -7288,13 +7303,16 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B236" t="s">
-        <v>712</v>
+        <v>704</v>
+      </c>
+      <c r="C236" t="s">
+        <v>705</v>
       </c>
       <c r="D236" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E236" t="s">
         <v>10</v>
@@ -7302,16 +7320,16 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="B237" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C237" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="D237" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E237" t="s">
         <v>10</v>
@@ -7319,16 +7337,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="B238" t="s">
-        <v>717</v>
-      </c>
-      <c r="C238" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="D238" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E238" t="s">
         <v>10</v>
@@ -7336,16 +7351,16 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="B239" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C239" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="D239" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E239" t="s">
         <v>10</v>
@@ -7353,16 +7368,13 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B240" t="s">
-        <v>723</v>
-      </c>
-      <c r="C240" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="D240" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E240" t="s">
         <v>10</v>
@@ -7370,13 +7382,16 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B241" t="s">
-        <v>726</v>
+        <v>718</v>
+      </c>
+      <c r="C241" t="s">
+        <v>719</v>
       </c>
       <c r="D241" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E241" t="s">
         <v>10</v>
@@ -7384,13 +7399,16 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="B242" t="s">
-        <v>728</v>
+        <v>721</v>
+      </c>
+      <c r="C242" t="s">
+        <v>722</v>
       </c>
       <c r="D242" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
@@ -7398,16 +7416,16 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B243" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="C243" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D243" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E243" t="s">
         <v>10</v>
@@ -7415,16 +7433,16 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="B244" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C244" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="D244" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
@@ -7432,16 +7450,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="B245" t="s">
-        <v>736</v>
-      </c>
-      <c r="C245" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="D245" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
@@ -7449,13 +7464,13 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B246" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="D246" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
@@ -7463,16 +7478,16 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B247" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="C247" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D247" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
@@ -7480,16 +7495,16 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B248" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="C248" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="D248" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
@@ -7497,16 +7512,16 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B249" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="C249" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="D249" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
@@ -7514,16 +7529,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="B250" t="s">
-        <v>750</v>
-      </c>
-      <c r="C250" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="D250" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
@@ -7531,16 +7543,16 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="B251" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="C251" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="D251" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
@@ -7548,16 +7560,16 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="B252" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="C252" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="D252" t="s">
-        <v>758</v>
+        <v>709</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
@@ -7565,16 +7577,16 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="B253" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="C253" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="D253" t="s">
-        <v>758</v>
+        <v>709</v>
       </c>
       <c r="E253" t="s">
         <v>10</v>
@@ -7582,16 +7594,16 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="B254" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="C254" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D254" t="s">
-        <v>758</v>
+        <v>709</v>
       </c>
       <c r="E254" t="s">
         <v>10</v>
@@ -7599,16 +7611,16 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B255" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C255" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="D255" t="s">
-        <v>758</v>
+        <v>709</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
@@ -7616,16 +7628,16 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="B256" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="C256" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="D256" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
@@ -7633,16 +7645,16 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="B257" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="C257" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="D257" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
@@ -7650,16 +7662,16 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="B258" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="C258" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="D258" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
@@ -7667,16 +7679,16 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B259" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="C259" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="D259" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E259" t="s">
         <v>10</v>
@@ -7684,16 +7696,16 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="B260" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="C260" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="D260" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E260" t="s">
         <v>10</v>
@@ -7701,16 +7713,16 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="B261" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C261" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="D261" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E261" t="s">
         <v>10</v>
@@ -7718,16 +7730,16 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="B262" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="C262" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="D262" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
@@ -7735,16 +7747,16 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B263" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="C263" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="D263" t="s">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="E263" t="s">
         <v>10</v>
@@ -7752,16 +7764,16 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="B264" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C264" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="D264" t="s">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="E264" t="s">
         <v>10</v>
@@ -7769,16 +7781,16 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="B265" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="C265" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="D265" t="s">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
@@ -7786,13 +7798,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="B266" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="C266" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="D266" t="s">
         <v>793</v>
@@ -7803,16 +7815,16 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="B267" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="C267" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D267" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
@@ -7820,16 +7832,16 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="B268" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C268" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="D268" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
@@ -7837,13 +7849,16 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B269" t="s">
-        <v>810</v>
+        <v>802</v>
+      </c>
+      <c r="C269" t="s">
+        <v>803</v>
       </c>
       <c r="D269" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
@@ -7851,16 +7866,16 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="B270" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="C270" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="D270" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
@@ -7868,16 +7883,16 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B271" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="C271" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D271" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
@@ -7885,16 +7900,16 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="B272" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="C272" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="D272" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
@@ -7902,13 +7917,10 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B273" t="s">
-        <v>823</v>
-      </c>
-      <c r="C273" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="D273" t="s">
         <v>815</v>
@@ -7919,30 +7931,33 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="B274" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="C274" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="D274" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E274" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="B275" t="s">
-        <v>829</v>
+        <v>821</v>
+      </c>
+      <c r="C275" t="s">
+        <v>822</v>
       </c>
       <c r="D275" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
@@ -7950,16 +7965,16 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="B276" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="C276" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="D276" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
@@ -7967,53 +7982,47 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="B277" t="s">
-        <v>834</v>
+        <v>827</v>
+      </c>
+      <c r="C277" t="s">
+        <v>828</v>
       </c>
       <c r="D277" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
-      </c>
-      <c r="F277" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B278" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="C278" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D278" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="E278" t="s">
-        <v>10</v>
-      </c>
-      <c r="F278" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="B279" t="s">
-        <v>841</v>
-      </c>
-      <c r="C279" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="D279" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="E279" t="s">
         <v>10</v>
@@ -8021,16 +8030,16 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="B280" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="C280" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="D280" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="E280" t="s">
         <v>10</v>
@@ -8038,53 +8047,53 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="B281" t="s">
-        <v>847</v>
-      </c>
-      <c r="C281" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D281" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E281" t="s">
         <v>10</v>
       </c>
       <c r="F281" t="s">
-        <v>27</v>
+        <v>840</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="B282" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="C282" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="D282" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E282" t="s">
         <v>10</v>
+      </c>
+      <c r="F282" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="B283" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C283" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="D283" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E283" t="s">
         <v>10</v>
@@ -8092,53 +8101,53 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="B284" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="C284" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="D284" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E284" t="s">
         <v>10</v>
-      </c>
-      <c r="F284" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="B285" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C285" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D285" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E285" t="s">
         <v>10</v>
+      </c>
+      <c r="F285" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="B286" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="C286" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="D286" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E286" t="s">
         <v>10</v>
@@ -8146,16 +8155,16 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="B287" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="C287" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="D287" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E287" t="s">
         <v>10</v>
@@ -8163,73 +8172,70 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="B288" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="C288" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="D288" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E288" t="s">
         <v>10</v>
+      </c>
+      <c r="F288" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="B289" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="C289" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="D289" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E289" t="s">
         <v>10</v>
-      </c>
-      <c r="F289" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="B290" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="C290" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="D290" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E290" t="s">
         <v>10</v>
-      </c>
-      <c r="F290" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="B291" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C291" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="D291" t="s">
-        <v>878</v>
+        <v>839</v>
       </c>
       <c r="E291" t="s">
         <v>10</v>
@@ -8237,70 +8243,73 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B292" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="C292" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="D292" t="s">
-        <v>882</v>
+        <v>839</v>
       </c>
       <c r="E292" t="s">
         <v>10</v>
-      </c>
-      <c r="F292" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="B293" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C293" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D293" t="s">
-        <v>886</v>
+        <v>839</v>
       </c>
       <c r="E293" t="s">
         <v>10</v>
+      </c>
+      <c r="F293" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="B294" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="C294" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="D294" t="s">
-        <v>886</v>
+        <v>839</v>
       </c>
       <c r="E294" t="s">
         <v>10</v>
+      </c>
+      <c r="F294" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B295" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C295" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="D295" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="E295" t="s">
         <v>10</v>
@@ -8308,30 +8317,36 @@
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B296" t="s">
-        <v>895</v>
+        <v>884</v>
+      </c>
+      <c r="C296" t="s">
+        <v>885</v>
       </c>
       <c r="D296" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="E296" t="s">
         <v>10</v>
+      </c>
+      <c r="F296" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="B297" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="C297" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="D297" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E297" t="s">
         <v>10</v>
@@ -8339,13 +8354,16 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="B298" t="s">
-        <v>900</v>
+        <v>892</v>
+      </c>
+      <c r="C298" t="s">
+        <v>893</v>
       </c>
       <c r="D298" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E298" t="s">
         <v>10</v>
@@ -8353,16 +8371,16 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="B299" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C299" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D299" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E299" t="s">
         <v>10</v>
@@ -8370,16 +8388,13 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="B300" t="s">
-        <v>905</v>
-      </c>
-      <c r="C300" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D300" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E300" t="s">
         <v>10</v>
@@ -8387,16 +8402,16 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="B301" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="C301" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="D301" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="E301" t="s">
         <v>10</v>
@@ -8404,16 +8419,13 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="B302" t="s">
-        <v>911</v>
-      </c>
-      <c r="C302" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="D302" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="E302" t="s">
         <v>10</v>
@@ -8421,16 +8433,16 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B303" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="C303" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="D303" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="E303" t="s">
         <v>10</v>
@@ -8438,16 +8450,16 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B304" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="C304" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D304" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="E304" t="s">
         <v>10</v>
@@ -8455,16 +8467,16 @@
     </row>
     <row r="305" spans="1:5">
       <c r="A305" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="B305" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="C305" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="D305" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="E305" t="s">
         <v>10</v>
@@ -8472,16 +8484,16 @@
     </row>
     <row r="306" spans="1:5">
       <c r="A306" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="B306" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C306" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D306" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E306" t="s">
         <v>10</v>
@@ -8489,16 +8501,16 @@
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="B307" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="C307" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="D307" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="E307" t="s">
         <v>10</v>
@@ -8506,33 +8518,33 @@
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="B308" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="C308" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D308" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="E308" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="B309" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="C309" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
       <c r="D309" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="E309" t="s">
         <v>10</v>
@@ -8540,13 +8552,16 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="B310" t="s">
-        <v>938</v>
+        <v>928</v>
+      </c>
+      <c r="C310" t="s">
+        <v>929</v>
       </c>
       <c r="D310" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="E310" t="s">
         <v>10</v>
@@ -8554,64 +8569,64 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="B311" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="C311" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="D311" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="E311" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="B312" t="s">
-        <v>945</v>
+        <v>935</v>
+      </c>
+      <c r="C312" t="s">
+        <v>936</v>
       </c>
       <c r="D312" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E312" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="B313" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="C313" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="D313" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E313" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="B314" t="s">
-        <v>950</v>
-      </c>
-      <c r="C314" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="D314" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="E314" t="s">
         <v>10</v>
@@ -8619,67 +8634,64 @@
     </row>
     <row r="315" spans="1:5">
       <c r="A315" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B315" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="C315" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="D315" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="E315" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="B316" t="s">
-        <v>957</v>
-      </c>
-      <c r="C316" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="D316" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="E316" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="317" spans="1:5">
       <c r="A317" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B317" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="C317" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="D317" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="E317" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="B318" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="C318" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="D318" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E318" t="s">
         <v>10</v>
@@ -8687,16 +8699,16 @@
     </row>
     <row r="319" spans="1:5">
       <c r="A319" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="B319" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="C319" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="D319" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E319" t="s">
         <v>10</v>
@@ -8704,16 +8716,16 @@
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="B320" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="C320" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="D320" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E320" t="s">
         <v>10</v>
@@ -8721,16 +8733,16 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="B321" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="C321" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D321" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E321" t="s">
         <v>10</v>
@@ -8738,16 +8750,16 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="B322" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="C322" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="D322" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E322" t="s">
         <v>10</v>
@@ -8755,38 +8767,106 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="B323" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="C323" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="D323" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="E323" t="s">
         <v>10</v>
-      </c>
-      <c r="F323" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
+        <v>972</v>
+      </c>
+      <c r="B324" t="s">
+        <v>973</v>
+      </c>
+      <c r="C324" t="s">
+        <v>974</v>
+      </c>
+      <c r="D324" t="s">
+        <v>956</v>
+      </c>
+      <c r="E324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" t="s">
+        <v>975</v>
+      </c>
+      <c r="B325" t="s">
+        <v>976</v>
+      </c>
+      <c r="C325" t="s">
+        <v>977</v>
+      </c>
+      <c r="D325" t="s">
+        <v>956</v>
+      </c>
+      <c r="E325" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" t="s">
+        <v>978</v>
+      </c>
+      <c r="B326" t="s">
+        <v>979</v>
+      </c>
+      <c r="C326" t="s">
+        <v>980</v>
+      </c>
+      <c r="D326" t="s">
+        <v>956</v>
+      </c>
+      <c r="E326" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" t="s">
         <v>981</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B327" t="s">
         <v>982</v>
       </c>
-      <c r="C324" t="s">
+      <c r="C327" t="s">
         <v>983</v>
       </c>
-      <c r="D324" t="s">
-        <v>980</v>
-      </c>
-      <c r="E324" t="s">
+      <c r="D327" t="s">
+        <v>984</v>
+      </c>
+      <c r="E327" t="s">
+        <v>10</v>
+      </c>
+      <c r="F327" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" t="s">
+        <v>985</v>
+      </c>
+      <c r="B328" t="s">
+        <v>986</v>
+      </c>
+      <c r="C328" t="s">
+        <v>987</v>
+      </c>
+      <c r="D328" t="s">
+        <v>984</v>
+      </c>
+      <c r="E328" t="s">
         <v>10</v>
       </c>
     </row>

--- a/api/clv2/xlsx/en/Sector.xlsx
+++ b/api/clv2/xlsx/en/Sector.xlsx
@@ -895,7 +895,7 @@
     <t>Human rights</t>
   </si>
   <si>
-    <t>Measures to support specialised official human rights institutions and mechanisms at universal, regional, national and local levels in their statutory roles to promote and protect civil and political, economic, social and cultural rights as defined in international conventions and covenants; translation of international human rights commitments into national legislation; reporting and follow-up; human rights dialogue. Human rights defenders and human rights NGOs; human rights advocacy, activism, mobilisation; awareness raising and public human rights education. Human rights programming targeting specific groups, e.g. children, persons with disabilities, migrants, ethnic, religious, linguistic and sexual minorities, indigenous people and those suffering from caste discrimination, victims of trafficking, victims of torture. (Use code 15230 when in the context of a peacekeeping operation and code 15180 for ending violence against women and girls. Use code 15190 for human rights programming for refugees or migrants, including when they are victims of trafficking.Use code 16070 for Fundamental Principles and Rights at Work, i.e. Child Labour, Forced Labour, Non-discrimination in employment and occupation, Freedom of Association and Collective Bargaining.)</t>
+    <t>Measures to support specialised official human rights institutions and mechanisms at universal, regional, national and local levels in their statutory roles to promote and protect civil and political, economic, social and cultural rights as defined in international conventions and covenants; translation of international human rights commitments into national legislation; reporting and follow-up; human rights dialogue. Human rights defenders and human rights NGOs; human rights advocacy, activism, mobilisation; awareness raising and public human rights education. Human rights programming targeting specific groups, e.g. children, persons with disabilities, ethnic, religious, linguistic and sexual minorities, indigenous people and those suffering from caste discrimination, victims of trafficking, victims of torture. (Use code 15230 when in the context of a peacekeeping operation and code 15180 for ending violence against women and girls. Use code 15190 for human rights programming for refugees or migrants, including when they are victims of trafficking.Use code 16070 for Fundamental Principles and Rights at Work, i.e. Child Labour, Forced Labour, Non-discrimination in employment and occupation, Freedom of Association and Collective Bargaining.)</t>
   </si>
   <si>
     <t>15161</t>
@@ -2293,7 +2293,7 @@
     <t>32174</t>
   </si>
   <si>
-    <t>Clean cooking appliances manufacturing</t>
+    <t>Clean cooking appliances manufacturing, market development and distribution</t>
   </si>
   <si>
     <t>Includes manufacturing and distribution of efficient biomass cooking stoves, gasifiers, liquid biofuels stoves, solar stoves, gas and biogas stoves, electric stoves.</t>
